--- a/data/proteomics/ecGEM_absolute_pro_across_compartment.xlsx
+++ b/data/proteomics/ecGEM_absolute_pro_across_compartment.xlsx
@@ -1037,16 +1037,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002789089909112443</v>
+        <v>0.002789089909112446</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003261946963489568</v>
+        <v>0.003261946963489564</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002985435584777134</v>
+        <v>0.002985435584777132</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002196174576519605</v>
+        <v>0.002196174576519606</v>
       </c>
       <c r="F2" t="n">
         <v>0.001554505329837952</v>
@@ -1055,22 +1055,22 @@
         <v>0.001628162641109837</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001424243781485717</v>
+        <v>0.001424243781485716</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001426433783978344</v>
+        <v>0.001426433783978345</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001394776382373676</v>
+        <v>0.001394776382373677</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00139565184923646</v>
+        <v>0.001395651849236461</v>
       </c>
       <c r="L2" t="n">
         <v>0.001478727074812343</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002091681617060734</v>
+        <v>0.002091681617060732</v>
       </c>
       <c r="N2" t="n">
         <v>0.002130349303924622</v>
@@ -1079,7 +1079,7 @@
         <v>0.001944798220975429</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002337050695204704</v>
+        <v>0.002337050695204707</v>
       </c>
       <c r="Q2" t="n">
         <v>0.001389921121527817</v>
@@ -1088,19 +1088,19 @@
         <v>0.002486697357324459</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002483024743292037</v>
+        <v>0.002483024743292039</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002647579501936081</v>
+        <v>0.002647579501936082</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003075047430155734</v>
+        <v>0.003075047430155733</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003165996751038781</v>
+        <v>0.00316599675103878</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002750579116873123</v>
+        <v>0.002750579116873124</v>
       </c>
       <c r="X2" t="n">
         <v>0.001718766626401084</v>
@@ -1109,43 +1109,43 @@
         <v>0.002174994579390263</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001187508468748142</v>
+        <v>0.001187508468748141</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001975801108823517</v>
+        <v>0.001975801108823518</v>
       </c>
       <c r="AB2" t="n">
         <v>0.001460744581266093</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.001918146401735119</v>
+        <v>0.001918146401735118</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.002279597035932454</v>
+        <v>0.002279597035932452</v>
       </c>
       <c r="AE2" t="n">
         <v>0.002856405310946128</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.002403471768803232</v>
+        <v>0.002403471768803231</v>
       </c>
       <c r="AG2" t="n">
         <v>0.002257162991080483</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.002087573838834057</v>
+        <v>0.002087573838834056</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.002130994005406564</v>
+        <v>0.002130994005406565</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.001779320199232576</v>
+        <v>0.001779320199232575</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.002229780770924003</v>
+        <v>0.002229780770924002</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.002014272657407696</v>
+        <v>0.002014272657407697</v>
       </c>
       <c r="AM2" t="n">
         <v>0.001929213357103222</v>
@@ -1166,19 +1166,19 @@
         <v>0.001692890160240495</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.001132055144528843</v>
+        <v>0.001132055144528844</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.001168372555359731</v>
+        <v>0.001168372555359732</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.001575950372277129</v>
+        <v>0.001575950372277131</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.002255374866666666</v>
+        <v>0.002255374866666667</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.002184562727940543</v>
+        <v>0.002184562727940542</v>
       </c>
       <c r="AX2" t="n">
         <v>0.002104601662986183</v>
@@ -1190,34 +1190,34 @@
         <v>0.002639808840198625</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.004632372349213295</v>
+        <v>0.004632372349213293</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.002668216445547569</v>
+        <v>0.002668216445547567</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.004593450969256783</v>
+        <v>0.004593450969256785</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.002101101616301523</v>
+        <v>0.002101101616301526</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.002644052098955674</v>
+        <v>0.002644052098955676</v>
       </c>
       <c r="BF2" t="n">
         <v>0.002545718614304898</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.002835660686174028</v>
+        <v>0.002835660686174027</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.002706242834833999</v>
+        <v>0.002706242834834002</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.003747387877857536</v>
+        <v>0.003747387877857538</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.003706208915424827</v>
+        <v>0.003706208915424828</v>
       </c>
       <c r="BK2" t="n">
         <v>0.003686241299394129</v>
@@ -1226,85 +1226,85 @@
         <v>0.003181353719329045</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.004033248271664659</v>
+        <v>0.004033248271664658</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.004040923374042935</v>
+        <v>0.004040923374042934</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.004288052833700116</v>
+        <v>0.004288052833700113</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.003909022933193027</v>
+        <v>0.003909022933193026</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.003745110287647575</v>
+        <v>0.003745110287647577</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.003049252700574094</v>
+        <v>0.003049252700574093</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.004293678498550643</v>
+        <v>0.004293678498550642</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.004631520566891492</v>
+        <v>0.004631520566891494</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.002252902970923498</v>
+        <v>0.002252902970923499</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.002166721066990613</v>
+        <v>0.002166721066990611</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.004336498143661241</v>
+        <v>0.004336498143661243</v>
       </c>
       <c r="BX2" t="n">
         <v>0.004264604022460171</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.005959005379741445</v>
+        <v>0.005959005379741454</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.00455847125931526</v>
+        <v>0.004558471259315262</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.004664884701021463</v>
+        <v>0.004664884701021462</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.00206976235135736</v>
+        <v>0.002069762351357361</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.002720839204821043</v>
+        <v>0.002720839204821042</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.002454215271207162</v>
+        <v>0.002454215271207165</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.00258813050447753</v>
+        <v>0.002588130504477531</v>
       </c>
       <c r="CF2" t="n">
         <v>0.002668354227325503</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.002850408685037662</v>
+        <v>0.002850408685037661</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.002053846843991832</v>
+        <v>0.002053846843991833</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.002333210620826676</v>
+        <v>0.002333210620826675</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.002384081749479943</v>
+        <v>0.002384081749479945</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.00224875342068901</v>
+        <v>0.002248753420689009</v>
       </c>
       <c r="CL2" t="n">
         <v>0.001889592188304577</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.00121005688272612</v>
+        <v>0.001210056882726121</v>
       </c>
       <c r="CN2" t="n">
         <v>0.001237050827577813</v>
@@ -1316,10 +1316,10 @@
         <v>0.001223392443903345</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.00123640377007429</v>
+        <v>0.001236403770074289</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.001214400374035062</v>
+        <v>0.001214400374035061</v>
       </c>
       <c r="CS2" t="n">
         <v>0.001242846015879849</v>
@@ -1340,13 +1340,13 @@
         <v>0.001240585477437071</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.001237697028597786</v>
+        <v>0.001237697028597788</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.001239470718663824</v>
+        <v>0.001239470718663826</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.001245094783342514</v>
+        <v>0.001245094783342515</v>
       </c>
       <c r="DB2" t="n">
         <v>0.001231314727660475</v>
@@ -1355,13 +1355,13 @@
         <v>0.001250480110833282</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.001237503542587311</v>
+        <v>0.001237503542587313</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.001288988403303318</v>
+        <v>0.001288988403303319</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.001279679014722205</v>
+        <v>0.001279679014722206</v>
       </c>
       <c r="DG2" t="n">
         <v>0.001273975137244672</v>
@@ -1370,19 +1370,19 @@
         <v>0.00129302629566564</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.001307240600822645</v>
+        <v>0.001307240600822644</v>
       </c>
       <c r="DJ2" t="n">
         <v>0.001314069203133028</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.001261950283330128</v>
+        <v>0.001261950283330127</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.001274852726501692</v>
+        <v>0.001274852726501693</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.001343127625318067</v>
+        <v>0.001343127625318068</v>
       </c>
       <c r="DN2" t="n">
         <v>0.001252390618634323</v>
@@ -1391,7 +1391,7 @@
         <v>0.001257302077167623</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.001266997785620201</v>
+        <v>0.001266997785620202</v>
       </c>
     </row>
     <row r="3">
@@ -1726,7 +1726,7 @@
         <v>4.767834035587528e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>5.049267802991104e-07</v>
+        <v>5.049267802991105e-07</v>
       </c>
       <c r="D4" t="n">
         <v>4.949835390905707e-07</v>
@@ -1735,7 +1735,7 @@
         <v>1.65644048540019e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5561011412e-07</v>
+        <v>2.556101141199999e-07</v>
       </c>
       <c r="G4" t="n">
         <v>4.20707329624e-07</v>
@@ -1825,7 +1825,7 @@
         <v>4.02290951677e-07</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.62856207976e-07</v>
+        <v>2.628562079760001e-07</v>
       </c>
       <c r="AK4" t="n">
         <v>3.59947243908e-07</v>
@@ -1858,7 +1858,7 @@
         <v>2.54703901474e-07</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.77206964128e-07</v>
+        <v>4.772069641279999e-07</v>
       </c>
       <c r="AV4" t="n">
         <v>9.891000000000002e-07</v>
@@ -1867,13 +1867,13 @@
         <v>6.691943429667282e-07</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.23893337213154e-07</v>
+        <v>7.238933372131541e-07</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.796544518539034e-07</v>
+        <v>5.796544518539035e-07</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.39383438269831e-07</v>
+        <v>6.393834382698311e-07</v>
       </c>
       <c r="BA4" t="n">
         <v>3.440951093570464e-06</v>
@@ -1930,43 +1930,43 @@
         <v>3.820476867319827e-06</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.691764426669344e-07</v>
+        <v>5.691764426669343e-07</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.156559378790998e-07</v>
+        <v>6.156559378790999e-07</v>
       </c>
       <c r="BU4" t="n">
-        <v>7.729045042318334e-07</v>
+        <v>7.729045042318335e-07</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.70361835691218e-07</v>
+        <v>7.703618356912181e-07</v>
       </c>
       <c r="BW4" t="n">
         <v>6.110027489717852e-07</v>
       </c>
       <c r="BX4" t="n">
-        <v>6.238862903747154e-07</v>
+        <v>6.238862903747153e-07</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.395783308957553e-07</v>
+        <v>7.395783308957554e-07</v>
       </c>
       <c r="BZ4" t="n">
-        <v>6.415697780808363e-07</v>
+        <v>6.415697780808361e-07</v>
       </c>
       <c r="CA4" t="n">
         <v>7.064259100681293e-07</v>
       </c>
       <c r="CB4" t="n">
-        <v>9.211872358071799e-07</v>
+        <v>9.211872358071798e-07</v>
       </c>
       <c r="CC4" t="n">
-        <v>7.456631021065158e-07</v>
+        <v>7.456631021065157e-07</v>
       </c>
       <c r="CD4" t="n">
         <v>1.391379266242516e-06</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.515271905560311e-06</v>
+        <v>1.515271905560312e-06</v>
       </c>
       <c r="CF4" t="n">
         <v>2.107280632638379e-06</v>
@@ -2023,7 +2023,7 @@
         <v>5.147670921952869e-07</v>
       </c>
       <c r="CX4" t="n">
-        <v>4.79371865455497e-07</v>
+        <v>4.793718654554969e-07</v>
       </c>
       <c r="CY4" t="n">
         <v>4.432104603456684e-07</v>
@@ -2038,7 +2038,7 @@
         <v>4.99434811771491e-07</v>
       </c>
       <c r="DC4" t="n">
-        <v>4.643428623531338e-07</v>
+        <v>4.643428623531339e-07</v>
       </c>
       <c r="DD4" t="n">
         <v>4.946804767287208e-07</v>
@@ -2068,7 +2068,7 @@
         <v>4.677650526335634e-07</v>
       </c>
       <c r="DM4" t="n">
-        <v>4.894770649092914e-07</v>
+        <v>4.894770649092915e-07</v>
       </c>
       <c r="DN4" t="n">
         <v>4.678943681136179e-07</v>
@@ -2451,58 +2451,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001517172110086583</v>
+        <v>0.001517172110086582</v>
       </c>
       <c r="C6" t="n">
         <v>0.000907161168834068</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0007910250416219663</v>
+        <v>0.0007910250416219666</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001018370535335372</v>
+        <v>0.001018370535335371</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0006809576837215202</v>
+        <v>0.0006809576837215199</v>
       </c>
       <c r="G6" t="n">
         <v>0.0007413553883853359</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0006777698786108077</v>
+        <v>0.0006777698786108076</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000648863878355667</v>
+        <v>0.0006488638783556673</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0005996363158010768</v>
+        <v>0.0005996363158010773</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0006298683277803272</v>
+        <v>0.0006298683277803271</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0006729246035505318</v>
+        <v>0.0006729246035505319</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009472159598732002</v>
+        <v>0.0009472159598732</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009552340755060922</v>
+        <v>0.0009552340755060913</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0008935516315664512</v>
+        <v>0.000893551631566451</v>
       </c>
       <c r="P6" t="n">
         <v>0.001092349573714423</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.000604173884546236</v>
+        <v>0.0006041738845462363</v>
       </c>
       <c r="R6" t="n">
         <v>0.001177051307197048</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001091168343543609</v>
+        <v>0.001091168343543608</v>
       </c>
       <c r="T6" t="n">
         <v>0.001162764740028258</v>
@@ -2517,52 +2517,52 @@
         <v>0.001229009438949799</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0006511368885527281</v>
+        <v>0.0006511368885527276</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0008634413394306489</v>
+        <v>0.000863441339430649</v>
       </c>
       <c r="Z6" t="n">
         <v>0.000481476391599704</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0008160191779724464</v>
+        <v>0.0008160191779724462</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0006699175509989459</v>
+        <v>0.0006699175509989457</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0008166917101082262</v>
+        <v>0.0008166917101082256</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0009671104444196924</v>
+        <v>0.000967110444419692</v>
       </c>
       <c r="AE6" t="n">
         <v>0.001258756341002262</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0009762795871151673</v>
+        <v>0.0009762795871151676</v>
       </c>
       <c r="AG6" t="n">
         <v>0.001029653907384779</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0008676597859003032</v>
+        <v>0.000867659785900303</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.000848325521232799</v>
+        <v>0.0008483255212327988</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0006536127986632184</v>
+        <v>0.0006536127986632179</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0009320673566888116</v>
+        <v>0.0009320673566888113</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0006970971927042915</v>
+        <v>0.0006970971927042919</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0008402638097944402</v>
+        <v>0.00084026380979444</v>
       </c>
       <c r="AN6" t="n">
         <v>0.001046516732959581</v>
@@ -2574,43 +2574,43 @@
         <v>0.0010544931836897</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0009446252311596148</v>
+        <v>0.0009446252311596153</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0007110489200537888</v>
+        <v>0.0007110489200537887</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.000547014625181137</v>
+        <v>0.0005470146251811371</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0005587983044892318</v>
+        <v>0.0005587983044892321</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.00065937744821812</v>
+        <v>0.0006593774482181199</v>
       </c>
       <c r="AV6" t="n">
         <v>0.001037378033333334</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0006386694694071304</v>
+        <v>0.0006386694694071306</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0005484747843320167</v>
+        <v>0.0005484747843320174</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0006933205638113998</v>
+        <v>0.0006933205638113997</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0006155648967384228</v>
+        <v>0.0006155648967384225</v>
       </c>
       <c r="BA6" t="n">
         <v>0.001524737462699975</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.001217356698369616</v>
+        <v>0.001217356698369617</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.001800835855612344</v>
+        <v>0.001800835855612345</v>
       </c>
       <c r="BD6" t="n">
         <v>0.00103856192391463</v>
@@ -2622,7 +2622,7 @@
         <v>0.001070429310811168</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.001103382733073639</v>
+        <v>0.00110338273307364</v>
       </c>
       <c r="BH6" t="n">
         <v>0.001073739604374053</v>
@@ -2631,7 +2631,7 @@
         <v>0.001209983356926635</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.001191488952461691</v>
+        <v>0.00119148895246169</v>
       </c>
       <c r="BK6" t="n">
         <v>0.00101091353507074</v>
@@ -2649,136 +2649,136 @@
         <v>0.001370477475251594</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.001288753332503702</v>
+        <v>0.001288753332503703</v>
       </c>
       <c r="BQ6" t="n">
         <v>0.001256173470717203</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.001334581157779442</v>
+        <v>0.001334581157779441</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0006765593457452466</v>
+        <v>0.000676559345745247</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0006730639148965215</v>
+        <v>0.0006730639148965214</v>
       </c>
       <c r="BU6" t="n">
         <v>0.0005690087315505017</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0005628174997770615</v>
+        <v>0.0005628174997770618</v>
       </c>
       <c r="BW6" t="n">
         <v>0.0006182932043956599</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0006382714511713476</v>
+        <v>0.0006382714511713473</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0005391263945216694</v>
+        <v>0.0005391263945216695</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0006923160968336961</v>
+        <v>0.0006923160968336963</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0006144408527671524</v>
+        <v>0.000614440852767153</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0005221502033828371</v>
+        <v>0.0005221502033828372</v>
       </c>
       <c r="CC6" t="n">
         <v>0.0004798122103503246</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.0008293148446994606</v>
+        <v>0.0008293148446994602</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0008432426361361013</v>
+        <v>0.0008432426361361005</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0008712655821684414</v>
+        <v>0.0008712655821684409</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0009192620887719067</v>
+        <v>0.0009192620887719065</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0006511341803808787</v>
+        <v>0.0006511341803808789</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.000722365657594327</v>
+        <v>0.0007223656575943271</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.000759040763998469</v>
+        <v>0.0007590407639984688</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0007761112620528266</v>
+        <v>0.0007761112620528263</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0007116335261458146</v>
+        <v>0.000711633526145815</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0005539041348841125</v>
+        <v>0.0005539041348841126</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0005780620128966049</v>
+        <v>0.0005780620128966047</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0005535583722732743</v>
+        <v>0.0005535583722732744</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0005700280482615842</v>
+        <v>0.0005700280482615841</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0005697893939936831</v>
+        <v>0.0005697893939936834</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0005610520264992133</v>
+        <v>0.0005610520264992136</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.000591107729978316</v>
+        <v>0.0005911077299783158</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0005933955054579772</v>
+        <v>0.0005933955054579766</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0005942450297246014</v>
+        <v>0.0005942450297246009</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0005843231764583777</v>
+        <v>0.0005843231764583776</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.000589782359613149</v>
+        <v>0.0005897823596131487</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.0005902077487280802</v>
+        <v>0.00059020774872808</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0005821504702350958</v>
+        <v>0.0005821504702350962</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0005921505950543069</v>
+        <v>0.0005921505950543071</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0005858707263415544</v>
+        <v>0.000585870726341555</v>
       </c>
       <c r="DB6" t="n">
         <v>0.0005907738276034113</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.0005933652801908319</v>
+        <v>0.0005933652801908316</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.0005900100415158605</v>
+        <v>0.0005900100415158604</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.000590140449504905</v>
+        <v>0.0005901404495049052</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0005929363630136867</v>
+        <v>0.0005929363630136863</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.0005868962083948631</v>
+        <v>0.0005868962083948626</v>
       </c>
       <c r="DH6" t="n">
         <v>0.0005964568072855142</v>
@@ -2787,25 +2787,25 @@
         <v>0.000606707359252503</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0005980268106675347</v>
+        <v>0.0005980268106675349</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0005926686391573927</v>
+        <v>0.0005926686391573929</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0006050491151323017</v>
+        <v>0.0006050491151323015</v>
       </c>
       <c r="DM6" t="n">
         <v>0.0006111597539049073</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0005961861132289826</v>
+        <v>0.0005961861132289827</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0005955559121688798</v>
+        <v>0.0005955559121688797</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0005979156105338961</v>
+        <v>0.0005979156105338963</v>
       </c>
     </row>
     <row r="7">
@@ -2815,22 +2815,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003067389143782686</v>
+        <v>0.003067389143782689</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002729869001229307</v>
+        <v>0.002729869001229308</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002978525307045904</v>
+        <v>0.002978525307045905</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003001526250152221</v>
+        <v>0.00300152625015222</v>
       </c>
       <c r="F7" t="n">
         <v>0.00115411915638893</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00116002269304934</v>
+        <v>0.001160022693049341</v>
       </c>
       <c r="H7" t="n">
         <v>0.0009837223344501969</v>
@@ -2848,10 +2848,10 @@
         <v>0.001061592181304019</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0016602391408856</v>
+        <v>0.001660239140885598</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001678218386950699</v>
+        <v>0.0016782183869507</v>
       </c>
       <c r="O7" t="n">
         <v>0.001635268345641581</v>
@@ -2860,22 +2860,22 @@
         <v>0.001994791356937436</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001039800026148299</v>
+        <v>0.0010398000261483</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002068945977937834</v>
+        <v>0.002068945977937835</v>
       </c>
       <c r="S7" t="n">
         <v>0.002100675245290025</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002815656696559568</v>
+        <v>0.002815656696559569</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003421642685936557</v>
+        <v>0.003421642685936559</v>
       </c>
       <c r="V7" t="n">
-        <v>0.003384327338132427</v>
+        <v>0.003384327338132426</v>
       </c>
       <c r="W7" t="n">
         <v>0.002517566713940511</v>
@@ -2884,145 +2884,145 @@
         <v>0.001359230532772757</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001635558525337125</v>
+        <v>0.001635558525337123</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0007808639841957752</v>
+        <v>0.0007808639841957744</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001364423479177047</v>
+        <v>0.001364423479177048</v>
       </c>
       <c r="AB7" t="n">
         <v>0.001067983650604462</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.001374938319779312</v>
+        <v>0.001374938319779311</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001761009836300333</v>
+        <v>0.001761009836300335</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.00218990750756118</v>
+        <v>0.002189907507561178</v>
       </c>
       <c r="AF7" t="n">
         <v>0.00183180413091699</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.001557599507747437</v>
+        <v>0.001557599507747435</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.001381559304315967</v>
+        <v>0.001381559304315966</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.001476382811665842</v>
+        <v>0.001476382811665841</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.001475393044184338</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.002080156548802198</v>
+        <v>0.002080156548802197</v>
       </c>
       <c r="AL7" t="n">
         <v>0.001599642664338672</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.001963701163822054</v>
+        <v>0.001963701163822057</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.002057989301866075</v>
+        <v>0.002057989301866076</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.001834485991505038</v>
+        <v>0.001834485991505039</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.001822812802961447</v>
+        <v>0.001822812802961448</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.002044557450666652</v>
+        <v>0.002044557450666651</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.001755729589832836</v>
+        <v>0.001755729589832835</v>
       </c>
       <c r="AS7" t="n">
         <v>0.0008230158636599263</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0008738275891666519</v>
+        <v>0.0008738275891666513</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.001181642603504181</v>
+        <v>0.00118164260350418</v>
       </c>
       <c r="AV7" t="n">
         <v>0.002064501066666667</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.002688606493406349</v>
+        <v>0.002688606493406347</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.002107750212299076</v>
+        <v>0.002107750212299074</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.003646991575267922</v>
+        <v>0.003646991575267923</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.003093332050895814</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.003908303368174814</v>
+        <v>0.003908303368174815</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.002656105562662379</v>
+        <v>0.002656105562662376</v>
       </c>
       <c r="BC7" t="n">
         <v>0.004051460260283826</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.002263984025509434</v>
+        <v>0.002263984025509433</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.002475824775949872</v>
+        <v>0.00247582477594987</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.002435683776271324</v>
+        <v>0.002435683776271323</v>
       </c>
       <c r="BG7" t="n">
         <v>0.002536186844849401</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.002495387554492979</v>
+        <v>0.002495387554492981</v>
       </c>
       <c r="BI7" t="n">
         <v>0.002838428214826635</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.002506285269941132</v>
+        <v>0.002506285269941133</v>
       </c>
       <c r="BK7" t="n">
         <v>0.002252266390692279</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.00231882226671772</v>
+        <v>0.002318822266717718</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.002978192148444439</v>
+        <v>0.002978192148444437</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.002994816649841098</v>
+        <v>0.002994816649841099</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.003029068365381866</v>
+        <v>0.003029068365381869</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.003032578116403074</v>
+        <v>0.003032578116403073</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.002888770937668764</v>
+        <v>0.002888770937668765</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.003256686929316423</v>
+        <v>0.003256686929316422</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.002087332963288407</v>
+        <v>0.002087332963288406</v>
       </c>
       <c r="BT7" t="n">
         <v>0.00202568131120261</v>
@@ -3031,7 +3031,7 @@
         <v>0.002262775380447174</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.00196022299732421</v>
+        <v>0.001960222997324211</v>
       </c>
       <c r="BW7" t="n">
         <v>0.002016896467026586</v>
@@ -3040,25 +3040,25 @@
         <v>0.001966106543302526</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.001933425056976682</v>
+        <v>0.001933425056976683</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.001983060537403843</v>
+        <v>0.001983060537403845</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.001740885836819773</v>
+        <v>0.001740885836819772</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.001643818219972685</v>
+        <v>0.001643818219972686</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.001569682978328865</v>
+        <v>0.001569682978328866</v>
       </c>
       <c r="CD7" t="n">
         <v>0.001901300855256964</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.001928649173643302</v>
+        <v>0.001928649173643303</v>
       </c>
       <c r="CF7" t="n">
         <v>0.001980072033369642</v>
@@ -3073,7 +3073,7 @@
         <v>0.001684721556793959</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.001728268324958015</v>
+        <v>0.001728268324958016</v>
       </c>
       <c r="CK7" t="n">
         <v>0.001722323331822503</v>
@@ -3085,19 +3085,19 @@
         <v>0.001253946956159671</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.001277562936529722</v>
+        <v>0.00127756293652972</v>
       </c>
       <c r="CO7" t="n">
         <v>0.00125023466813746</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.001264995006006001</v>
+        <v>0.001264995006006</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.001275292473820558</v>
+        <v>0.001275292473820557</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.001261549404315202</v>
+        <v>0.001261549404315203</v>
       </c>
       <c r="CS7" t="n">
         <v>0.001330946624505364</v>
@@ -3112,31 +3112,31 @@
         <v>0.001324293409488969</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.001324408536920591</v>
+        <v>0.001324408536920592</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.001330152258640687</v>
+        <v>0.001330152258640688</v>
       </c>
       <c r="CY7" t="n">
         <v>0.001321055315474503</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0013309532127688</v>
+        <v>0.001330953212768801</v>
       </c>
       <c r="DA7" t="n">
         <v>0.001321916083334028</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.001333521932872392</v>
+        <v>0.001333521932872391</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.00133529249830084</v>
+        <v>0.001335292498300839</v>
       </c>
       <c r="DD7" t="n">
         <v>0.001327740769206227</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.001355016665108441</v>
+        <v>0.001355016665108444</v>
       </c>
       <c r="DF7" t="n">
         <v>0.001351066433276104</v>
@@ -3145,7 +3145,7 @@
         <v>0.001347383494403116</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.001377089143835409</v>
+        <v>0.001377089143835407</v>
       </c>
       <c r="DI7" t="n">
         <v>0.001393725210508333</v>
@@ -3163,10 +3163,10 @@
         <v>0.001378012118820775</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.001363873044597685</v>
+        <v>0.001363873044597684</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.001350934896659266</v>
+        <v>0.001350934896659265</v>
       </c>
       <c r="DP7" t="n">
         <v>0.001342325396346042</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002100510462592406</v>
+        <v>0.002100510462592407</v>
       </c>
       <c r="C8" t="n">
         <v>0.001895046452360417</v>
@@ -3194,46 +3194,46 @@
         <v>0.0008271428933847369</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0008645439839577341</v>
+        <v>0.000864543983957734</v>
       </c>
       <c r="H8" t="n">
-        <v>0.000772263012191321</v>
+        <v>0.0007722630121913211</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0007355408626357024</v>
+        <v>0.0007355408626357019</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0006535386756523972</v>
+        <v>0.0006535386756523969</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000693355697908238</v>
+        <v>0.0006933556979082377</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0007202914127668788</v>
+        <v>0.0007202914127668786</v>
       </c>
       <c r="M8" t="n">
         <v>0.001131153614807681</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001144495394398213</v>
+        <v>0.001144495394398214</v>
       </c>
       <c r="O8" t="n">
         <v>0.001074373258554613</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00138586832278534</v>
+        <v>0.001385868322785341</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.000702731298572263</v>
+        <v>0.0007027312985722629</v>
       </c>
       <c r="R8" t="n">
         <v>0.001534481125751709</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001426624510038333</v>
+        <v>0.001426624510038332</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0012960407681084</v>
+        <v>0.001296040768108399</v>
       </c>
       <c r="U8" t="n">
         <v>0.001439605898713449</v>
@@ -3245,31 +3245,31 @@
         <v>0.001220731697980852</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0008608978806600518</v>
+        <v>0.0008608978806600519</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001132000459232332</v>
+        <v>0.001132000459232331</v>
       </c>
       <c r="Z8" t="n">
         <v>0.0006214545978980252</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0009800356943220141</v>
+        <v>0.0009800356943220139</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0007419273006867911</v>
+        <v>0.0007419273006867909</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0009073322106913279</v>
+        <v>0.0009073322106913281</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0009230735426019359</v>
+        <v>0.0009230735426019358</v>
       </c>
       <c r="AE8" t="n">
         <v>0.001169651854608219</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0009445412445032146</v>
+        <v>0.0009445412445032151</v>
       </c>
       <c r="AG8" t="n">
         <v>0.001130929157122457</v>
@@ -3278,25 +3278,25 @@
         <v>0.001003592182808837</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0009685390031590709</v>
+        <v>0.0009685390031590707</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.0007971455345354092</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0009464258153049811</v>
+        <v>0.0009464258153049808</v>
       </c>
       <c r="AL8" t="n">
         <v>0.001032100836786488</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0009394734289056795</v>
+        <v>0.0009394734289056798</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001527887137142105</v>
+        <v>0.001527887137142106</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001396134450982847</v>
+        <v>0.001396134450982848</v>
       </c>
       <c r="AP8" t="n">
         <v>0.001465521309056457</v>
@@ -3305,25 +3305,25 @@
         <v>0.001016391622132914</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0007880134479967338</v>
+        <v>0.0007880134479967337</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0005936492824849146</v>
+        <v>0.0005936492824849148</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0005970634948660619</v>
+        <v>0.000597063494866062</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0009146027222371428</v>
+        <v>0.0009146027222371431</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001266130033333334</v>
+        <v>0.001266130033333333</v>
       </c>
       <c r="AW8" t="n">
         <v>0.001001353325778946</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0009821250070586134</v>
+        <v>0.0009821250070586136</v>
       </c>
       <c r="AY8" t="n">
         <v>0.001385092464708465</v>
@@ -3338,19 +3338,19 @@
         <v>0.001745718676149256</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.002698702211308841</v>
+        <v>0.002698702211308842</v>
       </c>
       <c r="BD8" t="n">
         <v>0.00145207657031868</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001482720423119658</v>
+        <v>0.001482720423119657</v>
       </c>
       <c r="BF8" t="n">
         <v>0.001447056362365234</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.00155160058903696</v>
+        <v>0.001551600589036959</v>
       </c>
       <c r="BH8" t="n">
         <v>0.001494748973052823</v>
@@ -3362,7 +3362,7 @@
         <v>0.001545779362900664</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.001380702166290202</v>
+        <v>0.001380702166290203</v>
       </c>
       <c r="BL8" t="n">
         <v>0.001261286189326685</v>
@@ -3374,10 +3374,10 @@
         <v>0.001851308025002989</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001923197859947143</v>
+        <v>0.001923197859947144</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001787588763581899</v>
+        <v>0.0017875887635819</v>
       </c>
       <c r="BQ8" t="n">
         <v>0.00165906310731707</v>
@@ -3389,13 +3389,13 @@
         <v>0.001325237585336988</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001358688626539661</v>
+        <v>0.00135868862653966</v>
       </c>
       <c r="BU8" t="n">
         <v>0.001043392762746281</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0009050305949668675</v>
+        <v>0.0009050305949668678</v>
       </c>
       <c r="BW8" t="n">
         <v>0.001239974648819916</v>
@@ -3404,19 +3404,19 @@
         <v>0.001222347340293859</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.001466803960294855</v>
+        <v>0.001466803960294854</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.001285088599691144</v>
+        <v>0.001285088599691145</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.001014875754617674</v>
+        <v>0.001014875754617675</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0006775268145180985</v>
+        <v>0.0006775268145180982</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0007305625668306809</v>
+        <v>0.0007305625668306808</v>
       </c>
       <c r="CD8" t="n">
         <v>0.001365941646129984</v>
@@ -3425,7 +3425,7 @@
         <v>0.001419685377689362</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001331394541248587</v>
+        <v>0.001331394541248586</v>
       </c>
       <c r="CG8" t="n">
         <v>0.001345221618198644</v>
@@ -3434,46 +3434,46 @@
         <v>0.0008715781793176729</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0009405393536939192</v>
+        <v>0.0009405393536939189</v>
       </c>
       <c r="CJ8" t="n">
         <v>0.001001939286291494</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0009912433791582327</v>
+        <v>0.000991243379158233</v>
       </c>
       <c r="CL8" t="n">
         <v>0.0008908031579456471</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0009626144010869094</v>
+        <v>0.0009626144010869097</v>
       </c>
       <c r="CN8" t="n">
         <v>0.000989348134262704</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0009638096057019049</v>
+        <v>0.0009638096057019052</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0009687324723434824</v>
+        <v>0.0009687324723434821</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0009862553767234531</v>
+        <v>0.0009862553767234527</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0009678571711242372</v>
+        <v>0.0009678571711242371</v>
       </c>
       <c r="CS8" t="n">
         <v>0.001009478631473034</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.001010037278210594</v>
+        <v>0.001010037278210593</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.001010547959439606</v>
+        <v>0.001010547959439607</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0009894549864831791</v>
+        <v>0.0009894549864831795</v>
       </c>
       <c r="CW8" t="n">
         <v>0.001010065872611721</v>
@@ -3488,7 +3488,7 @@
         <v>0.001015108596401458</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.001017168292726599</v>
+        <v>0.0010171682927266</v>
       </c>
       <c r="DB8" t="n">
         <v>0.001008120703187615</v>
@@ -3500,7 +3500,7 @@
         <v>0.001009477342821114</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.001044088546000763</v>
+        <v>0.001044088546000762</v>
       </c>
       <c r="DF8" t="n">
         <v>0.001038453548806432</v>
@@ -3530,7 +3530,7 @@
         <v>0.001029422743105408</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.00102804288837091</v>
+        <v>0.001028042888370911</v>
       </c>
       <c r="DP8" t="n">
         <v>0.001035915855783454</v>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0009912966176939756</v>
+        <v>0.0009912966176939752</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0006489175857724035</v>
+        <v>0.0006489175857724034</v>
       </c>
       <c r="D11" t="n">
         <v>0.000327222292195227</v>
@@ -4102,7 +4102,7 @@
         <v>0.000243091771624347</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0002957372933875101</v>
+        <v>0.00029573729338751</v>
       </c>
       <c r="Z11" t="n">
         <v>0.000202556971345861</v>
@@ -4147,7 +4147,7 @@
         <v>0.00017201608461714</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0005519127517746399</v>
+        <v>0.00055191275177464</v>
       </c>
       <c r="AO11" t="n">
         <v>0.00041286703670101</v>
@@ -4207,7 +4207,7 @@
         <v>0.000296554529732093</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.0002832708462032548</v>
+        <v>0.0002832708462032549</v>
       </c>
       <c r="BI11" t="n">
         <v>0.0002765797046986051</v>
@@ -4243,7 +4243,7 @@
         <v>5.274203781245028e-05</v>
       </c>
       <c r="BT11" t="n">
-        <v>3.163403837070558e-05</v>
+        <v>3.163403837070557e-05</v>
       </c>
       <c r="BU11" t="n">
         <v>3.100820393671812e-05</v>
@@ -4252,7 +4252,7 @@
         <v>2.93299501557466e-05</v>
       </c>
       <c r="BW11" t="n">
-        <v>3.673845428030232e-05</v>
+        <v>3.673845428030233e-05</v>
       </c>
       <c r="BX11" t="n">
         <v>3.837940773952861e-05</v>
@@ -4261,10 +4261,10 @@
         <v>2.509935299224408e-05</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.434507995979129e-05</v>
+        <v>4.43450799597913e-05</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.597125971510224e-05</v>
+        <v>3.597125971510223e-05</v>
       </c>
       <c r="CB11" t="n">
         <v>4.801763967226998e-05</v>
@@ -4279,7 +4279,7 @@
         <v>0.0003075831140984993</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0002445755096230516</v>
+        <v>0.0002445755096230517</v>
       </c>
       <c r="CG11" t="n">
         <v>0.0002247342422000881</v>
@@ -4303,10 +4303,10 @@
         <v>0.0001806190851719268</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.000194249638115042</v>
+        <v>0.0001942496381150419</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0001750876274400748</v>
+        <v>0.0001750876274400749</v>
       </c>
       <c r="CP11" t="n">
         <v>0.0001840859025243767</v>
@@ -4318,7 +4318,7 @@
         <v>0.0001775146214627122</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.00018522405674806</v>
+        <v>0.0001852240567480601</v>
       </c>
       <c r="CT11" t="n">
         <v>0.000186741529405653</v>
@@ -4336,7 +4336,7 @@
         <v>0.0001881403729622807</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.000184367600728129</v>
+        <v>0.0001843676007281289</v>
       </c>
       <c r="CZ11" t="n">
         <v>0.0001888435356159083</v>
@@ -4357,13 +4357,13 @@
         <v>0.0001926601406096279</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.0001925697813380631</v>
+        <v>0.0001925697813380632</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0001894766413084311</v>
+        <v>0.0001894766413084312</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.0001957369687754576</v>
+        <v>0.0001957369687754577</v>
       </c>
       <c r="DI11" t="n">
         <v>0.0002004545837970643</v>
@@ -4375,13 +4375,13 @@
         <v>0.0001873207168673976</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0001930729633811145</v>
+        <v>0.0001930729633811144</v>
       </c>
       <c r="DM11" t="n">
         <v>0.0001886765923203643</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0001921633042450239</v>
+        <v>0.0001921633042450238</v>
       </c>
       <c r="DO11" t="n">
         <v>0.0001898182555562287</v>
@@ -4397,133 +4397,133 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.641755796595917e-05</v>
+        <v>5.641755796595914e-05</v>
       </c>
       <c r="C12" t="n">
-        <v>6.099841607543444e-05</v>
+        <v>6.099841607543441e-05</v>
       </c>
       <c r="D12" t="n">
-        <v>6.591100920985533e-05</v>
+        <v>6.591100920985532e-05</v>
       </c>
       <c r="E12" t="n">
         <v>0.0001217842236043435</v>
       </c>
       <c r="F12" t="n">
-        <v>4.702804620304099e-05</v>
+        <v>4.702804620304102e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>6.267239897635701e-05</v>
+        <v>6.2672398976357e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>5.423355403242101e-05</v>
+        <v>5.423355403242103e-05</v>
       </c>
       <c r="I12" t="n">
-        <v>5.4126547565832e-05</v>
+        <v>5.412654756583202e-05</v>
       </c>
       <c r="J12" t="n">
         <v>5.9706825725492e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>5.489949164330601e-05</v>
+        <v>5.489949164330599e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>5.932642877221302e-05</v>
+        <v>5.9326428772213e-05</v>
       </c>
       <c r="M12" t="n">
         <v>7.307995132909099e-05</v>
       </c>
       <c r="N12" t="n">
-        <v>7.627272152385499e-05</v>
+        <v>7.627272152385504e-05</v>
       </c>
       <c r="O12" t="n">
         <v>7.535358593703497e-05</v>
       </c>
       <c r="P12" t="n">
-        <v>7.952773957951295e-05</v>
+        <v>7.952773957951301e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.206631544844699e-05</v>
+        <v>4.206631544844701e-05</v>
       </c>
       <c r="R12" t="n">
         <v>8.285085269981502e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>8.585308601595e-05</v>
+        <v>8.585308601595001e-05</v>
       </c>
       <c r="T12" t="n">
-        <v>7.301924023777101e-05</v>
+        <v>7.301924023777096e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>9.489105559325198e-05</v>
+        <v>9.4891055593252e-05</v>
       </c>
       <c r="V12" t="n">
-        <v>8.372940859978299e-05</v>
+        <v>8.372940859978294e-05</v>
       </c>
       <c r="W12" t="n">
-        <v>6.999202738920301e-05</v>
+        <v>6.999202738920304e-05</v>
       </c>
       <c r="X12" t="n">
         <v>4.3489741814887e-05</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.119281883165802e-05</v>
+        <v>5.1192818831658e-05</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.396550077436499e-05</v>
+        <v>4.396550077436501e-05</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.1741558764523e-05</v>
+        <v>7.174155876452299e-05</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.385525491902499e-05</v>
+        <v>4.3855254919025e-05</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.168979976017901e-05</v>
+        <v>7.168979976017899e-05</v>
       </c>
       <c r="AD12" t="n">
-        <v>6.596195673841102e-05</v>
+        <v>6.596195673841098e-05</v>
       </c>
       <c r="AE12" t="n">
-        <v>6.899498619751201e-05</v>
+        <v>6.899498619751198e-05</v>
       </c>
       <c r="AF12" t="n">
-        <v>6.030654040334997e-05</v>
+        <v>6.030654040334999e-05</v>
       </c>
       <c r="AG12" t="n">
-        <v>8.332788092700899e-05</v>
+        <v>8.332788092700896e-05</v>
       </c>
       <c r="AH12" t="n">
-        <v>7.621242931865002e-05</v>
+        <v>7.621242931864997e-05</v>
       </c>
       <c r="AI12" t="n">
-        <v>8.1598036057091e-05</v>
+        <v>8.159803605709099e-05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.552391314210603e-05</v>
+        <v>4.552391314210601e-05</v>
       </c>
       <c r="AK12" t="n">
-        <v>6.649284948718601e-05</v>
+        <v>6.649284948718602e-05</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.991915880708101e-05</v>
+        <v>4.991915880708104e-05</v>
       </c>
       <c r="AM12" t="n">
-        <v>5.7835372793224e-05</v>
+        <v>5.783537279322402e-05</v>
       </c>
       <c r="AN12" t="n">
-        <v>8.138702462211699e-05</v>
+        <v>8.138702462211701e-05</v>
       </c>
       <c r="AO12" t="n">
-        <v>7.559166559743299e-05</v>
+        <v>7.559166559743297e-05</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.016834406589399e-05</v>
+        <v>8.0168344065894e-05</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.250558847080095e-05</v>
+        <v>6.250558847080096e-05</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.214093843198101e-05</v>
+        <v>5.214093843198098e-05</v>
       </c>
       <c r="AS12" t="n">
         <v>3.6124792705033e-05</v>
@@ -4535,13 +4535,13 @@
         <v>4.5145592713797e-05</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.797876666666669e-05</v>
+        <v>7.797876666666671e-05</v>
       </c>
       <c r="AW12" t="n">
         <v>0.0001020170164083773</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0001432473729292475</v>
+        <v>0.0001432473729292474</v>
       </c>
       <c r="AY12" t="n">
         <v>0.0001007803267982353</v>
@@ -4550,28 +4550,28 @@
         <v>0.0001088539088222298</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0001731978164102897</v>
+        <v>0.0001731978164102896</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0001472291493376383</v>
+        <v>0.0001472291493376382</v>
       </c>
       <c r="BC12" t="n">
         <v>0.0002364314851198428</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0001192015273042979</v>
+        <v>0.0001192015273042978</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.485516322868907e-05</v>
+        <v>8.485516322868904e-05</v>
       </c>
       <c r="BF12" t="n">
         <v>8.04906032079881e-05</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.615315778171082e-05</v>
+        <v>9.615315778171085e-05</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0001043961775919132</v>
+        <v>0.0001043961775919133</v>
       </c>
       <c r="BI12" t="n">
         <v>0.0001510864194647791</v>
@@ -4604,16 +4604,16 @@
         <v>0.00012337523611727</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.0001208878676820726</v>
+        <v>0.0001208878676820725</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.0001516138959986469</v>
+        <v>0.000151613895998647</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0001545350947195124</v>
+        <v>0.0001545350947195125</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0001284854737524962</v>
+        <v>0.0001284854737524963</v>
       </c>
       <c r="BW12" t="n">
         <v>0.0001324480827664938</v>
@@ -4628,13 +4628,13 @@
         <v>0.0001988491257506812</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0001719012980263556</v>
+        <v>0.0001719012980263557</v>
       </c>
       <c r="CB12" t="n">
         <v>0.0001910584577852782</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.0001924804796990976</v>
+        <v>0.0001924804796990977</v>
       </c>
       <c r="CD12" t="n">
         <v>7.943019875442934e-05</v>
@@ -4646,13 +4646,13 @@
         <v>0.0001352218832981502</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0001442194152377239</v>
+        <v>0.0001442194152377238</v>
       </c>
       <c r="CH12" t="n">
-        <v>9.78640584452453e-05</v>
+        <v>9.786405844524528e-05</v>
       </c>
       <c r="CI12" t="n">
-        <v>9.543663114407575e-05</v>
+        <v>9.543663114407576e-05</v>
       </c>
       <c r="CJ12" t="n">
         <v>8.100626714859634e-05</v>
@@ -4667,22 +4667,22 @@
         <v>2.767378574177015e-05</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.714407325699149e-05</v>
+        <v>2.714407325699148e-05</v>
       </c>
       <c r="CO12" t="n">
-        <v>2.845095863042478e-05</v>
+        <v>2.845095863042477e-05</v>
       </c>
       <c r="CP12" t="n">
         <v>3.172925592950623e-05</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.843204588492657e-05</v>
+        <v>2.843204588492658e-05</v>
       </c>
       <c r="CR12" t="n">
-        <v>3.040189830147518e-05</v>
+        <v>3.040189830147517e-05</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.712484246808702e-05</v>
+        <v>2.712484246808701e-05</v>
       </c>
       <c r="CT12" t="n">
         <v>2.675626456569084e-05</v>
@@ -4691,7 +4691,7 @@
         <v>2.644153860647998e-05</v>
       </c>
       <c r="CV12" t="n">
-        <v>3.000275248729798e-05</v>
+        <v>3.000275248729797e-05</v>
       </c>
       <c r="CW12" t="n">
         <v>2.656426865358238e-05</v>
@@ -4715,13 +4715,13 @@
         <v>2.631788898893959e-05</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.840264586824747e-05</v>
+        <v>2.840264586824746e-05</v>
       </c>
       <c r="DE12" t="n">
         <v>2.725424870757479e-05</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.735886841104184e-05</v>
+        <v>2.735886841104183e-05</v>
       </c>
       <c r="DG12" t="n">
         <v>2.610848380737249e-05</v>
@@ -4730,10 +4730,10 @@
         <v>2.56412871942277e-05</v>
       </c>
       <c r="DI12" t="n">
-        <v>2.525939137873163e-05</v>
+        <v>2.525939137873165e-05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.535797146999705e-05</v>
+        <v>2.535797146999704e-05</v>
       </c>
       <c r="DK12" t="n">
         <v>2.765254640766942e-05</v>
@@ -4742,7 +4742,7 @@
         <v>2.606481708359441e-05</v>
       </c>
       <c r="DM12" t="n">
-        <v>2.791500541266006e-05</v>
+        <v>2.791500541266007e-05</v>
       </c>
       <c r="DN12" t="n">
         <v>2.619216568561142e-05</v>
@@ -5020,16 +5020,16 @@
         <v>2.203826840502582e-05</v>
       </c>
       <c r="C14" t="n">
-        <v>2.865075060407798e-05</v>
+        <v>2.865075060407797e-05</v>
       </c>
       <c r="D14" t="n">
-        <v>4.252440093195754e-05</v>
+        <v>4.252440093195753e-05</v>
       </c>
       <c r="E14" t="n">
         <v>2.458813693692158e-05</v>
       </c>
       <c r="F14" t="n">
-        <v>2.278488857891e-05</v>
+        <v>2.278488857891001e-05</v>
       </c>
       <c r="G14" t="n">
         <v>2.444534715658e-05</v>
@@ -5041,7 +5041,7 @@
         <v>2.099970491851e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2147184484e-05</v>
+        <v>2.214718448400001e-05</v>
       </c>
       <c r="K14" t="n">
         <v>2.178151744891e-05</v>
@@ -5065,7 +5065,7 @@
         <v>2.081565595782e-05</v>
       </c>
       <c r="R14" t="n">
-        <v>2.727377272881e-05</v>
+        <v>2.727377272881001e-05</v>
       </c>
       <c r="S14" t="n">
         <v>3.137902905255e-05</v>
@@ -5080,7 +5080,7 @@
         <v>4.473527313877e-05</v>
       </c>
       <c r="W14" t="n">
-        <v>3.799569493278e-05</v>
+        <v>3.799569493278001e-05</v>
       </c>
       <c r="X14" t="n">
         <v>2.3852151204874e-05</v>
@@ -5098,7 +5098,7 @@
         <v>2.109781657208e-05</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.846595181169e-05</v>
+        <v>2.846595181168999e-05</v>
       </c>
       <c r="AD14" t="n">
         <v>4.275750747808e-05</v>
@@ -5107,10 +5107,10 @@
         <v>4.731786097944e-05</v>
       </c>
       <c r="AF14" t="n">
-        <v>4.297465657065001e-05</v>
+        <v>4.297465657065e-05</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.299725525757e-05</v>
+        <v>3.299725525757001e-05</v>
       </c>
       <c r="AH14" t="n">
         <v>3.074978785218001e-05</v>
@@ -5122,7 +5122,7 @@
         <v>2.515929681544e-05</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.325092764549001e-05</v>
+        <v>3.325092764548999e-05</v>
       </c>
       <c r="AL14" t="n">
         <v>2.710968364161e-05</v>
@@ -5131,13 +5131,13 @@
         <v>3.560846985678e-05</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.597518816554e-05</v>
+        <v>3.597518816554001e-05</v>
       </c>
       <c r="AO14" t="n">
         <v>3.241788296144e-05</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.983462051458001e-05</v>
+        <v>2.983462051458e-05</v>
       </c>
       <c r="AQ14" t="n">
         <v>3.571347705561e-05</v>
@@ -5155,16 +5155,16 @@
         <v>2.143427051508e-05</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.714166666666665e-05</v>
+        <v>7.714166666666667e-05</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.172790139976217e-05</v>
+        <v>3.172790139976218e-05</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.802500242506151e-05</v>
+        <v>3.80250024250615e-05</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.510689864461558e-05</v>
+        <v>3.510689864461559e-05</v>
       </c>
       <c r="AZ14" t="n">
         <v>3.740574487800726e-05</v>
@@ -5176,16 +5176,16 @@
         <v>8.126010945293718e-05</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0001471686852333628</v>
+        <v>0.0001471686852333627</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.680362340021648e-05</v>
+        <v>6.680362340021646e-05</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.881637728487493e-05</v>
+        <v>5.881637728487495e-05</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.67871597862308e-05</v>
+        <v>5.678715978623079e-05</v>
       </c>
       <c r="BG14" t="n">
         <v>6.734328600554907e-05</v>
@@ -5200,10 +5200,10 @@
         <v>0.0001034628759739289</v>
       </c>
       <c r="BK14" t="n">
-        <v>9.153488074513452e-05</v>
+        <v>9.153488074513451e-05</v>
       </c>
       <c r="BL14" t="n">
-        <v>7.847773906469612e-05</v>
+        <v>7.847773906469611e-05</v>
       </c>
       <c r="BM14" t="n">
         <v>0.000125393364241531</v>
@@ -5224,13 +5224,13 @@
         <v>7.115565376222185e-05</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.552688730680397e-05</v>
+        <v>8.552688730680395e-05</v>
       </c>
       <c r="BT14" t="n">
         <v>0.0001043524936227718</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.999438828429678e-05</v>
+        <v>3.999438828429679e-05</v>
       </c>
       <c r="BV14" t="n">
         <v>3.840243220541667e-05</v>
@@ -5239,28 +5239,28 @@
         <v>9.155687496592259e-05</v>
       </c>
       <c r="BX14" t="n">
-        <v>8.284786674625626e-05</v>
+        <v>8.284786674625627e-05</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.744477117491422e-05</v>
+        <v>9.744477117491421e-05</v>
       </c>
       <c r="BZ14" t="n">
-        <v>8.106118729614012e-05</v>
+        <v>8.106118729614013e-05</v>
       </c>
       <c r="CA14" t="n">
         <v>9.182252970823659e-05</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.380092889672296e-05</v>
+        <v>3.380092889672297e-05</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.719106504600213e-05</v>
+        <v>4.719106504600212e-05</v>
       </c>
       <c r="CD14" t="n">
-        <v>7.839612498854157e-05</v>
+        <v>7.839612498854154e-05</v>
       </c>
       <c r="CE14" t="n">
-        <v>8.63779996644289e-05</v>
+        <v>8.637799966442892e-05</v>
       </c>
       <c r="CF14" t="n">
         <v>0.0001050392014614921</v>
@@ -5272,7 +5272,7 @@
         <v>7.969750496154864e-05</v>
       </c>
       <c r="CI14" t="n">
-        <v>8.200493387474037e-05</v>
+        <v>8.200493387474038e-05</v>
       </c>
       <c r="CJ14" t="n">
         <v>6.958582685182912e-05</v>
@@ -5281,7 +5281,7 @@
         <v>5.612901330316652e-05</v>
       </c>
       <c r="CL14" t="n">
-        <v>4.510434022820878e-05</v>
+        <v>4.510434022820877e-05</v>
       </c>
       <c r="CM14" t="n">
         <v>1.618715316717387e-05</v>
@@ -5296,7 +5296,7 @@
         <v>1.700031706298369e-05</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.728403986352239e-05</v>
+        <v>1.728403986352238e-05</v>
       </c>
       <c r="CR14" t="n">
         <v>1.675382623948599e-05</v>
@@ -5317,13 +5317,13 @@
         <v>1.62970336364011e-05</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.647227631183039e-05</v>
+        <v>1.64722763118304e-05</v>
       </c>
       <c r="CY14" t="n">
         <v>1.692287471579168e-05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>1.681295740498247e-05</v>
+        <v>1.681295740498248e-05</v>
       </c>
       <c r="DA14" t="n">
         <v>1.632590918416772e-05</v>
@@ -5387,7 +5387,7 @@
         <v>3.34268818473815e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>5.807888297756072e-06</v>
+        <v>5.80788829775607e-06</v>
       </c>
       <c r="E15" t="n">
         <v>3.461048402747386e-06</v>
@@ -5465,10 +5465,10 @@
         <v>3.38624320081e-06</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.62740368723e-06</v>
+        <v>6.627403687230001e-06</v>
       </c>
       <c r="AE15" t="n">
-        <v>7.222510184439999e-06</v>
+        <v>7.22251018444e-06</v>
       </c>
       <c r="AF15" t="n">
         <v>6.41055337035e-06</v>
@@ -5477,7 +5477,7 @@
         <v>3.8472091707e-06</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.714540045509999e-06</v>
+        <v>3.71454004551e-06</v>
       </c>
       <c r="AI15" t="n">
         <v>3.91440593449e-06</v>
@@ -5594,7 +5594,7 @@
         <v>1.905172435426421e-05</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.689453479463197e-06</v>
+        <v>3.689453479463196e-06</v>
       </c>
       <c r="BV15" t="n">
         <v>3.443323994629313e-06</v>
@@ -5609,13 +5609,13 @@
         <v>2.456021686387671e-05</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.743608346712432e-05</v>
+        <v>1.743608346712431e-05</v>
       </c>
       <c r="CA15" t="n">
         <v>2.628793162378641e-05</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.112354255541288e-06</v>
+        <v>6.112354255541289e-06</v>
       </c>
       <c r="CC15" t="n">
         <v>1.163916683883568e-05</v>
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8.98373618775846e-06</v>
+        <v>8.983736187758461e-06</v>
       </c>
       <c r="C16" t="n">
         <v>1.066845232631186e-05</v>
@@ -5763,7 +5763,7 @@
         <v>5.334587579156e-06</v>
       </c>
       <c r="H16" t="n">
-        <v>4.554073643868e-06</v>
+        <v>4.554073643868001e-06</v>
       </c>
       <c r="I16" t="n">
         <v>4.834294532181e-06</v>
@@ -5775,16 +5775,16 @@
         <v>5.413391604862e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>5.555361529091e-06</v>
+        <v>5.555361529090999e-06</v>
       </c>
       <c r="M16" t="n">
         <v>7.207708676172e-06</v>
       </c>
       <c r="N16" t="n">
-        <v>6.843758082547e-06</v>
+        <v>6.843758082546999e-06</v>
       </c>
       <c r="O16" t="n">
-        <v>6.706251249616e-06</v>
+        <v>6.706251249616001e-06</v>
       </c>
       <c r="P16" t="n">
         <v>7.653108476105e-06</v>
@@ -5805,10 +5805,10 @@
         <v>7.41629331366e-06</v>
       </c>
       <c r="V16" t="n">
-        <v>8.117239560960001e-06</v>
+        <v>8.117239560960003e-06</v>
       </c>
       <c r="W16" t="n">
-        <v>8.493408021970001e-06</v>
+        <v>8.493408021970003e-06</v>
       </c>
       <c r="X16" t="n">
         <v>5.033038304806e-06</v>
@@ -5823,22 +5823,22 @@
         <v>5.492667702989e-06</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.279294405907e-06</v>
+        <v>3.279294405906999e-06</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.760013007872e-06</v>
+        <v>5.760013007871999e-06</v>
       </c>
       <c r="AD16" t="n">
         <v>5.418940592998e-06</v>
       </c>
       <c r="AE16" t="n">
-        <v>6.392914599925e-06</v>
+        <v>6.392914599925001e-06</v>
       </c>
       <c r="AF16" t="n">
         <v>5.777171024117e-06</v>
       </c>
       <c r="AG16" t="n">
-        <v>6.754386086716e-06</v>
+        <v>6.754386086716001e-06</v>
       </c>
       <c r="AH16" t="n">
         <v>5.841736078659e-06</v>
@@ -5877,16 +5877,16 @@
         <v>3.50029353568e-06</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.709310082532e-06</v>
+        <v>3.709310082532001e-06</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.932731292477001e-06</v>
+        <v>2.932731292477e-06</v>
       </c>
       <c r="AV16" t="n">
         <v>1.001633333333333e-05</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.783209271849078e-05</v>
+        <v>1.783209271849079e-05</v>
       </c>
       <c r="AX16" t="n">
         <v>1.985977067833698e-05</v>
@@ -5940,7 +5940,7 @@
         <v>3.727110726715377e-05</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.060248926202258e-05</v>
+        <v>4.060248926202259e-05</v>
       </c>
       <c r="BP16" t="n">
         <v>3.913763130056459e-05</v>
@@ -5952,7 +5952,7 @@
         <v>7.633412586947858e-05</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.55369176959807e-05</v>
+        <v>1.553691769598071e-05</v>
       </c>
       <c r="BT16" t="n">
         <v>1.681231309642777e-05</v>
@@ -5967,7 +5967,7 @@
         <v>1.542521549674385e-05</v>
       </c>
       <c r="BX16" t="n">
-        <v>1.675241014047566e-05</v>
+        <v>1.675241014047567e-05</v>
       </c>
       <c r="BY16" t="n">
         <v>1.88581357747881e-05</v>
@@ -5991,7 +5991,7 @@
         <v>6.386529750259199e-06</v>
       </c>
       <c r="CF16" t="n">
-        <v>8.307219587664548e-06</v>
+        <v>8.30721958766455e-06</v>
       </c>
       <c r="CG16" t="n">
         <v>8.869618556827889e-06</v>
@@ -6157,16 +6157,16 @@
         <v>8.539367603695001e-06</v>
       </c>
       <c r="R17" t="n">
-        <v>9.765889307766e-06</v>
+        <v>9.765889307765998e-06</v>
       </c>
       <c r="S17" t="n">
         <v>1.2463461850079e-05</v>
       </c>
       <c r="T17" t="n">
-        <v>5.211384304165e-06</v>
+        <v>5.211384304165001e-06</v>
       </c>
       <c r="U17" t="n">
-        <v>6.457636283463e-06</v>
+        <v>6.457636283463001e-06</v>
       </c>
       <c r="V17" t="n">
         <v>5.938050662553001e-06</v>
@@ -6181,13 +6181,13 @@
         <v>3.090906052723e-06</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.476635252288e-06</v>
+        <v>9.476635252287998e-06</v>
       </c>
       <c r="AA17" t="n">
         <v>1.5543950564681e-05</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.815085472492e-06</v>
+        <v>8.815085472492002e-06</v>
       </c>
       <c r="AC17" t="n">
         <v>1.5870501568267e-05</v>
@@ -6223,7 +6223,7 @@
         <v>3.578206881358e-06</v>
       </c>
       <c r="AN17" t="n">
-        <v>8.741038350135001e-06</v>
+        <v>8.741038350135e-06</v>
       </c>
       <c r="AO17" t="n">
         <v>1.0548193293998e-05</v>
@@ -6232,7 +6232,7 @@
         <v>1.1896394557812e-05</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.105151366065e-06</v>
+        <v>4.105151366065001e-06</v>
       </c>
       <c r="AR17" t="n">
         <v>2.906933203379e-06</v>
@@ -6241,7 +6241,7 @@
         <v>8.143340971875e-06</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.76064550608e-06</v>
+        <v>9.760645506080001e-06</v>
       </c>
       <c r="AU17" t="n">
         <v>7.194644669889e-06</v>
@@ -6259,7 +6259,7 @@
         <v>1.145603263742012e-06</v>
       </c>
       <c r="AZ17" t="n">
-        <v>9.848869503534065e-07</v>
+        <v>9.848869503534067e-07</v>
       </c>
       <c r="BA17" t="n">
         <v>1.777519872532608e-06</v>
@@ -6331,7 +6331,7 @@
         <v>3.778894176022329e-06</v>
       </c>
       <c r="BX17" t="n">
-        <v>4.33253197768524e-06</v>
+        <v>4.332531977685239e-06</v>
       </c>
       <c r="BY17" t="n">
         <v>2.445375957263081e-06</v>
@@ -6826,7 +6826,7 @@
         <v>1.829319169115066e-06</v>
       </c>
       <c r="E19" t="n">
-        <v>3.373118530498713e-06</v>
+        <v>3.373118530498712e-06</v>
       </c>
       <c r="F19" t="n">
         <v>9.4919015806e-07</v>
@@ -7014,19 +7014,19 @@
         <v>7.960947118897376e-07</v>
       </c>
       <c r="BS19" t="n">
-        <v>5.409041666655154e-07</v>
+        <v>5.409041666655153e-07</v>
       </c>
       <c r="BT19" t="n">
         <v>8.267832899585634e-07</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.219628981270449e-06</v>
+        <v>3.219628981270448e-06</v>
       </c>
       <c r="BV19" t="n">
         <v>2.898255296274663e-06</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.359230188662179e-07</v>
+        <v>7.359230188662178e-07</v>
       </c>
       <c r="BX19" t="n">
         <v>8.938319697520726e-07</v>
@@ -7041,7 +7041,7 @@
         <v>1.485713491430138e-06</v>
       </c>
       <c r="CB19" t="n">
-        <v>7.095975985111592e-06</v>
+        <v>7.095975985111593e-06</v>
       </c>
       <c r="CC19" t="n">
         <v>4.017049225599283e-06</v>
@@ -7080,19 +7080,19 @@
         <v>4.522614125631117e-07</v>
       </c>
       <c r="CO19" t="n">
-        <v>4.273089881653806e-07</v>
+        <v>4.273089881653805e-07</v>
       </c>
       <c r="CP19" t="n">
         <v>4.724292814914771e-07</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.209803842788905e-07</v>
+        <v>4.209803842788906e-07</v>
       </c>
       <c r="CR19" t="n">
         <v>4.480843651552326e-07</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.852244531976702e-07</v>
+        <v>3.852244531976701e-07</v>
       </c>
       <c r="CT19" t="n">
         <v>4.620965691672564e-07</v>
@@ -7128,7 +7128,7 @@
         <v>1.164212462133901e-06</v>
       </c>
       <c r="DE19" t="n">
-        <v>6.996340624199466e-07</v>
+        <v>6.996340624199465e-07</v>
       </c>
       <c r="DF19" t="n">
         <v>4.062526345196793e-07</v>
@@ -7140,7 +7140,7 @@
         <v>3.648419381464357e-07</v>
       </c>
       <c r="DI19" t="n">
-        <v>4.530512456461531e-07</v>
+        <v>4.530512456461532e-07</v>
       </c>
       <c r="DJ19" t="n">
         <v>3.852717517093218e-07</v>
@@ -7158,7 +7158,7 @@
         <v>6.037051278079529e-07</v>
       </c>
       <c r="DO19" t="n">
-        <v>3.86781411300971e-07</v>
+        <v>3.867814113009709e-07</v>
       </c>
       <c r="DP19" t="n">
         <v>3.936692857429302e-07</v>
@@ -7177,7 +7177,7 @@
         <v>9.059398984731089e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>8.023532676242606e-05</v>
+        <v>8.023532676242607e-05</v>
       </c>
       <c r="E20" t="n">
         <v>6.143770637919307e-05</v>
@@ -7207,7 +7207,7 @@
         <v>5.560174744803e-05</v>
       </c>
       <c r="N20" t="n">
-        <v>5.430685890777001e-05</v>
+        <v>5.430685890777e-05</v>
       </c>
       <c r="O20" t="n">
         <v>5.351228424232e-05</v>
@@ -7228,7 +7228,7 @@
         <v>4.401966630052e-05</v>
       </c>
       <c r="U20" t="n">
-        <v>4.488265647335e-05</v>
+        <v>4.488265647335001e-05</v>
       </c>
       <c r="V20" t="n">
         <v>4.816608973623e-05</v>
@@ -7258,7 +7258,7 @@
         <v>2.2963068608487e-05</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.146972561451e-05</v>
+        <v>3.146972561451001e-05</v>
       </c>
       <c r="AF20" t="n">
         <v>2.570270286875e-05</v>
@@ -7315,7 +7315,7 @@
         <v>0.0001480520299783544</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.680731558723901e-05</v>
+        <v>8.680731558723902e-05</v>
       </c>
       <c r="AY20" t="n">
         <v>0.0001939325467153005</v>
@@ -7378,7 +7378,7 @@
         <v>3.027692389272666e-05</v>
       </c>
       <c r="BS20" t="n">
-        <v>9.665221769627593e-05</v>
+        <v>9.665221769627592e-05</v>
       </c>
       <c r="BT20" t="n">
         <v>0.0001170368246259861</v>
@@ -7387,7 +7387,7 @@
         <v>0.0001009617147712498</v>
       </c>
       <c r="BV20" t="n">
-        <v>7.468015911781429e-05</v>
+        <v>7.468015911781427e-05</v>
       </c>
       <c r="BW20" t="n">
         <v>7.149108156104364e-05</v>
@@ -8022,13 +8022,13 @@
         <v>0.0003391161071029701</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0003641652263605138</v>
+        <v>0.0003641652263605139</v>
       </c>
       <c r="F23" t="n">
         <v>0.000230424621062976</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000247830266770496</v>
+        <v>0.0002478302667704959</v>
       </c>
       <c r="H23" t="n">
         <v>0.00020787930207662</v>
@@ -8037,7 +8037,7 @@
         <v>0.000194493425280166</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0001647535216536201</v>
+        <v>0.00016475352165362</v>
       </c>
       <c r="K23" t="n">
         <v>0.000185381544645871</v>
@@ -8046,7 +8046,7 @@
         <v>0.000160529967346987</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0003161348123276611</v>
+        <v>0.000316134812327661</v>
       </c>
       <c r="N23" t="n">
         <v>0.00032821944206928</v>
@@ -8061,7 +8061,7 @@
         <v>0.000182177389886671</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0005500204697614171</v>
+        <v>0.000550020469761417</v>
       </c>
       <c r="S23" t="n">
         <v>0.000447085185179899</v>
@@ -8082,19 +8082,19 @@
         <v>0.000246537542089732</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.0002954333852870631</v>
+        <v>0.0002954333852870629</v>
       </c>
       <c r="Z23" t="n">
         <v>0.000212120710794537</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.000317874080746215</v>
+        <v>0.0003178740807462151</v>
       </c>
       <c r="AB23" t="n">
         <v>0.000154706249773661</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.000255005321983555</v>
+        <v>0.0002550053219835551</v>
       </c>
       <c r="AD23" t="n">
         <v>0.000186335899768822</v>
@@ -8121,19 +8121,19 @@
         <v>0.000216004150208319</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.0003079526746306689</v>
+        <v>0.000307952674630669</v>
       </c>
       <c r="AM23" t="n">
         <v>0.000171258717030985</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.0005649980348151131</v>
+        <v>0.000564998034815113</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.0004199810356886431</v>
+        <v>0.0004199810356886429</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.0004816518594911269</v>
+        <v>0.000481651859491127</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.00016327550200293</v>
@@ -8148,7 +8148,7 @@
         <v>0.000117126269562505</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.000331702296992018</v>
+        <v>0.0003317022969920181</v>
       </c>
       <c r="AV23" t="n">
         <v>0.0004933461666666667</v>
@@ -8157,7 +8157,7 @@
         <v>4.869050005014866e-05</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.246978427922783e-05</v>
+        <v>5.246978427922782e-05</v>
       </c>
       <c r="AY23" t="n">
         <v>0.0001083613256860283</v>
@@ -8169,28 +8169,28 @@
         <v>0.0005760074691448202</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.000415960962413723</v>
+        <v>0.0004159609624137231</v>
       </c>
       <c r="BC23" t="n">
-        <v>0.0006626988762114163</v>
+        <v>0.0006626988762114164</v>
       </c>
       <c r="BD23" t="n">
         <v>0.0003338121150566797</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.0003090901511531718</v>
+        <v>0.0003090901511531719</v>
       </c>
       <c r="BF23" t="n">
-        <v>0.00029954387749905</v>
+        <v>0.0002995438774990501</v>
       </c>
       <c r="BG23" t="n">
-        <v>0.0003274334497234606</v>
+        <v>0.0003274334497234605</v>
       </c>
       <c r="BH23" t="n">
         <v>0.0003169689169855</v>
       </c>
       <c r="BI23" t="n">
-        <v>0.0003264617926132513</v>
+        <v>0.0003264617926132514</v>
       </c>
       <c r="BJ23" t="n">
         <v>0.0002230945097577382</v>
@@ -8205,10 +8205,10 @@
         <v>0.0003386012913761208</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.000335170017905181</v>
+        <v>0.0003351700179051811</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.0003212751597537197</v>
+        <v>0.0003212751597537196</v>
       </c>
       <c r="BP23" t="n">
         <v>0.0003484597734116739</v>
@@ -8220,34 +8220,34 @@
         <v>0.0003791757049397874</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.082248280696802e-05</v>
+        <v>8.0822482806968e-05</v>
       </c>
       <c r="BT23" t="n">
-        <v>6.374019454646459e-05</v>
+        <v>6.374019454646457e-05</v>
       </c>
       <c r="BU23" t="n">
-        <v>5.765261136181501e-05</v>
+        <v>5.7652611361815e-05</v>
       </c>
       <c r="BV23" t="n">
-        <v>5.473294454966051e-05</v>
+        <v>5.47329445496605e-05</v>
       </c>
       <c r="BW23" t="n">
         <v>6.626709741757704e-05</v>
       </c>
       <c r="BX23" t="n">
-        <v>6.548925849639757e-05</v>
+        <v>6.548925849639756e-05</v>
       </c>
       <c r="BY23" t="n">
         <v>4.755022936279851e-05</v>
       </c>
       <c r="BZ23" t="n">
-        <v>6.677200924643892e-05</v>
+        <v>6.677200924643893e-05</v>
       </c>
       <c r="CA23" t="n">
         <v>6.784134826347187e-05</v>
       </c>
       <c r="CB23" t="n">
-        <v>4.447840439255906e-05</v>
+        <v>4.447840439255905e-05</v>
       </c>
       <c r="CC23" t="n">
         <v>4.231031597907948e-05</v>
@@ -8259,10 +8259,10 @@
         <v>0.0003463165772779967</v>
       </c>
       <c r="CF23" t="n">
-        <v>0.0003047627129898815</v>
+        <v>0.0003047627129898814</v>
       </c>
       <c r="CG23" t="n">
-        <v>0.0002874233779499023</v>
+        <v>0.0002874233779499024</v>
       </c>
       <c r="CH23" t="n">
         <v>0.0001666499839013095</v>
@@ -8271,7 +8271,7 @@
         <v>0.000166332389313785</v>
       </c>
       <c r="CJ23" t="n">
-        <v>0.0001712461393798544</v>
+        <v>0.0001712461393798545</v>
       </c>
       <c r="CK23" t="n">
         <v>0.0001792934384884859</v>
@@ -8289,16 +8289,16 @@
         <v>0.000182270130230995</v>
       </c>
       <c r="CP23" t="n">
-        <v>0.0001913875342668877</v>
+        <v>0.0001913875342668878</v>
       </c>
       <c r="CQ23" t="n">
-        <v>0.0001899144670785241</v>
+        <v>0.000189914467078524</v>
       </c>
       <c r="CR23" t="n">
         <v>0.0001851638601521489</v>
       </c>
       <c r="CS23" t="n">
-        <v>0.0001920917655108689</v>
+        <v>0.0001920917655108688</v>
       </c>
       <c r="CT23" t="n">
         <v>0.0001939683089704209</v>
@@ -8319,7 +8319,7 @@
         <v>0.0001916270895070747</v>
       </c>
       <c r="CZ23" t="n">
-        <v>0.0001961717710081791</v>
+        <v>0.000196171771008179</v>
       </c>
       <c r="DA23" t="n">
         <v>0.0001916267993793342</v>
@@ -8352,19 +8352,19 @@
         <v>0.0002009907694992277</v>
       </c>
       <c r="DK23" t="n">
-        <v>0.0001943060470249355</v>
+        <v>0.0001943060470249356</v>
       </c>
       <c r="DL23" t="n">
         <v>0.0002002114892733328</v>
       </c>
       <c r="DM23" t="n">
-        <v>0.0001951968494241513</v>
+        <v>0.0001951968494241512</v>
       </c>
       <c r="DN23" t="n">
         <v>0.0001991735922002039</v>
       </c>
       <c r="DO23" t="n">
-        <v>0.0001967459237552531</v>
+        <v>0.000196745923755253</v>
       </c>
       <c r="DP23" t="n">
         <v>0.000198566327204517</v>
@@ -9633,7 +9633,7 @@
         <v>8.6960729991e-08</v>
       </c>
       <c r="N28" t="n">
-        <v>8.654681813399999e-08</v>
+        <v>8.654681813400001e-08</v>
       </c>
       <c r="O28" t="n">
         <v>8.591378756000001e-08</v>
@@ -9666,7 +9666,7 @@
         <v>5.9245805447e-08</v>
       </c>
       <c r="Y28" t="n">
-        <v>7.183074551600002e-08</v>
+        <v>7.183074551600001e-08</v>
       </c>
       <c r="Z28" t="n">
         <v>4.1716594375e-08</v>
@@ -9741,7 +9741,7 @@
         <v>1.897821657035007e-07</v>
       </c>
       <c r="AX28" t="n">
-        <v>2.033619763837396e-07</v>
+        <v>2.033619763837395e-07</v>
       </c>
       <c r="AY28" t="n">
         <v>2.02156294989726e-07</v>
@@ -9814,7 +9814,7 @@
         <v>2.314592510344073e-07</v>
       </c>
       <c r="CC28" t="n">
-        <v>1.922081262681836e-07</v>
+        <v>1.922081262681835e-07</v>
       </c>
       <c r="CD28" t="n">
         <v>2.949014096731737e-08</v>
@@ -9925,46 +9925,46 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7.692967373158586e-05</v>
+        <v>7.692967373158588e-05</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0003444433898232062</v>
+        <v>0.0003444433898232063</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0001861116761821458</v>
+        <v>0.0001861116761821457</v>
       </c>
       <c r="E29" t="n">
-        <v>5.204681034905215e-05</v>
+        <v>5.204681034905214e-05</v>
       </c>
       <c r="F29" t="n">
         <v>5.511008393493801e-05</v>
       </c>
       <c r="G29" t="n">
-        <v>5.054430319448e-05</v>
+        <v>5.054430319448001e-05</v>
       </c>
       <c r="H29" t="n">
-        <v>4.479270046260801e-05</v>
+        <v>4.4792700462608e-05</v>
       </c>
       <c r="I29" t="n">
         <v>5.3047184642332e-05</v>
       </c>
       <c r="J29" t="n">
-        <v>5.452489866783302e-05</v>
+        <v>5.4524898667833e-05</v>
       </c>
       <c r="K29" t="n">
-        <v>5.1262325794241e-05</v>
+        <v>5.126232579424101e-05</v>
       </c>
       <c r="L29" t="n">
-        <v>5.5453906583097e-05</v>
+        <v>5.545390658309699e-05</v>
       </c>
       <c r="M29" t="n">
-        <v>6.657261299466697e-05</v>
+        <v>6.657261299466703e-05</v>
       </c>
       <c r="N29" t="n">
-        <v>6.8969297426689e-05</v>
+        <v>6.896929742668897e-05</v>
       </c>
       <c r="O29" t="n">
-        <v>6.809355433631501e-05</v>
+        <v>6.809355433631502e-05</v>
       </c>
       <c r="P29" t="n">
         <v>7.154994810042901e-05</v>
@@ -9973,10 +9973,10 @@
         <v>5.328708166238e-05</v>
       </c>
       <c r="R29" t="n">
-        <v>5.7624809985695e-05</v>
+        <v>5.762480998569499e-05</v>
       </c>
       <c r="S29" t="n">
-        <v>7.427430528921e-05</v>
+        <v>7.427430528920998e-05</v>
       </c>
       <c r="T29" t="n">
         <v>6.437691527735801e-05</v>
@@ -9985,10 +9985,10 @@
         <v>8.428273438511001e-05</v>
       </c>
       <c r="V29" t="n">
-        <v>7.894184518045598e-05</v>
+        <v>7.894184518045599e-05</v>
       </c>
       <c r="W29" t="n">
-        <v>4.0201494049085e-05</v>
+        <v>4.020149404908501e-05</v>
       </c>
       <c r="X29" t="n">
         <v>2.4278059908331e-05</v>
@@ -10000,67 +10000,67 @@
         <v>2.472279133866499e-05</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.4704247496114e-05</v>
+        <v>4.470424749611399e-05</v>
       </c>
       <c r="AB29" t="n">
         <v>5.141332779313001e-05</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.959410103697998e-05</v>
+        <v>4.959410103698e-05</v>
       </c>
       <c r="AD29" t="n">
         <v>4.8257404809878e-05</v>
       </c>
       <c r="AE29" t="n">
-        <v>5.5324037106637e-05</v>
+        <v>5.532403710663699e-05</v>
       </c>
       <c r="AF29" t="n">
-        <v>5.333064341487099e-05</v>
+        <v>5.333064341487098e-05</v>
       </c>
       <c r="AG29" t="n">
         <v>7.202238955822001e-05</v>
       </c>
       <c r="AH29" t="n">
-        <v>6.407129125167201e-05</v>
+        <v>6.407129125167202e-05</v>
       </c>
       <c r="AI29" t="n">
-        <v>6.494843521788697e-05</v>
+        <v>6.494843521788701e-05</v>
       </c>
       <c r="AJ29" t="n">
         <v>2.7784835220191e-05</v>
       </c>
       <c r="AK29" t="n">
-        <v>3.7602757100893e-05</v>
+        <v>3.760275710089298e-05</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.5809099194239e-05</v>
+        <v>2.580909919423901e-05</v>
       </c>
       <c r="AM29" t="n">
-        <v>3.790872273898701e-05</v>
+        <v>3.790872273898702e-05</v>
       </c>
       <c r="AN29" t="n">
-        <v>5.294206128547499e-05</v>
+        <v>5.2942061285475e-05</v>
       </c>
       <c r="AO29" t="n">
-        <v>6.940020613122802e-05</v>
+        <v>6.940020613122801e-05</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.838335872680501e-05</v>
+        <v>6.8383358726805e-05</v>
       </c>
       <c r="AQ29" t="n">
         <v>3.8123549954748e-05</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.5331435144374e-05</v>
+        <v>3.533143514437401e-05</v>
       </c>
       <c r="AS29" t="n">
         <v>4.7164627157122e-05</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.689238757798701e-05</v>
+        <v>5.6892387577987e-05</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.9080444559817e-05</v>
+        <v>3.908044455981699e-05</v>
       </c>
       <c r="AV29" t="n">
         <v>4.559500000000001e-05</v>
@@ -10069,31 +10069,31 @@
         <v>5.144526525979744e-05</v>
       </c>
       <c r="AX29" t="n">
-        <v>6.23044857775338e-05</v>
+        <v>6.230448577753379e-05</v>
       </c>
       <c r="AY29" t="n">
-        <v>6.504330090086813e-05</v>
+        <v>6.504330090086818e-05</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.745894805653416e-05</v>
+        <v>5.745894805653417e-05</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.671287151959669e-05</v>
+        <v>6.671287151959671e-05</v>
       </c>
       <c r="BB29" t="n">
-        <v>3.774196183800358e-05</v>
+        <v>3.774196183800359e-05</v>
       </c>
       <c r="BC29" t="n">
         <v>7.069155864839168e-05</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.112844739387019e-05</v>
+        <v>3.112844739387018e-05</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.148489172327493e-05</v>
+        <v>6.148489172327492e-05</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.446100244391852e-05</v>
+        <v>5.446100244391851e-05</v>
       </c>
       <c r="BG29" t="n">
         <v>6.017612243992909e-05</v>
@@ -10105,7 +10105,7 @@
         <v>4.922858235636e-05</v>
       </c>
       <c r="BJ29" t="n">
-        <v>6.107170974261043e-05</v>
+        <v>6.107170974261041e-05</v>
       </c>
       <c r="BK29" t="n">
         <v>8.107323419545002e-05</v>
@@ -10114,28 +10114,28 @@
         <v>4.949210268116905e-05</v>
       </c>
       <c r="BM29" t="n">
-        <v>7.621318529890403e-05</v>
+        <v>7.621318529890401e-05</v>
       </c>
       <c r="BN29" t="n">
         <v>7.008970623214878e-05</v>
       </c>
       <c r="BO29" t="n">
-        <v>7.897261083859184e-05</v>
+        <v>7.897261083859183e-05</v>
       </c>
       <c r="BP29" t="n">
-        <v>7.457921460478248e-05</v>
+        <v>7.457921460478246e-05</v>
       </c>
       <c r="BQ29" t="n">
-        <v>6.620977625705747e-05</v>
+        <v>6.620977625705746e-05</v>
       </c>
       <c r="BR29" t="n">
-        <v>9.934569025655929e-05</v>
+        <v>9.934569025655927e-05</v>
       </c>
       <c r="BS29" t="n">
         <v>4.601915106479632e-05</v>
       </c>
       <c r="BT29" t="n">
-        <v>5.375118539641248e-05</v>
+        <v>5.375118539641247e-05</v>
       </c>
       <c r="BU29" t="n">
         <v>7.55738617027936e-05</v>
@@ -10144,25 +10144,25 @@
         <v>6.027462296589724e-05</v>
       </c>
       <c r="BW29" t="n">
-        <v>5.345972436302423e-05</v>
+        <v>5.345972436302422e-05</v>
       </c>
       <c r="BX29" t="n">
         <v>5.333694617377145e-05</v>
       </c>
       <c r="BY29" t="n">
-        <v>6.745797288349683e-05</v>
+        <v>6.74579728834968e-05</v>
       </c>
       <c r="BZ29" t="n">
         <v>0.0001112143815810282</v>
       </c>
       <c r="CA29" t="n">
-        <v>8.236182997453296e-05</v>
+        <v>8.236182997453293e-05</v>
       </c>
       <c r="CB29" t="n">
         <v>8.301975700220137e-05</v>
       </c>
       <c r="CC29" t="n">
-        <v>8.374421861066442e-05</v>
+        <v>8.374421861066446e-05</v>
       </c>
       <c r="CD29" t="n">
         <v>2.980743736405913e-05</v>
@@ -10174,22 +10174,22 @@
         <v>3.287539736986301e-05</v>
       </c>
       <c r="CG29" t="n">
-        <v>3.658093945565344e-05</v>
+        <v>3.658093945565343e-05</v>
       </c>
       <c r="CH29" t="n">
-        <v>2.80342468508211e-05</v>
+        <v>2.803424685082109e-05</v>
       </c>
       <c r="CI29" t="n">
         <v>3.16078312351871e-05</v>
       </c>
       <c r="CJ29" t="n">
-        <v>3.222635445258547e-05</v>
+        <v>3.222635445258548e-05</v>
       </c>
       <c r="CK29" t="n">
         <v>3.06253484994772e-05</v>
       </c>
       <c r="CL29" t="n">
-        <v>2.75642530154822e-05</v>
+        <v>2.756425301548219e-05</v>
       </c>
       <c r="CM29" t="n">
         <v>1.610138647914337e-05</v>
@@ -10219,13 +10219,13 @@
         <v>1.635092144603757e-05</v>
       </c>
       <c r="CV29" t="n">
-        <v>1.69735327820445e-05</v>
+        <v>1.697353278204449e-05</v>
       </c>
       <c r="CW29" t="n">
-        <v>1.661331786238683e-05</v>
+        <v>1.661331786238682e-05</v>
       </c>
       <c r="CX29" t="n">
-        <v>1.681963637626923e-05</v>
+        <v>1.681963637626924e-05</v>
       </c>
       <c r="CY29" t="n">
         <v>1.747863425890582e-05</v>
@@ -10234,10 +10234,10 @@
         <v>1.758448136882068e-05</v>
       </c>
       <c r="DA29" t="n">
-        <v>1.70216074304962e-05</v>
+        <v>1.702160743049619e-05</v>
       </c>
       <c r="DB29" t="n">
-        <v>1.790394307805398e-05</v>
+        <v>1.790394307805397e-05</v>
       </c>
       <c r="DC29" t="n">
         <v>1.703558167586488e-05</v>
@@ -10276,10 +10276,10 @@
         <v>1.775829637145537e-05</v>
       </c>
       <c r="DO29" t="n">
-        <v>1.730537790751677e-05</v>
+        <v>1.730537790751678e-05</v>
       </c>
       <c r="DP29" t="n">
-        <v>1.685233612966953e-05</v>
+        <v>1.685233612966952e-05</v>
       </c>
     </row>
     <row r="30">
@@ -10541,19 +10541,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0001734101199804806</v>
+        <v>0.0001734101199804805</v>
       </c>
       <c r="C32" t="n">
         <v>0.0001195082503147362</v>
       </c>
       <c r="D32" t="n">
-        <v>9.710928381808741e-05</v>
+        <v>9.710928381808743e-05</v>
       </c>
       <c r="E32" t="n">
         <v>0.0001642149265789828</v>
       </c>
       <c r="F32" t="n">
-        <v>6.203777936982001e-05</v>
+        <v>6.203777936982e-05</v>
       </c>
       <c r="G32" t="n">
         <v>7.341784819211999e-05</v>
@@ -10562,16 +10562,16 @@
         <v>6.303642246779e-05</v>
       </c>
       <c r="I32" t="n">
-        <v>6.41397000712e-05</v>
+        <v>6.413970007119999e-05</v>
       </c>
       <c r="J32" t="n">
-        <v>7.132303324244999e-05</v>
+        <v>7.132303324244998e-05</v>
       </c>
       <c r="K32" t="n">
-        <v>7.316499202999998e-05</v>
+        <v>7.316499203000001e-05</v>
       </c>
       <c r="L32" t="n">
-        <v>7.394101628125002e-05</v>
+        <v>7.394101628124999e-05</v>
       </c>
       <c r="M32" t="n">
         <v>0.00011966500665306</v>
@@ -10616,13 +10616,13 @@
         <v>5.324144767424e-05</v>
       </c>
       <c r="AA32" t="n">
-        <v>9.653595031653e-05</v>
+        <v>9.653595031652999e-05</v>
       </c>
       <c r="AB32" t="n">
-        <v>6.639770465575999e-05</v>
+        <v>6.639770465576001e-05</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.952645196157e-05</v>
+        <v>9.952645196157003e-05</v>
       </c>
       <c r="AD32" t="n">
         <v>0.0001179099381426</v>
@@ -10643,13 +10643,13 @@
         <v>0.00011648817235502</v>
       </c>
       <c r="AJ32" t="n">
-        <v>8.798520122866e-05</v>
+        <v>8.798520122865999e-05</v>
       </c>
       <c r="AK32" t="n">
         <v>0.00012832622726822</v>
       </c>
       <c r="AL32" t="n">
-        <v>8.06116195323e-05</v>
+        <v>8.061161953229999e-05</v>
       </c>
       <c r="AM32" t="n">
         <v>0.00011178416157802</v>
@@ -10670,7 +10670,7 @@
         <v>0.00010727096192997</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.479084226385001e-05</v>
+        <v>5.479084226384999e-05</v>
       </c>
       <c r="AT32" t="n">
         <v>6.12433582209e-05</v>
@@ -10682,16 +10682,16 @@
         <v>0.0001752736666666667</v>
       </c>
       <c r="AW32" t="n">
-        <v>9.455642648461431e-05</v>
+        <v>9.455642648461433e-05</v>
       </c>
       <c r="AX32" t="n">
-        <v>8.636579930041365e-05</v>
+        <v>8.636579930041363e-05</v>
       </c>
       <c r="AY32" t="n">
         <v>0.0001008927137661198</v>
       </c>
       <c r="AZ32" t="n">
-        <v>9.275773081110527e-05</v>
+        <v>9.275773081110528e-05</v>
       </c>
       <c r="BA32" t="n">
         <v>0.0002500503001034255</v>
@@ -10724,7 +10724,7 @@
         <v>0.0002781387510694121</v>
       </c>
       <c r="BK32" t="n">
-        <v>0.0002581000581288609</v>
+        <v>0.0002581000581288608</v>
       </c>
       <c r="BL32" t="n">
         <v>0.0002247940897089007</v>
@@ -10742,10 +10742,10 @@
         <v>0.0002280767511549319</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0.0002072279308000663</v>
+        <v>0.0002072279308000664</v>
       </c>
       <c r="BR32" t="n">
-        <v>0.0002016614509946529</v>
+        <v>0.000201661450994653</v>
       </c>
       <c r="BS32" t="n">
         <v>5.901397091579508e-05</v>
@@ -10766,13 +10766,13 @@
         <v>6.112368924950195e-05</v>
       </c>
       <c r="BY32" t="n">
-        <v>6.501128138758526e-05</v>
+        <v>6.501128138758528e-05</v>
       </c>
       <c r="BZ32" t="n">
-        <v>8.827094047198175e-05</v>
+        <v>8.827094047198174e-05</v>
       </c>
       <c r="CA32" t="n">
-        <v>6.999689186016782e-05</v>
+        <v>6.99968918601678e-05</v>
       </c>
       <c r="CB32" t="n">
         <v>8.587084713300477e-05</v>
@@ -10781,7 +10781,7 @@
         <v>6.304144776759681e-05</v>
       </c>
       <c r="CD32" t="n">
-        <v>9.283505636866943e-05</v>
+        <v>9.283505636866942e-05</v>
       </c>
       <c r="CE32" t="n">
         <v>9.979905811376792e-05</v>
@@ -10793,10 +10793,10 @@
         <v>0.0001604821152519813</v>
       </c>
       <c r="CH32" t="n">
-        <v>0.0001354671941676416</v>
+        <v>0.0001354671941676415</v>
       </c>
       <c r="CI32" t="n">
-        <v>0.0001686487173393003</v>
+        <v>0.0001686487173393002</v>
       </c>
       <c r="CJ32" t="n">
         <v>0.0001846883658608165</v>
@@ -10808,25 +10808,25 @@
         <v>0.0001711423484600997</v>
       </c>
       <c r="CM32" t="n">
-        <v>8.171449077247469e-05</v>
+        <v>8.171449077247467e-05</v>
       </c>
       <c r="CN32" t="n">
-        <v>8.329230304937269e-05</v>
+        <v>8.329230304937265e-05</v>
       </c>
       <c r="CO32" t="n">
         <v>8.433441688357315e-05</v>
       </c>
       <c r="CP32" t="n">
-        <v>8.573383056375892e-05</v>
+        <v>8.57338305637589e-05</v>
       </c>
       <c r="CQ32" t="n">
-        <v>8.366994596545834e-05</v>
+        <v>8.366994596545832e-05</v>
       </c>
       <c r="CR32" t="n">
-        <v>8.512145836451274e-05</v>
+        <v>8.512145836451271e-05</v>
       </c>
       <c r="CS32" t="n">
-        <v>9.111272217482948e-05</v>
+        <v>9.111272217482949e-05</v>
       </c>
       <c r="CT32" t="n">
         <v>8.987488334175804e-05</v>
@@ -10841,13 +10841,13 @@
         <v>8.849342300874057e-05</v>
       </c>
       <c r="CX32" t="n">
-        <v>8.916867437969758e-05</v>
+        <v>8.916867437969756e-05</v>
       </c>
       <c r="CY32" t="n">
-        <v>8.705434431925434e-05</v>
+        <v>8.705434431925428e-05</v>
       </c>
       <c r="CZ32" t="n">
-        <v>8.820389350463012e-05</v>
+        <v>8.820389350463008e-05</v>
       </c>
       <c r="DA32" t="n">
         <v>8.753720862401917e-05</v>
@@ -10856,28 +10856,28 @@
         <v>8.762799763977749e-05</v>
       </c>
       <c r="DC32" t="n">
-        <v>8.762635353696009e-05</v>
+        <v>8.762635353696007e-05</v>
       </c>
       <c r="DD32" t="n">
-        <v>8.756998506079865e-05</v>
+        <v>8.756998506079868e-05</v>
       </c>
       <c r="DE32" t="n">
-        <v>8.606011506165191e-05</v>
+        <v>8.606011506165192e-05</v>
       </c>
       <c r="DF32" t="n">
-        <v>8.733996682119702e-05</v>
+        <v>8.733996682119699e-05</v>
       </c>
       <c r="DG32" t="n">
         <v>8.520029055129324e-05</v>
       </c>
       <c r="DH32" t="n">
-        <v>8.71624903994688e-05</v>
+        <v>8.716249039946879e-05</v>
       </c>
       <c r="DI32" t="n">
-        <v>8.94930594173863e-05</v>
+        <v>8.949305941738633e-05</v>
       </c>
       <c r="DJ32" t="n">
-        <v>8.651061706196161e-05</v>
+        <v>8.651061706196158e-05</v>
       </c>
       <c r="DK32" t="n">
         <v>8.755659088338757e-05</v>
@@ -10889,13 +10889,13 @@
         <v>9.345240790441899e-05</v>
       </c>
       <c r="DN32" t="n">
-        <v>8.711850103598019e-05</v>
+        <v>8.71185010359802e-05</v>
       </c>
       <c r="DO32" t="n">
-        <v>8.717715826121774e-05</v>
+        <v>8.717715826121775e-05</v>
       </c>
       <c r="DP32" t="n">
-        <v>8.700363984635554e-05</v>
+        <v>8.700363984635551e-05</v>
       </c>
     </row>
     <row r="33">
@@ -10932,7 +10932,7 @@
         <v>0.0002447854431087</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00026026090850113</v>
+        <v>0.0002602609085011301</v>
       </c>
       <c r="L33" t="n">
         <v>0.00031472267546659</v>
@@ -10941,7 +10941,7 @@
         <v>0.00040678997813074</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0004207899502157399</v>
+        <v>0.00042078995021574</v>
       </c>
       <c r="O33" t="n">
         <v>0.0003566942526332701</v>
@@ -10959,22 +10959,22 @@
         <v>0.0004023773695734701</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0007424711324885801</v>
+        <v>0.0007424711324885802</v>
       </c>
       <c r="U33" t="n">
         <v>0.00086169708224854</v>
       </c>
       <c r="V33" t="n">
-        <v>0.00088381823935824</v>
+        <v>0.0008838182393582401</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0004925415806193801</v>
+        <v>0.0004925415806193803</v>
       </c>
       <c r="X33" t="n">
         <v>0.00027930724586416</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.00041190420533422</v>
+        <v>0.0004119042053342201</v>
       </c>
       <c r="Z33" t="n">
         <v>0.00019777099991465</v>
@@ -10983,7 +10983,7 @@
         <v>0.00032300394091914</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.00031548104220215</v>
+        <v>0.0003154810422021499</v>
       </c>
       <c r="AC33" t="n">
         <v>0.00033846466274471</v>
@@ -10998,16 +10998,16 @@
         <v>0.00042956483051239</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.0005038605825267</v>
+        <v>0.0005038605825267001</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.0003877644341846501</v>
+        <v>0.00038776443418465</v>
       </c>
       <c r="AI33" t="n">
         <v>0.00034328382257693</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.00027405793747322</v>
+        <v>0.0002740579374732199</v>
       </c>
       <c r="AK33" t="n">
         <v>0.00038146056493067</v>
@@ -11016,13 +11016,13 @@
         <v>0.00028616300702778</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.000429422846298</v>
+        <v>0.0004294228462979999</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.0004047902984606299</v>
+        <v>0.00040479029846063</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.0005108560027667799</v>
+        <v>0.00051085600276678</v>
       </c>
       <c r="AP33" t="n">
         <v>0.00044812604967152</v>
@@ -11037,7 +11037,7 @@
         <v>0.00026163801349696</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.00026407494217144</v>
+        <v>0.0002640749421714399</v>
       </c>
       <c r="AU33" t="n">
         <v>0.00027265615378664</v>
@@ -11046,10 +11046,10 @@
         <v>0.0001360313333333333</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.0003105522521111555</v>
+        <v>0.0003105522521111554</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.0002942848220244344</v>
+        <v>0.0002942848220244343</v>
       </c>
       <c r="AY33" t="n">
         <v>0.0003564000071692077</v>
@@ -11058,7 +11058,7 @@
         <v>0.000353603787163771</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.000463326404695468</v>
+        <v>0.0004633264046954681</v>
       </c>
       <c r="BB33" t="n">
         <v>0.0003101900701874885</v>
@@ -11067,7 +11067,7 @@
         <v>0.0004755284124357525</v>
       </c>
       <c r="BD33" t="n">
-        <v>0.0002555376077422433</v>
+        <v>0.0002555376077422434</v>
       </c>
       <c r="BE33" t="n">
         <v>0.0002689871742490704</v>
@@ -11079,10 +11079,10 @@
         <v>0.0002936094467648264</v>
       </c>
       <c r="BH33" t="n">
-        <v>0.0002720804840118223</v>
+        <v>0.0002720804840118224</v>
       </c>
       <c r="BI33" t="n">
-        <v>0.0003496002356345566</v>
+        <v>0.0003496002356345567</v>
       </c>
       <c r="BJ33" t="n">
         <v>0.0003144471975403022</v>
@@ -11094,19 +11094,19 @@
         <v>0.0003117789453259216</v>
       </c>
       <c r="BM33" t="n">
-        <v>0.0003640544302154102</v>
+        <v>0.0003640544302154101</v>
       </c>
       <c r="BN33" t="n">
         <v>0.0003694249565112089</v>
       </c>
       <c r="BO33" t="n">
-        <v>0.0003613114419507307</v>
+        <v>0.0003613114419507305</v>
       </c>
       <c r="BP33" t="n">
         <v>0.0003913507508382597</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0.0003990477733113583</v>
+        <v>0.0003990477733113584</v>
       </c>
       <c r="BR33" t="n">
         <v>0.0003748259857022584</v>
@@ -11118,28 +11118,28 @@
         <v>0.000353709168416827</v>
       </c>
       <c r="BU33" t="n">
-        <v>0.0003176339832398152</v>
+        <v>0.0003176339832398153</v>
       </c>
       <c r="BV33" t="n">
         <v>0.0002786523249728813</v>
       </c>
       <c r="BW33" t="n">
-        <v>0.0003109268411350254</v>
+        <v>0.0003109268411350255</v>
       </c>
       <c r="BX33" t="n">
-        <v>0.0002976032671211089</v>
+        <v>0.0002976032671211088</v>
       </c>
       <c r="BY33" t="n">
         <v>0.0002673830090824672</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0.0003189427792699174</v>
+        <v>0.0003189427792699175</v>
       </c>
       <c r="CA33" t="n">
-        <v>0.00034579465381522</v>
+        <v>0.0003457946538152199</v>
       </c>
       <c r="CB33" t="n">
-        <v>0.0003185863124765644</v>
+        <v>0.0003185863124765643</v>
       </c>
       <c r="CC33" t="n">
         <v>0.0003817163032685806</v>
@@ -11148,19 +11148,19 @@
         <v>0.0002724882513177023</v>
       </c>
       <c r="CE33" t="n">
-        <v>0.000288425598558459</v>
+        <v>0.0002884255985584591</v>
       </c>
       <c r="CF33" t="n">
         <v>0.0002707378234545668</v>
       </c>
       <c r="CG33" t="n">
-        <v>0.0002780647240263204</v>
+        <v>0.0002780647240263203</v>
       </c>
       <c r="CH33" t="n">
         <v>0.0001928303203072798</v>
       </c>
       <c r="CI33" t="n">
-        <v>0.000221032975932743</v>
+        <v>0.0002210329759327429</v>
       </c>
       <c r="CJ33" t="n">
         <v>0.0002499558747267908</v>
@@ -11169,10 +11169,10 @@
         <v>0.0002488590408431331</v>
       </c>
       <c r="CL33" t="n">
-        <v>0.0002069714442234416</v>
+        <v>0.0002069714442234415</v>
       </c>
       <c r="CM33" t="n">
-        <v>0.0001824783455299723</v>
+        <v>0.0001824783455299722</v>
       </c>
       <c r="CN33" t="n">
         <v>0.00017737645903318</v>
@@ -11193,16 +11193,16 @@
         <v>0.0001619213739791897</v>
       </c>
       <c r="CT33" t="n">
-        <v>0.0001601912204910277</v>
+        <v>0.0001601912204910278</v>
       </c>
       <c r="CU33" t="n">
         <v>0.0001581272079260696</v>
       </c>
       <c r="CV33" t="n">
-        <v>0.0001571672006665932</v>
+        <v>0.0001571672006665931</v>
       </c>
       <c r="CW33" t="n">
-        <v>0.0001594473740698072</v>
+        <v>0.0001594473740698073</v>
       </c>
       <c r="CX33" t="n">
         <v>0.0001589911620540893</v>
@@ -11217,7 +11217,7 @@
         <v>0.0001565356971078086</v>
       </c>
       <c r="DB33" t="n">
-        <v>0.000156164270495506</v>
+        <v>0.0001561642704955061</v>
       </c>
       <c r="DC33" t="n">
         <v>0.0001647690105310284</v>
@@ -11226,16 +11226,16 @@
         <v>0.0001543207179403995</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.0001779435986323321</v>
+        <v>0.000177943598632332</v>
       </c>
       <c r="DF33" t="n">
         <v>0.0001721589513800822</v>
       </c>
       <c r="DG33" t="n">
-        <v>0.0001745999027369293</v>
+        <v>0.0001745999027369294</v>
       </c>
       <c r="DH33" t="n">
-        <v>0.0001724773722120612</v>
+        <v>0.0001724773722120613</v>
       </c>
       <c r="DI33" t="n">
         <v>0.0001707556138136515</v>
@@ -11250,13 +11250,13 @@
         <v>0.0001607773853764452</v>
       </c>
       <c r="DM33" t="n">
-        <v>0.0001581499951351135</v>
+        <v>0.0001581499951351136</v>
       </c>
       <c r="DN33" t="n">
-        <v>0.0001638103487246291</v>
+        <v>0.0001638103487246292</v>
       </c>
       <c r="DO33" t="n">
-        <v>0.0001620675488380538</v>
+        <v>0.0001620675488380537</v>
       </c>
       <c r="DP33" t="n">
         <v>0.0001671767291823867</v>
@@ -11872,10 +11872,10 @@
         <v>2.3270328229e-07</v>
       </c>
       <c r="G36" t="n">
-        <v>3.189174733900001e-07</v>
+        <v>3.1891747339e-07</v>
       </c>
       <c r="H36" t="n">
-        <v>2.8422397544e-07</v>
+        <v>2.842239754400001e-07</v>
       </c>
       <c r="I36" t="n">
         <v>2.7798341255e-07</v>
@@ -11884,7 +11884,7 @@
         <v>3.3596501428e-07</v>
       </c>
       <c r="K36" t="n">
-        <v>3.059662164700001e-07</v>
+        <v>3.0596621647e-07</v>
       </c>
       <c r="L36" t="n">
         <v>3.3424027703e-07</v>
@@ -11920,7 +11920,7 @@
         <v>8.6066165563e-07</v>
       </c>
       <c r="W36" t="n">
-        <v>6.465267482199999e-07</v>
+        <v>6.4652674822e-07</v>
       </c>
       <c r="X36" t="n">
         <v>2.9948662313e-07</v>
@@ -11941,16 +11941,16 @@
         <v>3.7005955587e-07</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.632866993499999e-07</v>
+        <v>4.632866993500001e-07</v>
       </c>
       <c r="AE36" t="n">
-        <v>6.357895746199999e-07</v>
+        <v>6.357895746200001e-07</v>
       </c>
       <c r="AF36" t="n">
-        <v>4.6278736952e-07</v>
+        <v>4.627873695199999e-07</v>
       </c>
       <c r="AG36" t="n">
-        <v>4.351310418700001e-07</v>
+        <v>4.3513104187e-07</v>
       </c>
       <c r="AH36" t="n">
         <v>3.9176407076e-07</v>
@@ -12004,7 +12004,7 @@
         <v>3.317464596753775e-06</v>
       </c>
       <c r="AY36" t="n">
-        <v>3.485286004182648e-06</v>
+        <v>3.485286004182649e-06</v>
       </c>
       <c r="AZ36" t="n">
         <v>3.341559181778685e-06</v>
@@ -12070,7 +12070,7 @@
         <v>2.486438749168069e-06</v>
       </c>
       <c r="BU36" t="n">
-        <v>3.204541367434686e-06</v>
+        <v>3.204541367434687e-06</v>
       </c>
       <c r="BV36" t="n">
         <v>3.071166435287869e-06</v>
@@ -12221,43 +12221,43 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6.857127930960835e-05</v>
+        <v>6.857127930960836e-05</v>
       </c>
       <c r="C37" t="n">
         <v>0.0001047887683767744</v>
       </c>
       <c r="D37" t="n">
-        <v>0.000172453454979587</v>
+        <v>0.0001724534549795871</v>
       </c>
       <c r="E37" t="n">
         <v>6.055671129307664e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>5.189534162091001e-05</v>
+        <v>5.189534162091002e-05</v>
       </c>
       <c r="G37" t="n">
-        <v>6.438556889403002e-05</v>
+        <v>6.438556889403e-05</v>
       </c>
       <c r="H37" t="n">
-        <v>5.691751601847999e-05</v>
+        <v>5.691751601847998e-05</v>
       </c>
       <c r="I37" t="n">
-        <v>5.8798870794809e-05</v>
+        <v>5.879887079480901e-05</v>
       </c>
       <c r="J37" t="n">
         <v>6.125784280468e-05</v>
       </c>
       <c r="K37" t="n">
-        <v>5.803952792494999e-05</v>
+        <v>5.803952792495e-05</v>
       </c>
       <c r="L37" t="n">
         <v>5.75796023475e-05</v>
       </c>
       <c r="M37" t="n">
-        <v>7.318654259678002e-05</v>
+        <v>7.318654259677999e-05</v>
       </c>
       <c r="N37" t="n">
-        <v>7.740033951147999e-05</v>
+        <v>7.740033951148e-05</v>
       </c>
       <c r="O37" t="n">
         <v>6.625095685627001e-05</v>
@@ -12266,13 +12266,13 @@
         <v>7.739648118364e-05</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.148929809209e-05</v>
+        <v>4.148929809208998e-05</v>
       </c>
       <c r="R37" t="n">
         <v>6.924874404502e-05</v>
       </c>
       <c r="S37" t="n">
-        <v>8.334685208070004e-05</v>
+        <v>8.33468520807e-05</v>
       </c>
       <c r="T37" t="n">
         <v>0.000102591819617044</v>
@@ -12281,28 +12281,28 @@
         <v>0.00015177402590989</v>
       </c>
       <c r="V37" t="n">
-        <v>0.0001474661239131201</v>
+        <v>0.00014746612391312</v>
       </c>
       <c r="W37" t="n">
-        <v>9.921905308042001e-05</v>
+        <v>9.921905308042e-05</v>
       </c>
       <c r="X37" t="n">
         <v>5.292114758622e-05</v>
       </c>
       <c r="Y37" t="n">
-        <v>6.417884728273001e-05</v>
+        <v>6.417884728273e-05</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.797155861962499e-05</v>
+        <v>4.7971558619625e-05</v>
       </c>
       <c r="AA37" t="n">
         <v>7.632800757388e-05</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.646445345190001e-05</v>
+        <v>4.64644534519e-05</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.677735804073e-05</v>
+        <v>7.677735804073001e-05</v>
       </c>
       <c r="AD37" t="n">
         <v>0.00010859767616725</v>
@@ -12314,19 +12314,19 @@
         <v>0.00011727826843867</v>
       </c>
       <c r="AG37" t="n">
-        <v>8.501394584468001e-05</v>
+        <v>8.501394584468e-05</v>
       </c>
       <c r="AH37" t="n">
-        <v>7.623333648891999e-05</v>
+        <v>7.623333648891998e-05</v>
       </c>
       <c r="AI37" t="n">
-        <v>8.004517031233999e-05</v>
+        <v>8.004517031234001e-05</v>
       </c>
       <c r="AJ37" t="n">
         <v>5.943831137354301e-05</v>
       </c>
       <c r="AK37" t="n">
-        <v>8.281514216104999e-05</v>
+        <v>8.281514216104998e-05</v>
       </c>
       <c r="AL37" t="n">
         <v>5.854662076042e-05</v>
@@ -12344,34 +12344,34 @@
         <v>9.419333287196e-05</v>
       </c>
       <c r="AQ37" t="n">
-        <v>9.571243592493e-05</v>
+        <v>9.571243592493002e-05</v>
       </c>
       <c r="AR37" t="n">
-        <v>7.536949747735002e-05</v>
+        <v>7.536949747734999e-05</v>
       </c>
       <c r="AS37" t="n">
         <v>3.5787311076533e-05</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.8327888123642e-05</v>
+        <v>3.832788812364201e-05</v>
       </c>
       <c r="AU37" t="n">
-        <v>5.9534601566729e-05</v>
+        <v>5.953460156672898e-05</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.0001658303333333334</v>
+        <v>0.0001658303333333333</v>
       </c>
       <c r="AW37" t="n">
         <v>8.096743104991673e-05</v>
       </c>
       <c r="AX37" t="n">
-        <v>6.245961757152301e-05</v>
+        <v>6.245961757152302e-05</v>
       </c>
       <c r="AY37" t="n">
-        <v>8.343271169656123e-05</v>
+        <v>8.343271169656125e-05</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.896880088478882e-05</v>
+        <v>3.896880088478884e-05</v>
       </c>
       <c r="BA37" t="n">
         <v>0.0002200727002194408</v>
@@ -12389,7 +12389,7 @@
         <v>0.0002008964291840201</v>
       </c>
       <c r="BF37" t="n">
-        <v>0.000192055951396188</v>
+        <v>0.0001920559513961879</v>
       </c>
       <c r="BG37" t="n">
         <v>0.0002311023640160996</v>
@@ -12401,37 +12401,37 @@
         <v>0.000380122682310279</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0.0005343683513825639</v>
+        <v>0.0005343683513825638</v>
       </c>
       <c r="BK37" t="n">
-        <v>0.0006450834890185152</v>
+        <v>0.0006450834890185153</v>
       </c>
       <c r="BL37" t="n">
-        <v>0.0004957509911969114</v>
+        <v>0.0004957509911969113</v>
       </c>
       <c r="BM37" t="n">
-        <v>0.0004079503718843905</v>
+        <v>0.0004079503718843906</v>
       </c>
       <c r="BN37" t="n">
         <v>0.0004156404366515111</v>
       </c>
       <c r="BO37" t="n">
-        <v>0.0004689237693627864</v>
+        <v>0.0004689237693627863</v>
       </c>
       <c r="BP37" t="n">
         <v>0.000365316230988625</v>
       </c>
       <c r="BQ37" t="n">
-        <v>0.0003715256825287943</v>
+        <v>0.0003715256825287944</v>
       </c>
       <c r="BR37" t="n">
-        <v>0.0002138018438125042</v>
+        <v>0.0002138018438125041</v>
       </c>
       <c r="BS37" t="n">
         <v>0.0002085575010433408</v>
       </c>
       <c r="BT37" t="n">
-        <v>0.0002774965957379155</v>
+        <v>0.0002774965957379154</v>
       </c>
       <c r="BU37" t="n">
         <v>6.24080786056558e-05</v>
@@ -12440,7 +12440,7 @@
         <v>6.331127852965861e-05</v>
       </c>
       <c r="BW37" t="n">
-        <v>0.0002316026696632918</v>
+        <v>0.0002316026696632919</v>
       </c>
       <c r="BX37" t="n">
         <v>0.0002103152436674878</v>
@@ -12449,7 +12449,7 @@
         <v>0.0004419958403361116</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0.0002354434649530312</v>
+        <v>0.0002354434649530311</v>
       </c>
       <c r="CA37" t="n">
         <v>0.0002424057871614251</v>
@@ -12473,7 +12473,7 @@
         <v>0.0001801039679873708</v>
       </c>
       <c r="CH37" t="n">
-        <v>0.0001495859927230416</v>
+        <v>0.0001495859927230415</v>
       </c>
       <c r="CI37" t="n">
         <v>0.0001835875309255167</v>
@@ -12485,25 +12485,25 @@
         <v>0.0002068958431821309</v>
       </c>
       <c r="CL37" t="n">
-        <v>0.0001596957452220077</v>
+        <v>0.0001596957452220078</v>
       </c>
       <c r="CM37" t="n">
-        <v>4.654788820550795e-05</v>
+        <v>4.654788820550794e-05</v>
       </c>
       <c r="CN37" t="n">
         <v>5.000302342058697e-05</v>
       </c>
       <c r="CO37" t="n">
-        <v>4.981682673003274e-05</v>
+        <v>4.981682673003275e-05</v>
       </c>
       <c r="CP37" t="n">
-        <v>4.984634869768117e-05</v>
+        <v>4.984634869768116e-05</v>
       </c>
       <c r="CQ37" t="n">
         <v>4.999948327998436e-05</v>
       </c>
       <c r="CR37" t="n">
-        <v>4.95575240447661e-05</v>
+        <v>4.955752404476608e-05</v>
       </c>
       <c r="CS37" t="n">
         <v>4.860945724309583e-05</v>
@@ -12512,52 +12512,52 @@
         <v>5.038261451731774e-05</v>
       </c>
       <c r="CU37" t="n">
-        <v>4.846308882301239e-05</v>
+        <v>4.846308882301238e-05</v>
       </c>
       <c r="CV37" t="n">
-        <v>4.919692895713137e-05</v>
+        <v>4.919692895713136e-05</v>
       </c>
       <c r="CW37" t="n">
-        <v>4.906374216550586e-05</v>
+        <v>4.906374216550584e-05</v>
       </c>
       <c r="CX37" t="n">
-        <v>4.926093867056133e-05</v>
+        <v>4.926093867056134e-05</v>
       </c>
       <c r="CY37" t="n">
-        <v>4.61671391568093e-05</v>
+        <v>4.616713915680931e-05</v>
       </c>
       <c r="CZ37" t="n">
-        <v>4.772061664400127e-05</v>
+        <v>4.772061664400128e-05</v>
       </c>
       <c r="DA37" t="n">
         <v>4.646603072722332e-05</v>
       </c>
       <c r="DB37" t="n">
-        <v>4.534813680992092e-05</v>
+        <v>4.534813680992094e-05</v>
       </c>
       <c r="DC37" t="n">
-        <v>4.722237679111698e-05</v>
+        <v>4.722237679111699e-05</v>
       </c>
       <c r="DD37" t="n">
-        <v>4.664597073909567e-05</v>
+        <v>4.664597073909568e-05</v>
       </c>
       <c r="DE37" t="n">
         <v>4.759451872835914e-05</v>
       </c>
       <c r="DF37" t="n">
-        <v>4.778203589355124e-05</v>
+        <v>4.778203589355127e-05</v>
       </c>
       <c r="DG37" t="n">
         <v>4.591835686293929e-05</v>
       </c>
       <c r="DH37" t="n">
-        <v>4.76111704149709e-05</v>
+        <v>4.761117041497089e-05</v>
       </c>
       <c r="DI37" t="n">
-        <v>4.868991203999873e-05</v>
+        <v>4.868991203999871e-05</v>
       </c>
       <c r="DJ37" t="n">
-        <v>4.7377849228753e-05</v>
+        <v>4.737784922875302e-05</v>
       </c>
       <c r="DK37" t="n">
         <v>4.647658789842752e-05</v>
@@ -12566,13 +12566,13 @@
         <v>4.894035405651986e-05</v>
       </c>
       <c r="DM37" t="n">
-        <v>5.112473326611857e-05</v>
+        <v>5.112473326611858e-05</v>
       </c>
       <c r="DN37" t="n">
         <v>4.786195837479132e-05</v>
       </c>
       <c r="DO37" t="n">
-        <v>4.857105614752593e-05</v>
+        <v>4.857105614752592e-05</v>
       </c>
       <c r="DP37" t="n">
         <v>4.916988486805984e-05</v>
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7.759290423526627e-07</v>
+        <v>7.759290423526625e-07</v>
       </c>
       <c r="C43" t="n">
         <v>9.263273192704931e-07</v>
@@ -13297,10 +13297,10 @@
         <v>6.5651674992e-07</v>
       </c>
       <c r="H43" t="n">
-        <v>5.414965335700001e-07</v>
+        <v>5.4149653357e-07</v>
       </c>
       <c r="I43" t="n">
-        <v>6.0952354282e-07</v>
+        <v>6.095235428199999e-07</v>
       </c>
       <c r="J43" t="n">
         <v>6.2066742405e-07</v>
@@ -13309,13 +13309,13 @@
         <v>5.924545609100001e-07</v>
       </c>
       <c r="L43" t="n">
-        <v>6.4740461436e-07</v>
+        <v>6.474046143600001e-07</v>
       </c>
       <c r="M43" t="n">
-        <v>7.688124200300001e-07</v>
+        <v>7.6881242003e-07</v>
       </c>
       <c r="N43" t="n">
-        <v>7.744193016100001e-07</v>
+        <v>7.7441930161e-07</v>
       </c>
       <c r="O43" t="n">
         <v>6.9735085518e-07</v>
@@ -13324,7 +13324,7 @@
         <v>8.282529715700002e-07</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.9064818703e-07</v>
+        <v>4.906481870300001e-07</v>
       </c>
       <c r="R43" t="n">
         <v>7.416873272600001e-07</v>
@@ -13372,28 +13372,28 @@
         <v>1.011663428e-06</v>
       </c>
       <c r="AG43" t="n">
-        <v>9.1456069671e-07</v>
+        <v>9.145606967100001e-07</v>
       </c>
       <c r="AH43" t="n">
-        <v>8.003130058400001e-07</v>
+        <v>8.0031300584e-07</v>
       </c>
       <c r="AI43" t="n">
         <v>9.1425859776e-07</v>
       </c>
       <c r="AJ43" t="n">
-        <v>7.866403440500001e-07</v>
+        <v>7.866403440500002e-07</v>
       </c>
       <c r="AK43" t="n">
         <v>1.0400013237e-06</v>
       </c>
       <c r="AL43" t="n">
-        <v>7.8398103734e-07</v>
+        <v>7.839810373399999e-07</v>
       </c>
       <c r="AM43" t="n">
         <v>1.15002475659e-06</v>
       </c>
       <c r="AN43" t="n">
-        <v>8.352845198600001e-07</v>
+        <v>8.352845198600002e-07</v>
       </c>
       <c r="AO43" t="n">
         <v>1.1727457228e-06</v>
@@ -13414,7 +13414,7 @@
         <v>5.2566440302e-07</v>
       </c>
       <c r="AU43" t="n">
-        <v>4.857216655899999e-07</v>
+        <v>4.8572166559e-07</v>
       </c>
       <c r="AV43" t="n">
         <v>1.697166666666667e-06</v>
@@ -13426,7 +13426,7 @@
         <v>1.006693617117063e-06</v>
       </c>
       <c r="AY43" t="n">
-        <v>5.15363965499766e-07</v>
+        <v>5.153639654997659e-07</v>
       </c>
       <c r="AZ43" t="n">
         <v>5.457979250302989e-07</v>
@@ -13438,7 +13438,7 @@
         <v>3.803151298241777e-06</v>
       </c>
       <c r="BC43" t="n">
-        <v>5.983822277777044e-06</v>
+        <v>5.983822277777043e-06</v>
       </c>
       <c r="BD43" t="n">
         <v>3.277402650168929e-06</v>
@@ -13504,10 +13504,10 @@
         <v>1.037492179449527e-06</v>
       </c>
       <c r="BY43" t="n">
-        <v>9.500859357554416e-07</v>
+        <v>9.500859357554415e-07</v>
       </c>
       <c r="BZ43" t="n">
-        <v>9.250402259280711e-07</v>
+        <v>9.250402259280712e-07</v>
       </c>
       <c r="CA43" t="n">
         <v>8.76372938176563e-07</v>
@@ -13537,7 +13537,7 @@
         <v>1.498156246801486e-06</v>
       </c>
       <c r="CJ43" t="n">
-        <v>1.447905242510759e-06</v>
+        <v>1.447905242510758e-06</v>
       </c>
       <c r="CK43" t="n">
         <v>1.306814898018517e-06</v>
@@ -13552,7 +13552,7 @@
         <v>4.778695239119519e-07</v>
       </c>
       <c r="CO43" t="n">
-        <v>4.441386749312785e-07</v>
+        <v>4.441386749312784e-07</v>
       </c>
       <c r="CP43" t="n">
         <v>5.033294736253894e-07</v>
@@ -13567,25 +13567,25 @@
         <v>4.088664166134908e-07</v>
       </c>
       <c r="CT43" t="n">
-        <v>4.769431901891249e-07</v>
+        <v>4.76943190189125e-07</v>
       </c>
       <c r="CU43" t="n">
-        <v>4.553712668702312e-07</v>
+        <v>4.553712668702313e-07</v>
       </c>
       <c r="CV43" t="n">
         <v>3.777401311417769e-07</v>
       </c>
       <c r="CW43" t="n">
-        <v>3.997132952906446e-07</v>
+        <v>3.997132952906447e-07</v>
       </c>
       <c r="CX43" t="n">
         <v>3.978569201785158e-07</v>
       </c>
       <c r="CY43" t="n">
-        <v>4.191645894795528e-07</v>
+        <v>4.191645894795529e-07</v>
       </c>
       <c r="CZ43" t="n">
-        <v>4.204243535862252e-07</v>
+        <v>4.204243535862253e-07</v>
       </c>
       <c r="DA43" t="n">
         <v>3.933382397583578e-07</v>
@@ -13600,16 +13600,16 @@
         <v>1.103742385882716e-06</v>
       </c>
       <c r="DE43" t="n">
-        <v>9.493171723785981e-07</v>
+        <v>9.49317172378598e-07</v>
       </c>
       <c r="DF43" t="n">
         <v>4.283014776267663e-07</v>
       </c>
       <c r="DG43" t="n">
-        <v>4.24461673738153e-07</v>
+        <v>4.244616737381531e-07</v>
       </c>
       <c r="DH43" t="n">
-        <v>3.852672485846851e-07</v>
+        <v>3.85267248584685e-07</v>
       </c>
       <c r="DI43" t="n">
         <v>3.953909844981572e-07</v>
@@ -13633,7 +13633,7 @@
         <v>4.136955484961763e-07</v>
       </c>
       <c r="DP43" t="n">
-        <v>4.213863032697697e-07</v>
+        <v>4.213863032697696e-07</v>
       </c>
     </row>
     <row r="44">
@@ -13661,19 +13661,19 @@
         <v>8.563742572920001e-07</v>
       </c>
       <c r="H44" t="n">
-        <v>7.449025653120002e-07</v>
+        <v>7.449025653120001e-07</v>
       </c>
       <c r="I44" t="n">
-        <v>7.78252690495e-07</v>
+        <v>7.782526904950001e-07</v>
       </c>
       <c r="J44" t="n">
-        <v>9.345764390590001e-07</v>
+        <v>9.34576439059e-07</v>
       </c>
       <c r="K44" t="n">
-        <v>8.434846144460001e-07</v>
+        <v>8.434846144459998e-07</v>
       </c>
       <c r="L44" t="n">
-        <v>8.817635708130001e-07</v>
+        <v>8.81763570813e-07</v>
       </c>
       <c r="M44" t="n">
         <v>1.273164906155e-06</v>
@@ -13688,7 +13688,7 @@
         <v>1.514119399806e-06</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.09807433796e-07</v>
+        <v>6.098074337959999e-07</v>
       </c>
       <c r="R44" t="n">
         <v>1.543995241911e-06</v>
@@ -13709,10 +13709,10 @@
         <v>1.417060122315e-06</v>
       </c>
       <c r="X44" t="n">
-        <v>7.94214228791e-07</v>
+        <v>7.942142287909999e-07</v>
       </c>
       <c r="Y44" t="n">
-        <v>8.681844018569999e-07</v>
+        <v>8.681844018570002e-07</v>
       </c>
       <c r="Z44" t="n">
         <v>5.58879329904e-07</v>
@@ -13745,7 +13745,7 @@
         <v>1.225609693245e-06</v>
       </c>
       <c r="AJ44" t="n">
-        <v>8.354525352670001e-07</v>
+        <v>8.35452535267e-07</v>
       </c>
       <c r="AK44" t="n">
         <v>1.225981368802e-06</v>
@@ -13769,28 +13769,28 @@
         <v>9.58711714692e-07</v>
       </c>
       <c r="AR44" t="n">
-        <v>8.273206930549999e-07</v>
+        <v>8.273206930550002e-07</v>
       </c>
       <c r="AS44" t="n">
         <v>5.60213276749e-07</v>
       </c>
       <c r="AT44" t="n">
-        <v>5.721140868590001e-07</v>
+        <v>5.72114086859e-07</v>
       </c>
       <c r="AU44" t="n">
-        <v>5.87657569629e-07</v>
+        <v>5.876575696289999e-07</v>
       </c>
       <c r="AV44" t="n">
-        <v>6.848666666666666e-07</v>
+        <v>6.848666666666665e-07</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.844998791466065e-06</v>
+        <v>2.844998791466066e-06</v>
       </c>
       <c r="AX44" t="n">
-        <v>3.238349699934597e-06</v>
+        <v>3.238349699934596e-06</v>
       </c>
       <c r="AY44" t="n">
-        <v>2.999832958646122e-06</v>
+        <v>2.999832958646123e-06</v>
       </c>
       <c r="AZ44" t="n">
         <v>3.47925991302484e-06</v>
@@ -13799,7 +13799,7 @@
         <v>2.269842411551343e-06</v>
       </c>
       <c r="BB44" t="n">
-        <v>3.298424832014455e-06</v>
+        <v>3.298424832014456e-06</v>
       </c>
       <c r="BC44" t="n">
         <v>4.162950583170405e-06</v>
@@ -13832,7 +13832,7 @@
         <v>4.763734923613418e-07</v>
       </c>
       <c r="BM44" t="n">
-        <v>2.720649865327134e-06</v>
+        <v>2.720649865327133e-06</v>
       </c>
       <c r="BN44" t="n">
         <v>2.093600067253404e-06</v>
@@ -13859,16 +13859,16 @@
         <v>3.560797853165003e-06</v>
       </c>
       <c r="BV44" t="n">
-        <v>3.048208144374993e-06</v>
+        <v>3.048208144374992e-06</v>
       </c>
       <c r="BW44" t="n">
         <v>2.282879651159677e-06</v>
       </c>
       <c r="BX44" t="n">
-        <v>2.303899681316164e-06</v>
+        <v>2.303899681316165e-06</v>
       </c>
       <c r="BY44" t="n">
-        <v>2.079784171227332e-06</v>
+        <v>2.079784171227331e-06</v>
       </c>
       <c r="BZ44" t="n">
         <v>2.592673749587349e-06</v>
@@ -13889,7 +13889,7 @@
         <v>1.197507926758482e-06</v>
       </c>
       <c r="CF44" t="n">
-        <v>1.807899057132292e-06</v>
+        <v>1.807899057132291e-06</v>
       </c>
       <c r="CG44" t="n">
         <v>2.153282521653462e-06</v>
@@ -13910,19 +13910,19 @@
         <v>1.573310360490169e-06</v>
       </c>
       <c r="CM44" t="n">
-        <v>4.668438579194348e-07</v>
+        <v>4.668438579194347e-07</v>
       </c>
       <c r="CN44" t="n">
         <v>3.978235892689559e-07</v>
       </c>
       <c r="CO44" t="n">
-        <v>7.122128570417619e-07</v>
+        <v>7.12212857041762e-07</v>
       </c>
       <c r="CP44" t="n">
         <v>4.540004440952185e-07</v>
       </c>
       <c r="CQ44" t="n">
-        <v>4.244758568207435e-07</v>
+        <v>4.244758568207434e-07</v>
       </c>
       <c r="CR44" t="n">
         <v>4.16453843879636e-07</v>
@@ -13958,10 +13958,10 @@
         <v>4.109568573931989e-07</v>
       </c>
       <c r="DC44" t="n">
-        <v>5.308095272734793e-07</v>
+        <v>5.308095272734792e-07</v>
       </c>
       <c r="DD44" t="n">
-        <v>4.284279235722335e-07</v>
+        <v>4.284279235722336e-07</v>
       </c>
       <c r="DE44" t="n">
         <v>3.560971539608313e-07</v>
@@ -13979,7 +13979,7 @@
         <v>3.391776362159824e-07</v>
       </c>
       <c r="DJ44" t="n">
-        <v>3.168016409551447e-07</v>
+        <v>3.168016409551448e-07</v>
       </c>
       <c r="DK44" t="n">
         <v>3.678544652465259e-07</v>
@@ -13991,7 +13991,7 @@
         <v>2.363373450937932e-07</v>
       </c>
       <c r="DN44" t="n">
-        <v>3.659316311770611e-07</v>
+        <v>3.659316311770612e-07</v>
       </c>
       <c r="DO44" t="n">
         <v>9.253761387004203e-07</v>
@@ -14553,7 +14553,7 @@
         <v>8.938502009840001e-07</v>
       </c>
       <c r="J48" t="n">
-        <v>9.017025821790001e-07</v>
+        <v>9.01702582179e-07</v>
       </c>
       <c r="K48" t="n">
         <v>8.26549630342e-07</v>
@@ -14616,7 +14616,7 @@
         <v>4.07878146699e-06</v>
       </c>
       <c r="AE48" t="n">
-        <v>4.795156923840001e-06</v>
+        <v>4.79515692384e-06</v>
       </c>
       <c r="AF48" t="n">
         <v>4.058937860850001e-06</v>
@@ -14640,7 +14640,7 @@
         <v>1.89716712874e-06</v>
       </c>
       <c r="AM48" t="n">
-        <v>6.66421427814e-06</v>
+        <v>6.664214278139999e-06</v>
       </c>
       <c r="AN48" t="n">
         <v>1.92270021804e-06</v>
@@ -14661,7 +14661,7 @@
         <v>7.31778295896e-07</v>
       </c>
       <c r="AT48" t="n">
-        <v>7.411562351430001e-07</v>
+        <v>7.41156235143e-07</v>
       </c>
       <c r="AU48" t="n">
         <v>9.758767383900002e-07</v>
@@ -14676,7 +14676,7 @@
         <v>1.91948388068627e-06</v>
       </c>
       <c r="AY48" t="n">
-        <v>3.552318078852732e-06</v>
+        <v>3.552318078852733e-06</v>
       </c>
       <c r="AZ48" t="n">
         <v>3.712364186143334e-06</v>
@@ -14757,13 +14757,13 @@
         <v>1.805607300062963e-06</v>
       </c>
       <c r="BZ48" t="n">
-        <v>2.797485929441069e-06</v>
+        <v>2.79748592944107e-06</v>
       </c>
       <c r="CA48" t="n">
         <v>3.398958503494308e-06</v>
       </c>
       <c r="CB48" t="n">
-        <v>2.960406493650038e-06</v>
+        <v>2.960406493650039e-06</v>
       </c>
       <c r="CC48" t="n">
         <v>4.877169834042058e-06</v>
@@ -14775,7 +14775,7 @@
         <v>5.819985015740587e-06</v>
       </c>
       <c r="CF48" t="n">
-        <v>3.593457050900213e-06</v>
+        <v>3.593457050900212e-06</v>
       </c>
       <c r="CG48" t="n">
         <v>3.610726878748169e-06</v>
@@ -14808,13 +14808,13 @@
         <v>7.010766960184394e-07</v>
       </c>
       <c r="CQ48" t="n">
-        <v>6.136752710314709e-07</v>
+        <v>6.13675271031471e-07</v>
       </c>
       <c r="CR48" t="n">
         <v>5.807071610233161e-07</v>
       </c>
       <c r="CS48" t="n">
-        <v>6.121020676736057e-07</v>
+        <v>6.121020676736058e-07</v>
       </c>
       <c r="CT48" t="n">
         <v>6.929375725113689e-07</v>
@@ -14841,7 +14841,7 @@
         <v>6.377679911868758e-07</v>
       </c>
       <c r="DB48" t="n">
-        <v>4.71360724592858e-07</v>
+        <v>4.713607245928579e-07</v>
       </c>
       <c r="DC48" t="n">
         <v>6.465168920525147e-07</v>
@@ -14868,7 +14868,7 @@
         <v>7.706888037228985e-07</v>
       </c>
       <c r="DK48" t="n">
-        <v>8.335689490943276e-07</v>
+        <v>8.335689490943275e-07</v>
       </c>
       <c r="DL48" t="n">
         <v>7.523803090122475e-07</v>
@@ -14877,7 +14877,7 @@
         <v>7.823792394576019e-07</v>
       </c>
       <c r="DN48" t="n">
-        <v>9.264030100020706e-07</v>
+        <v>9.264030100020707e-07</v>
       </c>
       <c r="DO48" t="n">
         <v>7.095945972531834e-07</v>
@@ -15651,10 +15651,10 @@
         <v>0.000515885334817123</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003307900569942437</v>
+        <v>0.0003307900569942438</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0004408599331625325</v>
+        <v>0.0004408599331625326</v>
       </c>
       <c r="F54" t="n">
         <v>0.000140902108719196</v>
@@ -15672,10 +15672,10 @@
         <v>8.293966947341201e-05</v>
       </c>
       <c r="K54" t="n">
-        <v>8.327862934156099e-05</v>
+        <v>8.3278629341561e-05</v>
       </c>
       <c r="L54" t="n">
-        <v>8.656312844023098e-05</v>
+        <v>8.656312844023099e-05</v>
       </c>
       <c r="M54" t="n">
         <v>0.000168851553251448</v>
@@ -15693,22 +15693,22 @@
         <v>0.00012907891924807</v>
       </c>
       <c r="R54" t="n">
-        <v>0.0002545628961365729</v>
+        <v>0.000254562896136573</v>
       </c>
       <c r="S54" t="n">
         <v>0.000252772489320358</v>
       </c>
       <c r="T54" t="n">
-        <v>0.0003123861398319071</v>
+        <v>0.000312386139831907</v>
       </c>
       <c r="U54" t="n">
-        <v>0.0002958668963129081</v>
+        <v>0.000295866896312908</v>
       </c>
       <c r="V54" t="n">
         <v>0.000276089148588133</v>
       </c>
       <c r="W54" t="n">
-        <v>0.000233754460725607</v>
+        <v>0.0002337544607256071</v>
       </c>
       <c r="X54" t="n">
         <v>0.000175216221285004</v>
@@ -15717,7 +15717,7 @@
         <v>0.000233197437768465</v>
       </c>
       <c r="Z54" t="n">
-        <v>7.076641610926601e-05</v>
+        <v>7.0766416109266e-05</v>
       </c>
       <c r="AA54" t="n">
         <v>0.000117428810539258</v>
@@ -15774,10 +15774,10 @@
         <v>0.000179283497584328</v>
       </c>
       <c r="AS54" t="n">
-        <v>8.120384120442501e-05</v>
+        <v>8.120384120442498e-05</v>
       </c>
       <c r="AT54" t="n">
-        <v>9.077416008383499e-05</v>
+        <v>9.0774160083835e-05</v>
       </c>
       <c r="AU54" t="n">
         <v>0.000117136149649273</v>
@@ -15789,19 +15789,19 @@
         <v>0.000240649404328375</v>
       </c>
       <c r="AX54" t="n">
-        <v>0.0002429590163998539</v>
+        <v>0.000242959016399854</v>
       </c>
       <c r="AY54" t="n">
         <v>0.0003245908282213207</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0.0003211560737995639</v>
+        <v>0.0003211560737995638</v>
       </c>
       <c r="BA54" t="n">
         <v>0.0004770331679161811</v>
       </c>
       <c r="BB54" t="n">
-        <v>0.0003473150048107284</v>
+        <v>0.0003473150048107285</v>
       </c>
       <c r="BC54" t="n">
         <v>0.0005015693095362459</v>
@@ -15816,10 +15816,10 @@
         <v>0.0002658898361476365</v>
       </c>
       <c r="BG54" t="n">
-        <v>0.0002602720531031089</v>
+        <v>0.000260272053103109</v>
       </c>
       <c r="BH54" t="n">
-        <v>0.0002632887824461379</v>
+        <v>0.000263288782446138</v>
       </c>
       <c r="BI54" t="n">
         <v>0.0002227113274684656</v>
@@ -15837,7 +15837,7 @@
         <v>0.0002323275333783959</v>
       </c>
       <c r="BN54" t="n">
-        <v>0.0002280502256120225</v>
+        <v>0.0002280502256120226</v>
       </c>
       <c r="BO54" t="n">
         <v>0.0001988387227540186</v>
@@ -15852,7 +15852,7 @@
         <v>0.0002795085552511624</v>
       </c>
       <c r="BS54" t="n">
-        <v>0.0001584466283220529</v>
+        <v>0.0001584466283220528</v>
       </c>
       <c r="BT54" t="n">
         <v>8.59136206728588e-05</v>
@@ -15867,10 +15867,10 @@
         <v>0.0001088041157627451</v>
       </c>
       <c r="BX54" t="n">
-        <v>0.000100301203158066</v>
+        <v>0.0001003012031580659</v>
       </c>
       <c r="BY54" t="n">
-        <v>8.895662473699249e-05</v>
+        <v>8.895662473699246e-05</v>
       </c>
       <c r="BZ54" t="n">
         <v>0.0001138909618399733</v>
@@ -15888,7 +15888,7 @@
         <v>0.0002571076266247518</v>
       </c>
       <c r="CE54" t="n">
-        <v>0.0002640348066557464</v>
+        <v>0.0002640348066557465</v>
       </c>
       <c r="CF54" t="n">
         <v>0.000220537726473756</v>
@@ -15897,7 +15897,7 @@
         <v>0.0002023960354386911</v>
       </c>
       <c r="CH54" t="n">
-        <v>0.0001077698193660481</v>
+        <v>0.000107769819366048</v>
       </c>
       <c r="CI54" t="n">
         <v>0.0001121537614509555</v>
@@ -15942,7 +15942,7 @@
         <v>0.0002878872733129364</v>
       </c>
       <c r="CW54" t="n">
-        <v>0.0002972577968400163</v>
+        <v>0.0002972577968400164</v>
       </c>
       <c r="CX54" t="n">
         <v>0.0002880156805705588</v>
@@ -15951,16 +15951,16 @@
         <v>0.0002966482046324392</v>
       </c>
       <c r="CZ54" t="n">
-        <v>0.0002953083532076737</v>
+        <v>0.0002953083532076738</v>
       </c>
       <c r="DA54" t="n">
         <v>0.0003013361102666489</v>
       </c>
       <c r="DB54" t="n">
-        <v>0.0002899311207595873</v>
+        <v>0.0002899311207595874</v>
       </c>
       <c r="DC54" t="n">
-        <v>0.0002935139055580396</v>
+        <v>0.0002935139055580397</v>
       </c>
       <c r="DD54" t="n">
         <v>0.0002931775715733849</v>
@@ -15978,19 +15978,19 @@
         <v>0.0003045291959627506</v>
       </c>
       <c r="DI54" t="n">
-        <v>0.0003139541131491072</v>
+        <v>0.0003139541131491073</v>
       </c>
       <c r="DJ54" t="n">
-        <v>0.0003242014808437753</v>
+        <v>0.0003242014808437754</v>
       </c>
       <c r="DK54" t="n">
         <v>0.0003034643863215369</v>
       </c>
       <c r="DL54" t="n">
-        <v>0.000301247821719607</v>
+        <v>0.0003012478217196069</v>
       </c>
       <c r="DM54" t="n">
-        <v>0.0003005509783103488</v>
+        <v>0.0003005509783103489</v>
       </c>
       <c r="DN54" t="n">
         <v>0.0002883706791967664</v>
@@ -15999,7 +15999,7 @@
         <v>0.0002934493354598253</v>
       </c>
       <c r="DP54" t="n">
-        <v>0.0002964088463657096</v>
+        <v>0.0002964088463657097</v>
       </c>
     </row>
     <row r="55">
@@ -16009,7 +16009,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>8.370334948974562e-06</v>
+        <v>8.37033494897456e-06</v>
       </c>
       <c r="C55" t="n">
         <v>9.472104212038372e-06</v>
@@ -16030,7 +16030,7 @@
         <v>5.644894063427e-06</v>
       </c>
       <c r="I55" t="n">
-        <v>5.828014403199e-06</v>
+        <v>5.828014403199001e-06</v>
       </c>
       <c r="J55" t="n">
         <v>5.887135652105999e-06</v>
@@ -16042,10 +16042,10 @@
         <v>6.014676826820001e-06</v>
       </c>
       <c r="M55" t="n">
-        <v>7.334028862789999e-06</v>
+        <v>7.334028862790001e-06</v>
       </c>
       <c r="N55" t="n">
-        <v>7.070972685420001e-06</v>
+        <v>7.07097268542e-06</v>
       </c>
       <c r="O55" t="n">
         <v>7.29675946755e-06</v>
@@ -16066,7 +16066,7 @@
         <v>8.367763047570001e-06</v>
       </c>
       <c r="U55" t="n">
-        <v>9.25510768312e-06</v>
+        <v>9.255107683120001e-06</v>
       </c>
       <c r="V55" t="n">
         <v>1.015922528457e-05</v>
@@ -16084,19 +16084,19 @@
         <v>4.213426341117e-06</v>
       </c>
       <c r="AA55" t="n">
-        <v>6.98274094302e-06</v>
+        <v>6.982740943020001e-06</v>
       </c>
       <c r="AB55" t="n">
         <v>4.10400489123e-06</v>
       </c>
       <c r="AC55" t="n">
-        <v>7.300385063530001e-06</v>
+        <v>7.30038506353e-06</v>
       </c>
       <c r="AD55" t="n">
         <v>6.7231495801e-06</v>
       </c>
       <c r="AE55" t="n">
-        <v>7.89436142823e-06</v>
+        <v>7.894361428229999e-06</v>
       </c>
       <c r="AF55" t="n">
         <v>7.27482782976e-06</v>
@@ -16108,25 +16108,25 @@
         <v>7.42193083941e-06</v>
       </c>
       <c r="AI55" t="n">
-        <v>7.996735338889998e-06</v>
+        <v>7.996735338890001e-06</v>
       </c>
       <c r="AJ55" t="n">
         <v>6.13367583555e-06</v>
       </c>
       <c r="AK55" t="n">
-        <v>7.49437458636e-06</v>
+        <v>7.494374586360001e-06</v>
       </c>
       <c r="AL55" t="n">
-        <v>6.69940409574e-06</v>
+        <v>6.699404095739998e-06</v>
       </c>
       <c r="AM55" t="n">
-        <v>6.665920496359999e-06</v>
+        <v>6.665920496360001e-06</v>
       </c>
       <c r="AN55" t="n">
         <v>8.12947259612e-06</v>
       </c>
       <c r="AO55" t="n">
-        <v>8.933813097649998e-06</v>
+        <v>8.933813097650002e-06</v>
       </c>
       <c r="AP55" t="n">
         <v>8.977555525706e-06</v>
@@ -16135,7 +16135,7 @@
         <v>6.98622963271e-06</v>
       </c>
       <c r="AR55" t="n">
-        <v>6.437938025120001e-06</v>
+        <v>6.43793802512e-06</v>
       </c>
       <c r="AS55" t="n">
         <v>4.418022398885e-06</v>
@@ -16144,7 +16144,7 @@
         <v>4.572713602386e-06</v>
       </c>
       <c r="AU55" t="n">
-        <v>5.450156439617999e-06</v>
+        <v>5.450156439618e-06</v>
       </c>
       <c r="AV55" t="n">
         <v>1.39649e-05</v>
@@ -16171,7 +16171,7 @@
         <v>2.541533408864252e-05</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.699732864298232e-05</v>
+        <v>1.699732864298233e-05</v>
       </c>
       <c r="BE55" t="n">
         <v>1.23502256447712e-05</v>
@@ -16192,13 +16192,13 @@
         <v>1.501527887778147e-05</v>
       </c>
       <c r="BK55" t="n">
-        <v>5.106621016589174e-06</v>
+        <v>5.106621016589173e-06</v>
       </c>
       <c r="BL55" t="n">
         <v>7.956760738641646e-06</v>
       </c>
       <c r="BM55" t="n">
-        <v>4.832644064174692e-05</v>
+        <v>4.832644064174693e-05</v>
       </c>
       <c r="BN55" t="n">
         <v>4.607163946708734e-05</v>
@@ -16207,7 +16207,7 @@
         <v>4.37193093847891e-05</v>
       </c>
       <c r="BP55" t="n">
-        <v>2.332135252261706e-05</v>
+        <v>2.332135252261707e-05</v>
       </c>
       <c r="BQ55" t="n">
         <v>1.520885052203587e-05</v>
@@ -16273,7 +16273,7 @@
         <v>1.133025772298763e-05</v>
       </c>
       <c r="CL55" t="n">
-        <v>9.69922508443259e-06</v>
+        <v>9.699225084432588e-06</v>
       </c>
       <c r="CM55" t="n">
         <v>2.481315228216065e-06</v>
@@ -16285,7 +16285,7 @@
         <v>2.414525007204356e-06</v>
       </c>
       <c r="CP55" t="n">
-        <v>2.510443925889119e-06</v>
+        <v>2.51044392588912e-06</v>
       </c>
       <c r="CQ55" t="n">
         <v>2.330397383965461e-06</v>
@@ -16294,7 +16294,7 @@
         <v>2.372803471497839e-06</v>
       </c>
       <c r="CS55" t="n">
-        <v>2.476061215805098e-06</v>
+        <v>2.476061215805099e-06</v>
       </c>
       <c r="CT55" t="n">
         <v>2.240109133890824e-06</v>
@@ -16303,10 +16303,10 @@
         <v>2.420451115529976e-06</v>
       </c>
       <c r="CV55" t="n">
-        <v>2.276325901287971e-06</v>
+        <v>2.276325901287972e-06</v>
       </c>
       <c r="CW55" t="n">
-        <v>2.297827499830417e-06</v>
+        <v>2.297827499830416e-06</v>
       </c>
       <c r="CX55" t="n">
         <v>2.392049946828181e-06</v>
@@ -16324,13 +16324,13 @@
         <v>2.490101586980844e-06</v>
       </c>
       <c r="DC55" t="n">
-        <v>2.464641608923581e-06</v>
+        <v>2.464641608923582e-06</v>
       </c>
       <c r="DD55" t="n">
         <v>2.597741717479367e-06</v>
       </c>
       <c r="DE55" t="n">
-        <v>2.455266196565921e-06</v>
+        <v>2.45526619656592e-06</v>
       </c>
       <c r="DF55" t="n">
         <v>2.49154910627353e-06</v>
@@ -16360,7 +16360,7 @@
         <v>2.257649001698841e-06</v>
       </c>
       <c r="DO55" t="n">
-        <v>2.2561630182314e-06</v>
+        <v>2.256163018231401e-06</v>
       </c>
       <c r="DP55" t="n">
         <v>2.326298886188273e-06</v>
@@ -16388,10 +16388,10 @@
         <v>0.000106581784294613</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0001677574470930019</v>
+        <v>0.000167757447093002</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0001419080703416919</v>
+        <v>0.000141908070341692</v>
       </c>
       <c r="I56" t="n">
         <v>0.000152151620467302</v>
@@ -16412,19 +16412,19 @@
         <v>0.000214588914074697</v>
       </c>
       <c r="O56" t="n">
-        <v>0.0001928777418990781</v>
+        <v>0.000192877741899078</v>
       </c>
       <c r="P56" t="n">
         <v>0.000201940110489028</v>
       </c>
       <c r="Q56" t="n">
-        <v>9.440182293646301e-05</v>
+        <v>9.4401822936463e-05</v>
       </c>
       <c r="R56" t="n">
         <v>0.000229335487891209</v>
       </c>
       <c r="S56" t="n">
-        <v>0.000249970770223323</v>
+        <v>0.0002499707702233231</v>
       </c>
       <c r="T56" t="n">
         <v>0.000226284991898024</v>
@@ -16436,7 +16436,7 @@
         <v>0.000262094095250253</v>
       </c>
       <c r="W56" t="n">
-        <v>0.0002642275592367051</v>
+        <v>0.000264227559236705</v>
       </c>
       <c r="X56" t="n">
         <v>0.000137379671135246</v>
@@ -16451,7 +16451,7 @@
         <v>0.000207687346991633</v>
       </c>
       <c r="AB56" t="n">
-        <v>9.873062316118202e-05</v>
+        <v>9.8730623161182e-05</v>
       </c>
       <c r="AC56" t="n">
         <v>0.000208810595043546</v>
@@ -16460,7 +16460,7 @@
         <v>0.000214774019433758</v>
       </c>
       <c r="AE56" t="n">
-        <v>0.0002675931268734419</v>
+        <v>0.000267593126873442</v>
       </c>
       <c r="AF56" t="n">
         <v>0.000233068116488392</v>
@@ -16472,13 +16472,13 @@
         <v>0.000223804180478638</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.0002536559719695011</v>
+        <v>0.000253655971969501</v>
       </c>
       <c r="AJ56" t="n">
         <v>0.000181200289144212</v>
       </c>
       <c r="AK56" t="n">
-        <v>0.000219416615028068</v>
+        <v>0.0002194166150280681</v>
       </c>
       <c r="AL56" t="n">
         <v>0.000156174694426958</v>
@@ -16493,7 +16493,7 @@
         <v>0.000248747438228483</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.0002218990911244991</v>
+        <v>0.000221899091124499</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.000149962396370374</v>
@@ -16514,7 +16514,7 @@
         <v>6.252766666666666e-05</v>
       </c>
       <c r="AW56" t="n">
-        <v>5.8943292567826e-05</v>
+        <v>5.894329256782601e-05</v>
       </c>
       <c r="AX56" t="n">
         <v>5.719651989514783e-05</v>
@@ -16529,13 +16529,13 @@
         <v>2.380315163738701e-05</v>
       </c>
       <c r="BB56" t="n">
-        <v>9.939429550818977e-06</v>
+        <v>9.939429550818979e-06</v>
       </c>
       <c r="BC56" t="n">
         <v>1.430227453451898e-05</v>
       </c>
       <c r="BD56" t="n">
-        <v>9.831451816116536e-06</v>
+        <v>9.831451816116538e-06</v>
       </c>
       <c r="BE56" t="n">
         <v>1.41155709658053e-05</v>
@@ -16583,10 +16583,10 @@
         <v>0.0002089367493117272</v>
       </c>
       <c r="BT56" t="n">
-        <v>0.0002998740530377892</v>
+        <v>0.0002998740530377891</v>
       </c>
       <c r="BU56" t="n">
-        <v>6.80177315902709e-05</v>
+        <v>6.801773159027093e-05</v>
       </c>
       <c r="BV56" t="n">
         <v>8.382408593230526e-05</v>
@@ -16595,16 +16595,16 @@
         <v>0.0002518635407476899</v>
       </c>
       <c r="BX56" t="n">
-        <v>0.0002728483846868518</v>
+        <v>0.0002728483846868517</v>
       </c>
       <c r="BY56" t="n">
         <v>0.0004061609782820147</v>
       </c>
       <c r="BZ56" t="n">
-        <v>0.0003321944326705517</v>
+        <v>0.0003321944326705518</v>
       </c>
       <c r="CA56" t="n">
-        <v>0.0002896018560624719</v>
+        <v>0.0002896018560624718</v>
       </c>
       <c r="CB56" t="n">
         <v>0.0001212635841975925</v>
@@ -16619,13 +16619,13 @@
         <v>4.162564880833684e-05</v>
       </c>
       <c r="CF56" t="n">
-        <v>5.947664014193207e-05</v>
+        <v>5.947664014193208e-05</v>
       </c>
       <c r="CG56" t="n">
         <v>6.853808847320387e-05</v>
       </c>
       <c r="CH56" t="n">
-        <v>5.321869670610356e-05</v>
+        <v>5.321869670610355e-05</v>
       </c>
       <c r="CI56" t="n">
         <v>6.139840348185068e-05</v>
@@ -16640,49 +16640,49 @@
         <v>5.154771799867487e-05</v>
       </c>
       <c r="CM56" t="n">
-        <v>8.845484082018466e-06</v>
+        <v>8.845484082018464e-06</v>
       </c>
       <c r="CN56" t="n">
-        <v>9.017807541409163e-06</v>
+        <v>9.017807541409165e-06</v>
       </c>
       <c r="CO56" t="n">
-        <v>9.778791192269459e-06</v>
+        <v>9.778791192269458e-06</v>
       </c>
       <c r="CP56" t="n">
-        <v>9.610345324850096e-06</v>
+        <v>9.610345324850095e-06</v>
       </c>
       <c r="CQ56" t="n">
-        <v>9.007860905876556e-06</v>
+        <v>9.007860905876553e-06</v>
       </c>
       <c r="CR56" t="n">
-        <v>9.50962044520731e-06</v>
+        <v>9.509620445207311e-06</v>
       </c>
       <c r="CS56" t="n">
-        <v>8.37360614221729e-06</v>
+        <v>8.373606142217288e-06</v>
       </c>
       <c r="CT56" t="n">
         <v>9.389709094351488e-06</v>
       </c>
       <c r="CU56" t="n">
-        <v>9.317692939486619e-06</v>
+        <v>9.317692939486621e-06</v>
       </c>
       <c r="CV56" t="n">
-        <v>8.477054514743167e-06</v>
+        <v>8.477054514743169e-06</v>
       </c>
       <c r="CW56" t="n">
-        <v>9.233233334044428e-06</v>
+        <v>9.233233334044429e-06</v>
       </c>
       <c r="CX56" t="n">
-        <v>8.645501837801665e-06</v>
+        <v>8.645501837801669e-06</v>
       </c>
       <c r="CY56" t="n">
-        <v>9.018401192032194e-06</v>
+        <v>9.018401192032192e-06</v>
       </c>
       <c r="CZ56" t="n">
         <v>1.018692353489421e-05</v>
       </c>
       <c r="DA56" t="n">
-        <v>8.877610244495405e-06</v>
+        <v>8.877610244495401e-06</v>
       </c>
       <c r="DB56" t="n">
         <v>1.071092875820876e-05</v>
@@ -16697,37 +16697,37 @@
         <v>9.33748811060264e-06</v>
       </c>
       <c r="DF56" t="n">
-        <v>8.737482239465382e-06</v>
+        <v>8.73748223946538e-06</v>
       </c>
       <c r="DG56" t="n">
         <v>8.25561613609052e-06</v>
       </c>
       <c r="DH56" t="n">
-        <v>8.758141591019113e-06</v>
+        <v>8.75814159101911e-06</v>
       </c>
       <c r="DI56" t="n">
-        <v>8.581070237578802e-06</v>
+        <v>8.581070237578804e-06</v>
       </c>
       <c r="DJ56" t="n">
         <v>9.119522792561002e-06</v>
       </c>
       <c r="DK56" t="n">
-        <v>9.335515246927961e-06</v>
+        <v>9.33551524692796e-06</v>
       </c>
       <c r="DL56" t="n">
-        <v>9.164085460532355e-06</v>
+        <v>9.164085460532359e-06</v>
       </c>
       <c r="DM56" t="n">
         <v>8.725669129498434e-06</v>
       </c>
       <c r="DN56" t="n">
-        <v>8.69578167318435e-06</v>
+        <v>8.695781673184348e-06</v>
       </c>
       <c r="DO56" t="n">
-        <v>9.492231304769744e-06</v>
+        <v>9.492231304769741e-06</v>
       </c>
       <c r="DP56" t="n">
-        <v>8.834219036474206e-06</v>
+        <v>8.834219036474204e-06</v>
       </c>
     </row>
     <row r="57">
@@ -17158,7 +17158,7 @@
         <v>4.107341518829104e-06</v>
       </c>
       <c r="AY59" t="n">
-        <v>2.756000067460932e-06</v>
+        <v>2.756000067460933e-06</v>
       </c>
       <c r="AZ59" t="n">
         <v>4.069487639273606e-06</v>
@@ -17375,16 +17375,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7.01037669973003e-05</v>
+        <v>7.010376699730028e-05</v>
       </c>
       <c r="C60" t="n">
         <v>6.774996669537432e-05</v>
       </c>
       <c r="D60" t="n">
-        <v>5.509279346752725e-05</v>
+        <v>5.509279346752724e-05</v>
       </c>
       <c r="E60" t="n">
-        <v>6.560731385399422e-05</v>
+        <v>6.560731385399421e-05</v>
       </c>
       <c r="F60" t="n">
         <v>2.702012986194e-05</v>
@@ -17399,16 +17399,16 @@
         <v>3.865522327049e-05</v>
       </c>
       <c r="J60" t="n">
-        <v>4.105702136975001e-05</v>
+        <v>4.105702136975e-05</v>
       </c>
       <c r="K60" t="n">
-        <v>3.929136310721999e-05</v>
+        <v>3.929136310722e-05</v>
       </c>
       <c r="L60" t="n">
-        <v>4.292344633322999e-05</v>
+        <v>4.292344633323e-05</v>
       </c>
       <c r="M60" t="n">
-        <v>5.188648681400001e-05</v>
+        <v>5.1886486814e-05</v>
       </c>
       <c r="N60" t="n">
         <v>5.114627408657e-05</v>
@@ -17426,13 +17426,13 @@
         <v>6.06275439476e-05</v>
       </c>
       <c r="S60" t="n">
-        <v>6.365616050375e-05</v>
+        <v>6.365616050375001e-05</v>
       </c>
       <c r="T60" t="n">
-        <v>3.630055765051999e-05</v>
+        <v>3.630055765052e-05</v>
       </c>
       <c r="U60" t="n">
-        <v>4.751552513585999e-05</v>
+        <v>4.751552513586e-05</v>
       </c>
       <c r="V60" t="n">
         <v>5.369898206688e-05</v>
@@ -17447,7 +17447,7 @@
         <v>3.453815336831e-05</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.706268168828e-05</v>
+        <v>2.706268168827999e-05</v>
       </c>
       <c r="AA60" t="n">
         <v>4.369249021853e-05</v>
@@ -17456,13 +17456,13 @@
         <v>2.676691768243e-05</v>
       </c>
       <c r="AC60" t="n">
-        <v>4.145707315109999e-05</v>
+        <v>4.14570731511e-05</v>
       </c>
       <c r="AD60" t="n">
-        <v>2.551052018419001e-05</v>
+        <v>2.551052018419e-05</v>
       </c>
       <c r="AE60" t="n">
-        <v>3.422654584362e-05</v>
+        <v>3.422654584361999e-05</v>
       </c>
       <c r="AF60" t="n">
         <v>3.100999653174e-05</v>
@@ -17492,7 +17492,7 @@
         <v>5.687476456477001e-05</v>
       </c>
       <c r="AO60" t="n">
-        <v>5.713666807561e-05</v>
+        <v>5.713666807561001e-05</v>
       </c>
       <c r="AP60" t="n">
         <v>5.811326054782e-05</v>
@@ -17519,10 +17519,10 @@
         <v>4.109168912446714e-05</v>
       </c>
       <c r="AX60" t="n">
-        <v>4.089680204493371e-05</v>
+        <v>4.08968020449337e-05</v>
       </c>
       <c r="AY60" t="n">
-        <v>5.453550887059861e-05</v>
+        <v>5.45355088705986e-05</v>
       </c>
       <c r="AZ60" t="n">
         <v>5.391390363482284e-05</v>
@@ -17555,7 +17555,7 @@
         <v>2.578848967162072e-05</v>
       </c>
       <c r="BJ60" t="n">
-        <v>3.597799612515776e-05</v>
+        <v>3.597799612515775e-05</v>
       </c>
       <c r="BK60" t="n">
         <v>3.038930766854865e-05</v>
@@ -17567,13 +17567,13 @@
         <v>2.687897932638658e-05</v>
       </c>
       <c r="BN60" t="n">
-        <v>2.706881347628695e-05</v>
+        <v>2.706881347628694e-05</v>
       </c>
       <c r="BO60" t="n">
         <v>2.614178077980737e-05</v>
       </c>
       <c r="BP60" t="n">
-        <v>2.769913730355364e-05</v>
+        <v>2.769913730355363e-05</v>
       </c>
       <c r="BQ60" t="n">
         <v>2.700246948626703e-05</v>
@@ -17585,13 +17585,13 @@
         <v>2.408166500576601e-05</v>
       </c>
       <c r="BT60" t="n">
-        <v>2.497202219093881e-05</v>
+        <v>2.49720221909388e-05</v>
       </c>
       <c r="BU60" t="n">
         <v>3.925309430554146e-05</v>
       </c>
       <c r="BV60" t="n">
-        <v>3.47779609916767e-05</v>
+        <v>3.477796099167671e-05</v>
       </c>
       <c r="BW60" t="n">
         <v>2.387412911778771e-05</v>
@@ -17606,7 +17606,7 @@
         <v>2.870583095099681e-05</v>
       </c>
       <c r="CA60" t="n">
-        <v>2.581827185112504e-05</v>
+        <v>2.581827185112505e-05</v>
       </c>
       <c r="CB60" t="n">
         <v>3.265771155438884e-05</v>
@@ -17621,13 +17621,13 @@
         <v>3.750486969247778e-05</v>
       </c>
       <c r="CF60" t="n">
-        <v>4.675453118714764e-05</v>
+        <v>4.675453118714765e-05</v>
       </c>
       <c r="CG60" t="n">
         <v>4.945787308703234e-05</v>
       </c>
       <c r="CH60" t="n">
-        <v>3.367998973456261e-05</v>
+        <v>3.36799897345626e-05</v>
       </c>
       <c r="CI60" t="n">
         <v>3.600575487286535e-05</v>
@@ -17657,7 +17657,7 @@
         <v>2.253492525633144e-05</v>
       </c>
       <c r="CR60" t="n">
-        <v>2.358969996412207e-05</v>
+        <v>2.358969996412206e-05</v>
       </c>
       <c r="CS60" t="n">
         <v>1.765718249955251e-05</v>
@@ -17672,7 +17672,7 @@
         <v>1.803106925240807e-05</v>
       </c>
       <c r="CW60" t="n">
-        <v>1.824755528998115e-05</v>
+        <v>1.824755528998116e-05</v>
       </c>
       <c r="CX60" t="n">
         <v>1.875804757502099e-05</v>
@@ -17717,10 +17717,10 @@
         <v>1.894742600027705e-05</v>
       </c>
       <c r="DL60" t="n">
-        <v>1.93063428280944e-05</v>
+        <v>1.930634282809439e-05</v>
       </c>
       <c r="DM60" t="n">
-        <v>2.054762211117787e-05</v>
+        <v>2.054762211117788e-05</v>
       </c>
       <c r="DN60" t="n">
         <v>2.030585384573699e-05</v>
@@ -18151,13 +18151,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2.251379967911385e-05</v>
+        <v>2.251379967911386e-05</v>
       </c>
       <c r="C63" t="n">
         <v>3.474342679999257e-05</v>
       </c>
       <c r="D63" t="n">
-        <v>6.156162911021038e-05</v>
+        <v>6.156162911021037e-05</v>
       </c>
       <c r="E63" t="n">
         <v>2.728621960388695e-05</v>
@@ -18178,13 +18178,13 @@
         <v>3.190980342939e-05</v>
       </c>
       <c r="K63" t="n">
-        <v>3.450397359537001e-05</v>
+        <v>3.450397359537e-05</v>
       </c>
       <c r="L63" t="n">
         <v>4.127035601176e-05</v>
       </c>
       <c r="M63" t="n">
-        <v>3.425372954229e-05</v>
+        <v>3.425372954228999e-05</v>
       </c>
       <c r="N63" t="n">
         <v>3.533230121274001e-05</v>
@@ -18217,7 +18217,7 @@
         <v>8.32083439941e-05</v>
       </c>
       <c r="X63" t="n">
-        <v>3.476052556164e-05</v>
+        <v>3.476052556164001e-05</v>
       </c>
       <c r="Y63" t="n">
         <v>4.867911976225e-05</v>
@@ -18247,13 +18247,13 @@
         <v>6.930984295141002e-05</v>
       </c>
       <c r="AH63" t="n">
-        <v>5.710607380224e-05</v>
+        <v>5.710607380224001e-05</v>
       </c>
       <c r="AI63" t="n">
         <v>4.878885739026001e-05</v>
       </c>
       <c r="AJ63" t="n">
-        <v>3.730540457576e-05</v>
+        <v>3.730540457576001e-05</v>
       </c>
       <c r="AK63" t="n">
         <v>6.444942470880001e-05</v>
@@ -18271,7 +18271,7 @@
         <v>5.91948136086e-05</v>
       </c>
       <c r="AP63" t="n">
-        <v>4.752221975485e-05</v>
+        <v>4.752221975484999e-05</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.77355455432e-05</v>
@@ -18286,7 +18286,7 @@
         <v>3.540304820544e-05</v>
       </c>
       <c r="AU63" t="n">
-        <v>4.707226107511001e-05</v>
+        <v>4.707226107511002e-05</v>
       </c>
       <c r="AV63" t="n">
         <v>8.211e-06</v>
@@ -18298,7 +18298,7 @@
         <v>1.455315305396249e-05</v>
       </c>
       <c r="AY63" t="n">
-        <v>2.662507453541767e-05</v>
+        <v>2.662507453541768e-05</v>
       </c>
       <c r="AZ63" t="n">
         <v>1.850922277075422e-05</v>
@@ -18310,7 +18310,7 @@
         <v>2.862837842360958e-05</v>
       </c>
       <c r="BC63" t="n">
-        <v>5.166042049882431e-05</v>
+        <v>5.16604204988243e-05</v>
       </c>
       <c r="BD63" t="n">
         <v>2.272085212965437e-05</v>
@@ -18331,7 +18331,7 @@
         <v>2.580817877515776e-06</v>
       </c>
       <c r="BJ63" t="n">
-        <v>8.176053918598471e-06</v>
+        <v>8.176053918598472e-06</v>
       </c>
       <c r="BK63" t="n">
         <v>3.721761908884092e-06</v>
@@ -18379,7 +18379,7 @@
         <v>0.000104224854134634</v>
       </c>
       <c r="BZ63" t="n">
-        <v>5.082139821420082e-05</v>
+        <v>5.082139821420081e-05</v>
       </c>
       <c r="CA63" t="n">
         <v>2.514753039866682e-05</v>
@@ -18388,7 +18388,7 @@
         <v>8.579280239254088e-06</v>
       </c>
       <c r="CC63" t="n">
-        <v>8.463928108408935e-06</v>
+        <v>8.463928108408937e-06</v>
       </c>
       <c r="CD63" t="n">
         <v>1.018202850754955e-05</v>
@@ -18412,16 +18412,16 @@
         <v>1.890779840616588e-05</v>
       </c>
       <c r="CK63" t="n">
-        <v>1.996211301677384e-05</v>
+        <v>1.996211301677383e-05</v>
       </c>
       <c r="CL63" t="n">
-        <v>1.690378673420764e-05</v>
+        <v>1.690378673420765e-05</v>
       </c>
       <c r="CM63" t="n">
         <v>8.387039645840863e-06</v>
       </c>
       <c r="CN63" t="n">
-        <v>8.300053055958514e-06</v>
+        <v>8.300053055958512e-06</v>
       </c>
       <c r="CO63" t="n">
         <v>8.577322849331897e-06</v>
@@ -18430,10 +18430,10 @@
         <v>8.18205668905898e-06</v>
       </c>
       <c r="CQ63" t="n">
-        <v>8.21395983986132e-06</v>
+        <v>8.213959839861318e-06</v>
       </c>
       <c r="CR63" t="n">
-        <v>8.240158045486828e-06</v>
+        <v>8.240158045486829e-06</v>
       </c>
       <c r="CS63" t="n">
         <v>7.931780621472183e-06</v>
@@ -18448,19 +18448,19 @@
         <v>8.018573415499763e-06</v>
       </c>
       <c r="CW63" t="n">
-        <v>8.063543850137939e-06</v>
+        <v>8.063543850137937e-06</v>
       </c>
       <c r="CX63" t="n">
         <v>8.111817550900744e-06</v>
       </c>
       <c r="CY63" t="n">
-        <v>7.951755363490721e-06</v>
+        <v>7.951755363490722e-06</v>
       </c>
       <c r="CZ63" t="n">
-        <v>7.697120682764843e-06</v>
+        <v>7.697120682764845e-06</v>
       </c>
       <c r="DA63" t="n">
-        <v>8.238850060761348e-06</v>
+        <v>8.238850060761349e-06</v>
       </c>
       <c r="DB63" t="n">
         <v>7.924936649217557e-06</v>
@@ -18469,10 +18469,10 @@
         <v>7.990795911588602e-06</v>
       </c>
       <c r="DD63" t="n">
-        <v>8.217089834140509e-06</v>
+        <v>8.217089834140507e-06</v>
       </c>
       <c r="DE63" t="n">
-        <v>9.03031153607244e-06</v>
+        <v>9.030311536072442e-06</v>
       </c>
       <c r="DF63" t="n">
         <v>8.763128980007646e-06</v>
@@ -18487,10 +18487,10 @@
         <v>8.681484768915894e-06</v>
       </c>
       <c r="DJ63" t="n">
-        <v>9.338153446286909e-06</v>
+        <v>9.338153446286911e-06</v>
       </c>
       <c r="DK63" t="n">
-        <v>7.78314821654554e-06</v>
+        <v>7.783148216545541e-06</v>
       </c>
       <c r="DL63" t="n">
         <v>7.851951748885547e-06</v>
@@ -18499,10 +18499,10 @@
         <v>8.595896012783979e-06</v>
       </c>
       <c r="DN63" t="n">
-        <v>8.690515085633849e-06</v>
+        <v>8.690515085633847e-06</v>
       </c>
       <c r="DO63" t="n">
-        <v>8.586491649808973e-06</v>
+        <v>8.586491649808971e-06</v>
       </c>
       <c r="DP63" t="n">
         <v>8.541019878676557e-06</v>
@@ -18765,7 +18765,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>9.084716823376633e-05</v>
+        <v>9.084716823376632e-05</v>
       </c>
       <c r="C65" t="n">
         <v>0.0001181067904550569</v>
@@ -18780,7 +18780,7 @@
         <v>0.0001086792946557</v>
       </c>
       <c r="G65" t="n">
-        <v>7.625137166960002e-05</v>
+        <v>7.625137166959999e-05</v>
       </c>
       <c r="H65" t="n">
         <v>6.571362128870001e-05</v>
@@ -18792,10 +18792,10 @@
         <v>7.591484539389999e-05</v>
       </c>
       <c r="K65" t="n">
-        <v>7.213759432439999e-05</v>
+        <v>7.21375943244e-05</v>
       </c>
       <c r="L65" t="n">
-        <v>7.504137301700001e-05</v>
+        <v>7.504137301699999e-05</v>
       </c>
       <c r="M65" t="n">
         <v>0.0001037340052349</v>
@@ -18804,7 +18804,7 @@
         <v>0.0001093783657515</v>
       </c>
       <c r="O65" t="n">
-        <v>8.944143602890001e-05</v>
+        <v>8.94414360289e-05</v>
       </c>
       <c r="P65" t="n">
         <v>0.0001081886227036</v>
@@ -18819,7 +18819,7 @@
         <v>0.0001123252887527</v>
       </c>
       <c r="T65" t="n">
-        <v>0.0002261862223193</v>
+        <v>0.0002261862223193001</v>
       </c>
       <c r="U65" t="n">
         <v>0.0002341786438621</v>
@@ -18852,7 +18852,7 @@
         <v>0.0002598661030116</v>
       </c>
       <c r="AE65" t="n">
-        <v>0.0003223688978722</v>
+        <v>0.0003223688978721999</v>
       </c>
       <c r="AF65" t="n">
         <v>0.0002769308229589</v>
@@ -18903,61 +18903,61 @@
         <v>8.413149340679999e-05</v>
       </c>
       <c r="AV65" t="n">
-        <v>0.0003570336666666667</v>
+        <v>0.0003570336666666666</v>
       </c>
       <c r="AW65" t="n">
-        <v>0.0001269335978300245</v>
+        <v>0.0001269335978300244</v>
       </c>
       <c r="AX65" t="n">
-        <v>9.488527175644284e-05</v>
+        <v>9.488527175644285e-05</v>
       </c>
       <c r="AY65" t="n">
-        <v>9.809447311252341e-05</v>
+        <v>9.809447311252339e-05</v>
       </c>
       <c r="AZ65" t="n">
         <v>6.68076451009502e-05</v>
       </c>
       <c r="BA65" t="n">
-        <v>0.0008319715158459622</v>
+        <v>0.0008319715158459621</v>
       </c>
       <c r="BB65" t="n">
         <v>0.0002658885205505466</v>
       </c>
       <c r="BC65" t="n">
-        <v>0.0007582142993897351</v>
+        <v>0.000758214299389735</v>
       </c>
       <c r="BD65" t="n">
-        <v>0.0001945491572754466</v>
+        <v>0.0001945491572754465</v>
       </c>
       <c r="BE65" t="n">
-        <v>0.0003284284117625063</v>
+        <v>0.0003284284117625064</v>
       </c>
       <c r="BF65" t="n">
-        <v>0.000310344281598461</v>
+        <v>0.0003103442815984611</v>
       </c>
       <c r="BG65" t="n">
         <v>0.0003778176153366192</v>
       </c>
       <c r="BH65" t="n">
-        <v>0.0003432967276405301</v>
+        <v>0.00034329672764053</v>
       </c>
       <c r="BI65" t="n">
-        <v>0.0007032025616821654</v>
+        <v>0.0007032025616821652</v>
       </c>
       <c r="BJ65" t="n">
         <v>0.0007032021637014279</v>
       </c>
       <c r="BK65" t="n">
-        <v>0.0006511987813018929</v>
+        <v>0.0006511987813018931</v>
       </c>
       <c r="BL65" t="n">
-        <v>0.0004500229824261043</v>
+        <v>0.0004500229824261042</v>
       </c>
       <c r="BM65" t="n">
-        <v>0.0007727150681036201</v>
+        <v>0.0007727150681036202</v>
       </c>
       <c r="BN65" t="n">
-        <v>0.0007492950387927598</v>
+        <v>0.0007492950387927599</v>
       </c>
       <c r="BO65" t="n">
         <v>0.000820448206376619</v>
@@ -18966,7 +18966,7 @@
         <v>0.0007056881131567586</v>
       </c>
       <c r="BQ65" t="n">
-        <v>0.0006965436036100962</v>
+        <v>0.0006965436036100964</v>
       </c>
       <c r="BR65" t="n">
         <v>0.0003051790171404849</v>
@@ -18975,13 +18975,13 @@
         <v>0.0003979442486031944</v>
       </c>
       <c r="BT65" t="n">
-        <v>0.0005000180623733252</v>
+        <v>0.000500018062373325</v>
       </c>
       <c r="BU65" t="n">
-        <v>0.0001012825670658307</v>
+        <v>0.0001012825670658306</v>
       </c>
       <c r="BV65" t="n">
-        <v>0.0001038414401495918</v>
+        <v>0.0001038414401495917</v>
       </c>
       <c r="BW65" t="n">
         <v>0.0004422378098400441</v>
@@ -18996,25 +18996,25 @@
         <v>0.0003972673911671537</v>
       </c>
       <c r="CA65" t="n">
-        <v>0.0004720593040513363</v>
+        <v>0.0004720593040513364</v>
       </c>
       <c r="CB65" t="n">
-        <v>9.245517336809093e-05</v>
+        <v>9.245517336809091e-05</v>
       </c>
       <c r="CC65" t="n">
         <v>0.0001567307276927105</v>
       </c>
       <c r="CD65" t="n">
-        <v>0.0003510656753551421</v>
+        <v>0.000351065675355142</v>
       </c>
       <c r="CE65" t="n">
         <v>0.0003728889281235567</v>
       </c>
       <c r="CF65" t="n">
-        <v>0.0004328612183591953</v>
+        <v>0.0004328612183591952</v>
       </c>
       <c r="CG65" t="n">
-        <v>0.0004751609861870368</v>
+        <v>0.000475160986187037</v>
       </c>
       <c r="CH65" t="n">
         <v>0.0003674614877394113</v>
@@ -19026,7 +19026,7 @@
         <v>0.0003579727455726192</v>
       </c>
       <c r="CK65" t="n">
-        <v>0.0002926295907805424</v>
+        <v>0.0002926295907805423</v>
       </c>
       <c r="CL65" t="n">
         <v>0.0002291822823175677</v>
@@ -19038,19 +19038,19 @@
         <v>8.488652568625904e-05</v>
       </c>
       <c r="CO65" t="n">
-        <v>8.316536935840022e-05</v>
+        <v>8.316536935840021e-05</v>
       </c>
       <c r="CP65" t="n">
         <v>8.298430949277478e-05</v>
       </c>
       <c r="CQ65" t="n">
-        <v>8.413420040323762e-05</v>
+        <v>8.41342004032376e-05</v>
       </c>
       <c r="CR65" t="n">
         <v>8.320211853381824e-05</v>
       </c>
       <c r="CS65" t="n">
-        <v>8.775029645914211e-05</v>
+        <v>8.775029645914213e-05</v>
       </c>
       <c r="CT65" t="n">
         <v>8.64613337370995e-05</v>
@@ -19059,31 +19059,31 @@
         <v>8.743997595869641e-05</v>
       </c>
       <c r="CV65" t="n">
-        <v>8.930215407592589e-05</v>
+        <v>8.930215407592588e-05</v>
       </c>
       <c r="CW65" t="n">
-        <v>8.718086558640263e-05</v>
+        <v>8.718086558640262e-05</v>
       </c>
       <c r="CX65" t="n">
-        <v>8.727774852277881e-05</v>
+        <v>8.727774852277878e-05</v>
       </c>
       <c r="CY65" t="n">
         <v>8.813893378954286e-05</v>
       </c>
       <c r="CZ65" t="n">
-        <v>8.539381173378124e-05</v>
+        <v>8.539381173378125e-05</v>
       </c>
       <c r="DA65" t="n">
-        <v>8.795787977136946e-05</v>
+        <v>8.795787977136944e-05</v>
       </c>
       <c r="DB65" t="n">
-        <v>8.514644392314396e-05</v>
+        <v>8.514644392314393e-05</v>
       </c>
       <c r="DC65" t="n">
-        <v>8.948195178196892e-05</v>
+        <v>8.94819517819689e-05</v>
       </c>
       <c r="DD65" t="n">
-        <v>8.686264374184414e-05</v>
+        <v>8.686264374184413e-05</v>
       </c>
       <c r="DE65" t="n">
         <v>9.024913306923115e-05</v>
@@ -19095,10 +19095,10 @@
         <v>8.831384708319363e-05</v>
       </c>
       <c r="DH65" t="n">
-        <v>9.148598805497689e-05</v>
+        <v>9.14859880549769e-05</v>
       </c>
       <c r="DI65" t="n">
-        <v>8.801037678449087e-05</v>
+        <v>8.801037678449085e-05</v>
       </c>
       <c r="DJ65" t="n">
         <v>9.034020000485097e-05</v>
@@ -19113,13 +19113,13 @@
         <v>9.036771035926532e-05</v>
       </c>
       <c r="DN65" t="n">
-        <v>9.072992106203761e-05</v>
+        <v>9.072992106203763e-05</v>
       </c>
       <c r="DO65" t="n">
-        <v>9.086082197481096e-05</v>
+        <v>9.086082197481095e-05</v>
       </c>
       <c r="DP65" t="n">
-        <v>9.130995881317261e-05</v>
+        <v>9.130995881317258e-05</v>
       </c>
     </row>
     <row r="66">
@@ -19138,7 +19138,7 @@
         <v>4.24056778562363e-07</v>
       </c>
       <c r="E66" t="n">
-        <v>8.005476573417074e-07</v>
+        <v>8.005476573417073e-07</v>
       </c>
       <c r="F66" t="n">
         <v>1.85981640798e-07</v>
@@ -20585,10 +20585,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.973488310014527e-05</v>
+        <v>1.973488310014526e-05</v>
       </c>
       <c r="C72" t="n">
-        <v>2.882871086660242e-05</v>
+        <v>2.882871086660243e-05</v>
       </c>
       <c r="D72" t="n">
         <v>4.10294587942779e-05</v>
@@ -20672,7 +20672,7 @@
         <v>4.7787852857e-05</v>
       </c>
       <c r="AE72" t="n">
-        <v>5.5269435695e-05</v>
+        <v>5.526943569500001e-05</v>
       </c>
       <c r="AF72" t="n">
         <v>5.222865597e-05</v>
@@ -20729,7 +20729,7 @@
         <v>3.202282657756577e-05</v>
       </c>
       <c r="AX72" t="n">
-        <v>4.258933544783952e-05</v>
+        <v>4.258933544783951e-05</v>
       </c>
       <c r="AY72" t="n">
         <v>3.441945636196225e-05</v>
@@ -20759,7 +20759,7 @@
         <v>4.824382049047319e-05</v>
       </c>
       <c r="BH72" t="n">
-        <v>4.778353581821803e-05</v>
+        <v>4.778353581821802e-05</v>
       </c>
       <c r="BI72" t="n">
         <v>3.657966851544337e-05</v>
@@ -20768,13 +20768,13 @@
         <v>6.217770025572898e-05</v>
       </c>
       <c r="BK72" t="n">
-        <v>4.67317252175357e-05</v>
+        <v>4.673172521753571e-05</v>
       </c>
       <c r="BL72" t="n">
         <v>2.723280730654268e-05</v>
       </c>
       <c r="BM72" t="n">
-        <v>4.338360837761542e-05</v>
+        <v>4.338360837761541e-05</v>
       </c>
       <c r="BN72" t="n">
         <v>4.510707787446031e-05</v>
@@ -20798,7 +20798,7 @@
         <v>0.0001503140591695314</v>
       </c>
       <c r="BU72" t="n">
-        <v>4.393068870693417e-05</v>
+        <v>4.393068870693416e-05</v>
       </c>
       <c r="BV72" t="n">
         <v>6.439106404591212e-05</v>
@@ -20828,7 +20828,7 @@
         <v>2.261819020213844e-05</v>
       </c>
       <c r="CE72" t="n">
-        <v>2.709474702704741e-05</v>
+        <v>2.70947470270474e-05</v>
       </c>
       <c r="CF72" t="n">
         <v>3.503991778697453e-05</v>
@@ -20849,7 +20849,7 @@
         <v>5.230543244466873e-05</v>
       </c>
       <c r="CL72" t="n">
-        <v>4.226563462809732e-05</v>
+        <v>4.226563462809731e-05</v>
       </c>
       <c r="CM72" t="n">
         <v>7.250233766725013e-06</v>
@@ -20873,22 +20873,22 @@
         <v>7.879125413174246e-06</v>
       </c>
       <c r="CT72" t="n">
-        <v>7.639748151912395e-06</v>
+        <v>7.639748151912397e-06</v>
       </c>
       <c r="CU72" t="n">
-        <v>7.606960626657967e-06</v>
+        <v>7.606960626657968e-06</v>
       </c>
       <c r="CV72" t="n">
-        <v>8.315455593291674e-06</v>
+        <v>8.315455593291675e-06</v>
       </c>
       <c r="CW72" t="n">
         <v>7.893063391420569e-06</v>
       </c>
       <c r="CX72" t="n">
-        <v>7.371397555966319e-06</v>
+        <v>7.37139755596632e-06</v>
       </c>
       <c r="CY72" t="n">
-        <v>8.180358074710134e-06</v>
+        <v>8.180358074710136e-06</v>
       </c>
       <c r="CZ72" t="n">
         <v>7.848638015369921e-06</v>
@@ -20900,13 +20900,13 @@
         <v>7.445223522842463e-06</v>
       </c>
       <c r="DC72" t="n">
-        <v>7.223390821359649e-06</v>
+        <v>7.223390821359648e-06</v>
       </c>
       <c r="DD72" t="n">
         <v>7.345955914582588e-06</v>
       </c>
       <c r="DE72" t="n">
-        <v>7.642593551071107e-06</v>
+        <v>7.642593551071105e-06</v>
       </c>
       <c r="DF72" t="n">
         <v>7.057684241421383e-06</v>
@@ -20918,7 +20918,7 @@
         <v>7.380436755474863e-06</v>
       </c>
       <c r="DI72" t="n">
-        <v>7.4004508080343e-06</v>
+        <v>7.400450808034301e-06</v>
       </c>
       <c r="DJ72" t="n">
         <v>7.276733585350905e-06</v>
@@ -20930,7 +20930,7 @@
         <v>7.163080765965007e-06</v>
       </c>
       <c r="DM72" t="n">
-        <v>7.205598274767277e-06</v>
+        <v>7.205598274767276e-06</v>
       </c>
       <c r="DN72" t="n">
         <v>7.322897726766935e-06</v>
@@ -20939,7 +20939,7 @@
         <v>7.281954009772906e-06</v>
       </c>
       <c r="DP72" t="n">
-        <v>7.120828300477553e-06</v>
+        <v>7.120828300477554e-06</v>
       </c>
     </row>
     <row r="73">
@@ -20961,13 +20961,13 @@
         <v>1.439607738295328e-05</v>
       </c>
       <c r="F73" t="n">
-        <v>8.153574401448999e-06</v>
+        <v>8.153574401449e-06</v>
       </c>
       <c r="G73" t="n">
         <v>1.0366502107343e-05</v>
       </c>
       <c r="H73" t="n">
-        <v>8.305856010314001e-06</v>
+        <v>8.305856010313999e-06</v>
       </c>
       <c r="I73" t="n">
         <v>9.138060582981001e-06</v>
@@ -20994,7 +20994,7 @@
         <v>1.2238739133664e-05</v>
       </c>
       <c r="Q73" t="n">
-        <v>7.557336071243e-06</v>
+        <v>7.557336071243001e-06</v>
       </c>
       <c r="R73" t="n">
         <v>1.2001970380439e-05</v>
@@ -21021,13 +21021,13 @@
         <v>1.2257461276389e-05</v>
       </c>
       <c r="Z73" t="n">
-        <v>8.575640102151e-06</v>
+        <v>8.575640102150999e-06</v>
       </c>
       <c r="AA73" t="n">
         <v>1.292023536781e-05</v>
       </c>
       <c r="AB73" t="n">
-        <v>7.54942784943e-06</v>
+        <v>7.549427849429999e-06</v>
       </c>
       <c r="AC73" t="n">
         <v>1.2267651928845e-05</v>
@@ -21078,16 +21078,16 @@
         <v>1.0494296600469e-05</v>
       </c>
       <c r="AS73" t="n">
-        <v>6.427842627878001e-06</v>
+        <v>6.427842627878e-06</v>
       </c>
       <c r="AT73" t="n">
-        <v>6.642580152757001e-06</v>
+        <v>6.642580152756999e-06</v>
       </c>
       <c r="AU73" t="n">
         <v>9.605556304322e-06</v>
       </c>
       <c r="AV73" t="n">
-        <v>7.947133333333335e-05</v>
+        <v>7.947133333333333e-05</v>
       </c>
       <c r="AW73" t="n">
         <v>2.316160207538012e-05</v>
@@ -21099,7 +21099,7 @@
         <v>2.330639946019494e-05</v>
       </c>
       <c r="AZ73" t="n">
-        <v>1.931379165727816e-05</v>
+        <v>1.931379165727817e-05</v>
       </c>
       <c r="BA73" t="n">
         <v>0.000106241951489464</v>
@@ -21108,10 +21108,10 @@
         <v>4.889241610275521e-05</v>
       </c>
       <c r="BC73" t="n">
-        <v>8.409606758615346e-05</v>
+        <v>8.409606758615347e-05</v>
       </c>
       <c r="BD73" t="n">
-        <v>3.869193351669941e-05</v>
+        <v>3.869193351669942e-05</v>
       </c>
       <c r="BE73" t="n">
         <v>3.590733664153508e-05</v>
@@ -21123,22 +21123,22 @@
         <v>4.000243570129786e-05</v>
       </c>
       <c r="BH73" t="n">
-        <v>3.703729366398552e-05</v>
+        <v>3.703729366398553e-05</v>
       </c>
       <c r="BI73" t="n">
-        <v>6.96368276046164e-05</v>
+        <v>6.963682760461641e-05</v>
       </c>
       <c r="BJ73" t="n">
         <v>7.172942347641979e-05</v>
       </c>
       <c r="BK73" t="n">
-        <v>6.156126215509797e-05</v>
+        <v>6.156126215509798e-05</v>
       </c>
       <c r="BL73" t="n">
-        <v>4.938944684008635e-05</v>
+        <v>4.938944684008636e-05</v>
       </c>
       <c r="BM73" t="n">
-        <v>7.36134269103288e-05</v>
+        <v>7.361342691032879e-05</v>
       </c>
       <c r="BN73" t="n">
         <v>7.703867599352373e-05</v>
@@ -21147,13 +21147,13 @@
         <v>7.876196773746265e-05</v>
       </c>
       <c r="BP73" t="n">
-        <v>7.480174031418134e-05</v>
+        <v>7.480174031418133e-05</v>
       </c>
       <c r="BQ73" t="n">
         <v>8.314985972915974e-05</v>
       </c>
       <c r="BR73" t="n">
-        <v>5.792985773580206e-05</v>
+        <v>5.792985773580205e-05</v>
       </c>
       <c r="BS73" t="n">
         <v>0.0001681088945226711</v>
@@ -21168,7 +21168,7 @@
         <v>2.210283271591447e-05</v>
       </c>
       <c r="BW73" t="n">
-        <v>0.0002511236843627302</v>
+        <v>0.0002511236843627303</v>
       </c>
       <c r="BX73" t="n">
         <v>0.0002083909380165502</v>
@@ -21177,10 +21177,10 @@
         <v>0.000386822364174485</v>
       </c>
       <c r="BZ73" t="n">
-        <v>0.0002256711643254289</v>
+        <v>0.000225671164325429</v>
       </c>
       <c r="CA73" t="n">
-        <v>0.000122130475182102</v>
+        <v>0.0001221304751821021</v>
       </c>
       <c r="CB73" t="n">
         <v>1.200068915125211e-05</v>
@@ -21189,31 +21189,31 @@
         <v>1.803243699840493e-05</v>
       </c>
       <c r="CD73" t="n">
-        <v>5.944792152390173e-05</v>
+        <v>5.944792152390172e-05</v>
       </c>
       <c r="CE73" t="n">
-        <v>6.052421993735147e-05</v>
+        <v>6.052421993735148e-05</v>
       </c>
       <c r="CF73" t="n">
         <v>5.814966633091795e-05</v>
       </c>
       <c r="CG73" t="n">
-        <v>5.687055763370441e-05</v>
+        <v>5.687055763370442e-05</v>
       </c>
       <c r="CH73" t="n">
         <v>3.823486915198056e-05</v>
       </c>
       <c r="CI73" t="n">
-        <v>3.861097830247286e-05</v>
+        <v>3.861097830247287e-05</v>
       </c>
       <c r="CJ73" t="n">
         <v>3.719485453874263e-05</v>
       </c>
       <c r="CK73" t="n">
-        <v>2.865507168694977e-05</v>
+        <v>2.865507168694978e-05</v>
       </c>
       <c r="CL73" t="n">
-        <v>2.148068401562849e-05</v>
+        <v>2.14806840156285e-05</v>
       </c>
       <c r="CM73" t="n">
         <v>1.233694538766426e-05</v>
@@ -21231,7 +21231,7 @@
         <v>1.277216607907631e-05</v>
       </c>
       <c r="CR73" t="n">
-        <v>1.275004492952608e-05</v>
+        <v>1.275004492952609e-05</v>
       </c>
       <c r="CS73" t="n">
         <v>1.623170400531149e-05</v>
@@ -21288,7 +21288,7 @@
         <v>1.454438985474896e-05</v>
       </c>
       <c r="DK73" t="n">
-        <v>1.427023761416494e-05</v>
+        <v>1.427023761416495e-05</v>
       </c>
       <c r="DL73" t="n">
         <v>1.442325167524582e-05</v>
@@ -21297,7 +21297,7 @@
         <v>1.646621589758301e-05</v>
       </c>
       <c r="DN73" t="n">
-        <v>1.437542311413969e-05</v>
+        <v>1.43754231141397e-05</v>
       </c>
       <c r="DO73" t="n">
         <v>1.4507793067719e-05</v>
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>6.494834110972911e-06</v>
+        <v>6.494834110972912e-06</v>
       </c>
       <c r="C74" t="n">
         <v>6.509601333320847e-06</v>
@@ -21454,13 +21454,13 @@
         <v>6.5e-06</v>
       </c>
       <c r="AW74" t="n">
-        <v>8.47000020083377e-06</v>
+        <v>8.470000200833769e-06</v>
       </c>
       <c r="AX74" t="n">
         <v>1.015716434099254e-05</v>
       </c>
       <c r="AY74" t="n">
-        <v>1.095291190990355e-05</v>
+        <v>1.095291190990354e-05</v>
       </c>
       <c r="AZ74" t="n">
         <v>1.242642198061035e-05</v>
@@ -21541,13 +21541,13 @@
         <v>1.778602010627723e-05</v>
       </c>
       <c r="BZ74" t="n">
-        <v>1.730887242293337e-05</v>
+        <v>1.730887242293336e-05</v>
       </c>
       <c r="CA74" t="n">
         <v>1.834835509746196e-05</v>
       </c>
       <c r="CB74" t="n">
-        <v>8.842969070218413e-06</v>
+        <v>8.842969070218415e-06</v>
       </c>
       <c r="CC74" t="n">
         <v>1.391783423810512e-05</v>
@@ -21809,7 +21809,7 @@
         <v>7.451299022165432e-07</v>
       </c>
       <c r="D76" t="n">
-        <v>7.14294065703819e-07</v>
+        <v>7.142940657038189e-07</v>
       </c>
       <c r="E76" t="n">
         <v>1.85412918762176e-06</v>
@@ -21818,7 +21818,7 @@
         <v>6.2312507125e-07</v>
       </c>
       <c r="G76" t="n">
-        <v>6.609244049599999e-07</v>
+        <v>6.6092440496e-07</v>
       </c>
       <c r="H76" t="n">
         <v>5.813892887200001e-07</v>
@@ -21827,7 +21827,7 @@
         <v>5.7783879691e-07</v>
       </c>
       <c r="J76" t="n">
-        <v>6.390137746e-07</v>
+        <v>6.390137746000001e-07</v>
       </c>
       <c r="K76" t="n">
         <v>6.126626718e-07</v>
@@ -21836,10 +21836,10 @@
         <v>6.4689141862e-07</v>
       </c>
       <c r="M76" t="n">
-        <v>8.165824955999999e-07</v>
+        <v>8.165824956e-07</v>
       </c>
       <c r="N76" t="n">
-        <v>8.721412991800001e-07</v>
+        <v>8.7214129918e-07</v>
       </c>
       <c r="O76" t="n">
         <v>7.8486635871e-07</v>
@@ -21899,7 +21899,7 @@
         <v>9.581911613400001e-07</v>
       </c>
       <c r="AH76" t="n">
-        <v>9.2097269904e-07</v>
+        <v>9.209726990400001e-07</v>
       </c>
       <c r="AI76" t="n">
         <v>1.04685455659e-06</v>
@@ -21911,7 +21911,7 @@
         <v>1.12815301295e-06</v>
       </c>
       <c r="AL76" t="n">
-        <v>8.213243564e-07</v>
+        <v>8.213243564000001e-07</v>
       </c>
       <c r="AM76" t="n">
         <v>7.949933737900001e-07</v>
@@ -21923,13 +21923,13 @@
         <v>1.0234769959e-06</v>
       </c>
       <c r="AP76" t="n">
-        <v>8.927881265800001e-07</v>
+        <v>8.9278812658e-07</v>
       </c>
       <c r="AQ76" t="n">
         <v>8.611693847300001e-07</v>
       </c>
       <c r="AR76" t="n">
-        <v>7.511261264499999e-07</v>
+        <v>7.5112612645e-07</v>
       </c>
       <c r="AS76" t="n">
         <v>4.3465087206e-07</v>
@@ -22109,13 +22109,13 @@
         <v>4.101783127958375e-07</v>
       </c>
       <c r="CZ76" t="n">
-        <v>4.361939725972367e-07</v>
+        <v>4.361939725972368e-07</v>
       </c>
       <c r="DA76" t="n">
         <v>3.631643928737597e-07</v>
       </c>
       <c r="DB76" t="n">
-        <v>4.578423052745568e-07</v>
+        <v>4.578423052745569e-07</v>
       </c>
       <c r="DC76" t="n">
         <v>3.362836009383681e-07</v>
@@ -22151,7 +22151,7 @@
         <v>4.888931747929479e-07</v>
       </c>
       <c r="DN76" t="n">
-        <v>3.529915493248671e-07</v>
+        <v>3.529915493248672e-07</v>
       </c>
       <c r="DO76" t="n">
         <v>3.55605681868784e-07</v>
@@ -23234,7 +23234,7 @@
         <v>1.4082256015e-05</v>
       </c>
       <c r="AK83" t="n">
-        <v>1.8632427031e-05</v>
+        <v>1.863242703100001e-05</v>
       </c>
       <c r="AL83" t="n">
         <v>1.537679741e-05</v>
@@ -23288,7 +23288,7 @@
         <v>7.090690476308295e-05</v>
       </c>
       <c r="BC83" t="n">
-        <v>8.590739075363505e-05</v>
+        <v>8.590739075363503e-05</v>
       </c>
       <c r="BD83" t="n">
         <v>6.283248436789372e-05</v>
@@ -23297,7 +23297,7 @@
         <v>4.928594240899418e-05</v>
       </c>
       <c r="BF83" t="n">
-        <v>4.934244820598556e-05</v>
+        <v>4.934244820598557e-05</v>
       </c>
       <c r="BG83" t="n">
         <v>4.811781970422351e-05</v>
@@ -23315,13 +23315,13 @@
         <v>5.338602517635336e-05</v>
       </c>
       <c r="BL83" t="n">
-        <v>6.84487646569246e-05</v>
+        <v>6.844876465692462e-05</v>
       </c>
       <c r="BM83" t="n">
         <v>4.943956166771837e-05</v>
       </c>
       <c r="BN83" t="n">
-        <v>4.965280076353371e-05</v>
+        <v>4.96528007635337e-05</v>
       </c>
       <c r="BO83" t="n">
         <v>4.949655348804384e-05</v>
@@ -23330,7 +23330,7 @@
         <v>5.198567387512454e-05</v>
       </c>
       <c r="BQ83" t="n">
-        <v>5.186172935951512e-05</v>
+        <v>5.186172935951511e-05</v>
       </c>
       <c r="BR83" t="n">
         <v>5.75556078933909e-05</v>
@@ -23345,13 +23345,13 @@
         <v>3.080937179356583e-05</v>
       </c>
       <c r="BV83" t="n">
-        <v>2.907472790439911e-05</v>
+        <v>2.90747279043991e-05</v>
       </c>
       <c r="BW83" t="n">
         <v>2.582202215637605e-05</v>
       </c>
       <c r="BX83" t="n">
-        <v>2.374917704772768e-05</v>
+        <v>2.374917704772767e-05</v>
       </c>
       <c r="BY83" t="n">
         <v>3.327682851654579e-05</v>
@@ -23390,10 +23390,10 @@
         <v>3.609642011102163e-05</v>
       </c>
       <c r="CK83" t="n">
-        <v>4.201993377519451e-05</v>
+        <v>4.20199337751945e-05</v>
       </c>
       <c r="CL83" t="n">
-        <v>4.046520986740063e-05</v>
+        <v>4.046520986740062e-05</v>
       </c>
       <c r="CM83" t="n">
         <v>2.080973454012321e-05</v>
@@ -23417,7 +23417,7 @@
         <v>1.954349352825807e-05</v>
       </c>
       <c r="CT83" t="n">
-        <v>1.985691241212815e-05</v>
+        <v>1.985691241212814e-05</v>
       </c>
       <c r="CU83" t="n">
         <v>1.973200479700386e-05</v>
@@ -23429,7 +23429,7 @@
         <v>1.966806867071354e-05</v>
       </c>
       <c r="CX83" t="n">
-        <v>1.99506163767259e-05</v>
+        <v>1.995061637672591e-05</v>
       </c>
       <c r="CY83" t="n">
         <v>1.974181197097262e-05</v>
@@ -23447,10 +23447,10 @@
         <v>2.016041761133446e-05</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.957597868212608e-05</v>
+        <v>1.957597868212607e-05</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.980091730923837e-05</v>
+        <v>1.980091730923836e-05</v>
       </c>
       <c r="DF83" t="n">
         <v>1.982999584251253e-05</v>
@@ -23459,10 +23459,10 @@
         <v>1.924431353755959e-05</v>
       </c>
       <c r="DH83" t="n">
-        <v>1.960317895137507e-05</v>
+        <v>1.960317895137508e-05</v>
       </c>
       <c r="DI83" t="n">
-        <v>1.989093434521805e-05</v>
+        <v>1.989093434521806e-05</v>
       </c>
       <c r="DJ83" t="n">
         <v>1.928593422947698e-05</v>
@@ -23480,7 +23480,7 @@
         <v>1.906256433168205e-05</v>
       </c>
       <c r="DO83" t="n">
-        <v>1.944852999260505e-05</v>
+        <v>1.944852999260506e-05</v>
       </c>
       <c r="DP83" t="n">
         <v>1.937610454246983e-05</v>
@@ -23553,7 +23553,7 @@
         <v>6.080349700127e-06</v>
       </c>
       <c r="V84" t="n">
-        <v>4.164906299441001e-06</v>
+        <v>4.164906299441e-06</v>
       </c>
       <c r="W84" t="n">
         <v>3.377433950684e-06</v>
@@ -23568,7 +23568,7 @@
         <v>3.175234474527e-06</v>
       </c>
       <c r="AA84" t="n">
-        <v>4.164696391577e-06</v>
+        <v>4.164696391577001e-06</v>
       </c>
       <c r="AB84" t="n">
         <v>2.173518619059e-06</v>
@@ -23586,7 +23586,7 @@
         <v>3.378686456216e-06</v>
       </c>
       <c r="AG84" t="n">
-        <v>4.958453668122001e-06</v>
+        <v>4.958453668122002e-06</v>
       </c>
       <c r="AH84" t="n">
         <v>4.141683502043001e-06</v>
@@ -23604,10 +23604,10 @@
         <v>2.645381950378e-06</v>
       </c>
       <c r="AM84" t="n">
-        <v>2.729067256663e-06</v>
+        <v>2.729067256662999e-06</v>
       </c>
       <c r="AN84" t="n">
-        <v>5.408924783062e-06</v>
+        <v>5.408924783062001e-06</v>
       </c>
       <c r="AO84" t="n">
         <v>4.749008821532001e-06</v>
@@ -23700,7 +23700,7 @@
         <v>8.148407880454998e-06</v>
       </c>
       <c r="BS84" t="n">
-        <v>4.949845164011284e-06</v>
+        <v>4.949845164011285e-06</v>
       </c>
       <c r="BT84" t="n">
         <v>4.027132861463151e-06</v>
@@ -24004,7 +24004,7 @@
         <v>2.958906292081658e-05</v>
       </c>
       <c r="AY85" t="n">
-        <v>5.775629117424388e-06</v>
+        <v>5.775629117424389e-06</v>
       </c>
       <c r="AZ85" t="n">
         <v>1.25789804890326e-05</v>
@@ -24923,7 +24923,7 @@
         <v>1.385882998950942e-07</v>
       </c>
       <c r="F91" t="n">
-        <v>4.333330558e-08</v>
+        <v>4.333330558000001e-08</v>
       </c>
       <c r="G91" t="n">
         <v>4.703907893100001e-08</v>
@@ -24941,10 +24941,10 @@
         <v>5.1078636181e-08</v>
       </c>
       <c r="L91" t="n">
-        <v>6.339048791000001e-08</v>
+        <v>6.339048790999999e-08</v>
       </c>
       <c r="M91" t="n">
-        <v>6.649702107100001e-08</v>
+        <v>6.6497021071e-08</v>
       </c>
       <c r="N91" t="n">
         <v>6.76456901e-08</v>
@@ -24980,7 +24980,7 @@
         <v>5.270883221e-08</v>
       </c>
       <c r="Y91" t="n">
-        <v>6.180989027799999e-08</v>
+        <v>6.180989027800001e-08</v>
       </c>
       <c r="Z91" t="n">
         <v>2.3782964395e-08</v>
@@ -25022,7 +25022,7 @@
         <v>5.720719095100001e-08</v>
       </c>
       <c r="AM91" t="n">
-        <v>9.709893391200001e-08</v>
+        <v>9.7098933912e-08</v>
       </c>
       <c r="AN91" t="n">
         <v>4.7624431772e-08</v>
@@ -26055,7 +26055,7 @@
         <v>2.82602007326574e-05</v>
       </c>
       <c r="D95" t="n">
-        <v>6.805937641829211e-05</v>
+        <v>6.805937641829209e-05</v>
       </c>
       <c r="E95" t="n">
         <v>2.33174245508869e-06</v>
@@ -26073,7 +26073,7 @@
         <v>6.397584006550001e-06</v>
       </c>
       <c r="J95" t="n">
-        <v>6.129504873289999e-06</v>
+        <v>6.12950487329e-06</v>
       </c>
       <c r="K95" t="n">
         <v>5.993826939610001e-06</v>
@@ -26091,7 +26091,7 @@
         <v>5.64318985251e-06</v>
       </c>
       <c r="P95" t="n">
-        <v>6.57867292281e-06</v>
+        <v>6.578672922810001e-06</v>
       </c>
       <c r="Q95" t="n">
         <v>6.6350793525e-06</v>
@@ -26100,7 +26100,7 @@
         <v>5.69031718907e-06</v>
       </c>
       <c r="S95" t="n">
-        <v>5.889333211620001e-06</v>
+        <v>5.88933321162e-06</v>
       </c>
       <c r="T95" t="n">
         <v>1.644821648605e-05</v>
@@ -26121,7 +26121,7 @@
         <v>9.141662662800002e-06</v>
       </c>
       <c r="Z95" t="n">
-        <v>6.33599947214e-06</v>
+        <v>6.335999472139999e-06</v>
       </c>
       <c r="AA95" t="n">
         <v>1.067988555038e-05</v>
@@ -26154,7 +26154,7 @@
         <v>7.442642592389999e-06</v>
       </c>
       <c r="AK95" t="n">
-        <v>9.73479548689e-06</v>
+        <v>9.734795486890002e-06</v>
       </c>
       <c r="AL95" t="n">
         <v>7.113729967499999e-06</v>
@@ -26181,16 +26181,16 @@
         <v>5.222857519919999e-06</v>
       </c>
       <c r="AT95" t="n">
-        <v>5.89808868739e-06</v>
+        <v>5.898088687389999e-06</v>
       </c>
       <c r="AU95" t="n">
         <v>6.57348296847e-06</v>
       </c>
       <c r="AV95" t="n">
-        <v>5.407533333333334e-05</v>
+        <v>5.407533333333333e-05</v>
       </c>
       <c r="AW95" t="n">
-        <v>8.127346310807037e-06</v>
+        <v>8.127346310807039e-06</v>
       </c>
       <c r="AX95" t="n">
         <v>1.076414565954561e-05</v>
@@ -26199,7 +26199,7 @@
         <v>6.093704926102412e-06</v>
       </c>
       <c r="AZ95" t="n">
-        <v>6.537484911938831e-06</v>
+        <v>6.537484911938832e-06</v>
       </c>
       <c r="BA95" t="n">
         <v>5.772188110042482e-05</v>
@@ -26208,7 +26208,7 @@
         <v>1.621399584691526e-05</v>
       </c>
       <c r="BC95" t="n">
-        <v>3.764586696151903e-05</v>
+        <v>3.764586696151902e-05</v>
       </c>
       <c r="BD95" t="n">
         <v>1.263470318698201e-05</v>
@@ -26259,28 +26259,28 @@
         <v>0.0001220546121812214</v>
       </c>
       <c r="BT95" t="n">
-        <v>0.0002983945595339038</v>
+        <v>0.0002983945595339039</v>
       </c>
       <c r="BU95" t="n">
         <v>1.18634601559782e-05</v>
       </c>
       <c r="BV95" t="n">
-        <v>9.095259412878789e-06</v>
+        <v>9.09525941287879e-06</v>
       </c>
       <c r="BW95" t="n">
-        <v>0.0002068969091051999</v>
+        <v>0.0002068969091051998</v>
       </c>
       <c r="BX95" t="n">
         <v>0.0001696500545358093</v>
       </c>
       <c r="BY95" t="n">
-        <v>0.0002862825674379497</v>
+        <v>0.0002862825674379498</v>
       </c>
       <c r="BZ95" t="n">
         <v>0.0001745336162394073</v>
       </c>
       <c r="CA95" t="n">
-        <v>9.512481659620894e-05</v>
+        <v>9.512481659620893e-05</v>
       </c>
       <c r="CB95" t="n">
         <v>3.686650193420126e-06</v>
@@ -26292,19 +26292,19 @@
         <v>3.937550081081502e-05</v>
       </c>
       <c r="CE95" t="n">
-        <v>3.801732838097999e-05</v>
+        <v>3.801732838097998e-05</v>
       </c>
       <c r="CF95" t="n">
-        <v>3.460592900374057e-05</v>
+        <v>3.460592900374058e-05</v>
       </c>
       <c r="CG95" t="n">
-        <v>3.407595727097178e-05</v>
+        <v>3.407595727097177e-05</v>
       </c>
       <c r="CH95" t="n">
         <v>2.520790656057646e-05</v>
       </c>
       <c r="CI95" t="n">
-        <v>2.627762951690996e-05</v>
+        <v>2.627762951690995e-05</v>
       </c>
       <c r="CJ95" t="n">
         <v>2.400616303552767e-05</v>
@@ -26313,7 +26313,7 @@
         <v>1.493660315115663e-05</v>
       </c>
       <c r="CL95" t="n">
-        <v>9.904984606628778e-06</v>
+        <v>9.904984606628777e-06</v>
       </c>
       <c r="CM95" t="n">
         <v>3.848003500345494e-06</v>
@@ -26322,7 +26322,7 @@
         <v>3.618690899062219e-06</v>
       </c>
       <c r="CO95" t="n">
-        <v>4.912180826054315e-06</v>
+        <v>4.912180826054314e-06</v>
       </c>
       <c r="CP95" t="n">
         <v>5.409468188951582e-06</v>
@@ -26334,28 +26334,28 @@
         <v>3.752848339379046e-06</v>
       </c>
       <c r="CS95" t="n">
-        <v>4.767374612342249e-06</v>
+        <v>4.76737461234225e-06</v>
       </c>
       <c r="CT95" t="n">
         <v>4.095933720544344e-06</v>
       </c>
       <c r="CU95" t="n">
-        <v>3.312099773155222e-06</v>
+        <v>3.312099773155223e-06</v>
       </c>
       <c r="CV95" t="n">
-        <v>3.755623630604031e-06</v>
+        <v>3.75562363060403e-06</v>
       </c>
       <c r="CW95" t="n">
         <v>3.722406819970369e-06</v>
       </c>
       <c r="CX95" t="n">
-        <v>2.893127503385707e-06</v>
+        <v>2.893127503385706e-06</v>
       </c>
       <c r="CY95" t="n">
         <v>4.224904667456086e-06</v>
       </c>
       <c r="CZ95" t="n">
-        <v>4.339935667311627e-06</v>
+        <v>4.339935667311626e-06</v>
       </c>
       <c r="DA95" t="n">
         <v>3.738381653270341e-06</v>
@@ -29242,7 +29242,7 @@
         <v>6.744321539686166e-06</v>
       </c>
       <c r="C110" t="n">
-        <v>1.168770395950593e-05</v>
+        <v>1.168770395950592e-05</v>
       </c>
       <c r="D110" t="n">
         <v>1.127849466575618e-05</v>
@@ -29287,7 +29287,7 @@
         <v>1.13861265213e-06</v>
       </c>
       <c r="R110" t="n">
-        <v>3.001788510400001e-06</v>
+        <v>3.0017885104e-06</v>
       </c>
       <c r="S110" t="n">
         <v>2.28862740226e-06</v>
@@ -29305,7 +29305,7 @@
         <v>1.4604383444e-06</v>
       </c>
       <c r="X110" t="n">
-        <v>7.959529317599999e-07</v>
+        <v>7.9595293176e-07</v>
       </c>
       <c r="Y110" t="n">
         <v>1.224035331e-06</v>
@@ -29362,13 +29362,13 @@
         <v>2.29185956555e-06</v>
       </c>
       <c r="AQ110" t="n">
-        <v>9.697944721200003e-07</v>
+        <v>9.697944721200001e-07</v>
       </c>
       <c r="AR110" t="n">
-        <v>8.427629938599999e-07</v>
+        <v>8.427629938600001e-07</v>
       </c>
       <c r="AS110" t="n">
-        <v>9.091357166700001e-07</v>
+        <v>9.0913571667e-07</v>
       </c>
       <c r="AT110" t="n">
         <v>1.09205763122e-06</v>
@@ -29386,7 +29386,7 @@
         <v>1.550751041803479e-05</v>
       </c>
       <c r="AY110" t="n">
-        <v>2.282281725126863e-05</v>
+        <v>2.282281725126862e-05</v>
       </c>
       <c r="AZ110" t="n">
         <v>2.153401440556335e-05</v>
@@ -29401,13 +29401,13 @@
         <v>1.195347828481823e-05</v>
       </c>
       <c r="BD110" t="n">
-        <v>8.050679549649859e-06</v>
+        <v>8.050679549649857e-06</v>
       </c>
       <c r="BE110" t="n">
         <v>3.101428511308214e-06</v>
       </c>
       <c r="BF110" t="n">
-        <v>3.280030870113491e-06</v>
+        <v>3.280030870113492e-06</v>
       </c>
       <c r="BG110" t="n">
         <v>3.07422538493843e-06</v>
@@ -29446,7 +29446,7 @@
         <v>6.269798169711059e-05</v>
       </c>
       <c r="BS110" t="n">
-        <v>9.907763821469444e-06</v>
+        <v>9.907763821469443e-06</v>
       </c>
       <c r="BT110" t="n">
         <v>1.072955633328995e-05</v>
@@ -29473,7 +29473,7 @@
         <v>1.161627282241478e-05</v>
       </c>
       <c r="CB110" t="n">
-        <v>6.403522065065467e-06</v>
+        <v>6.403522065065468e-06</v>
       </c>
       <c r="CC110" t="n">
         <v>5.186332193458353e-06</v>
@@ -29509,7 +29509,7 @@
         <v>2.001515407434272e-06</v>
       </c>
       <c r="CN110" t="n">
-        <v>2.088295196266975e-06</v>
+        <v>2.088295196266976e-06</v>
       </c>
       <c r="CO110" t="n">
         <v>1.956013199803772e-06</v>
@@ -29554,7 +29554,7 @@
         <v>1.969676292487417e-06</v>
       </c>
       <c r="DC110" t="n">
-        <v>2.026631056943738e-06</v>
+        <v>2.026631056943737e-06</v>
       </c>
       <c r="DD110" t="n">
         <v>2.047861214541596e-06</v>
@@ -31305,7 +31305,7 @@
         <v>3.775527858669866e-06</v>
       </c>
       <c r="DN119" t="n">
-        <v>3.947763018300711e-06</v>
+        <v>3.94776301830071e-06</v>
       </c>
       <c r="DO119" t="n">
         <v>3.849073866797326e-06</v>
@@ -33657,7 +33657,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>4.866501051748607e-07</v>
+        <v>4.866501051748608e-07</v>
       </c>
       <c r="C135" t="n">
         <v>7.43342611361628e-07</v>
@@ -33687,7 +33687,7 @@
         <v>2.7688987079e-07</v>
       </c>
       <c r="L135" t="n">
-        <v>2.670949748900001e-07</v>
+        <v>2.6709497489e-07</v>
       </c>
       <c r="M135" t="n">
         <v>3.967632171700001e-07</v>
@@ -33708,7 +33708,7 @@
         <v>5.0247646134e-07</v>
       </c>
       <c r="S135" t="n">
-        <v>5.443394953900001e-07</v>
+        <v>5.443394953900002e-07</v>
       </c>
       <c r="T135" t="n">
         <v>4.5455806212e-07</v>
@@ -33756,7 +33756,7 @@
         <v>4.5079539983e-07</v>
       </c>
       <c r="AI135" t="n">
-        <v>5.126905734000001e-07</v>
+        <v>5.126905734e-07</v>
       </c>
       <c r="AJ135" t="n">
         <v>5.2048675868e-07</v>
@@ -33777,7 +33777,7 @@
         <v>5.0466413306e-07</v>
       </c>
       <c r="AP135" t="n">
-        <v>5.023486901200001e-07</v>
+        <v>5.0234869012e-07</v>
       </c>
       <c r="AQ135" t="n">
         <v>5.309659806599999e-07</v>
@@ -33807,7 +33807,7 @@
         <v>6.905639763787176e-07</v>
       </c>
       <c r="AZ135" t="n">
-        <v>5.479984300476028e-07</v>
+        <v>5.479984300476029e-07</v>
       </c>
       <c r="BA135" t="n">
         <v>3.645580189984423e-07</v>
@@ -33873,7 +33873,7 @@
         <v>9.192100996224135e-07</v>
       </c>
       <c r="BV135" t="n">
-        <v>8.986588762387384e-07</v>
+        <v>8.986588762387385e-07</v>
       </c>
       <c r="BW135" t="n">
         <v>1.958487361345722e-06</v>
